--- a/simulation/ATLANTA_2018_19_CAUSALITY_LEDGER.xlsx
+++ b/simulation/ATLANTA_2018_19_CAUSALITY_LEDGER.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R5e9a8a57774e4a37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Ledger" sheetId="2" r:id="Rb4b4a76e845549b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season Minutes" sheetId="3" r:id="Rb38bcf29f3f04f21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft Bridge" sheetId="4" r:id="R5a854161d79545d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gate Audit" sheetId="5" r:id="R6a11b9c68c094133"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" r:id="R6f33046343f843bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R243ec70f0c2544d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Ledger" sheetId="2" r:id="R004ae6c0cc164082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season Minutes" sheetId="3" r:id="R89934bb09586473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2018 Draft Board" sheetId="4" r:id="R4a11c7dc755f4e8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft Bridge" sheetId="5" r:id="Rdfaeae280acc4ad5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gate Audit" sheetId="6" r:id="Ra5b8f023a20e46c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" r:id="R41ecceb893434cf6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +175,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="59">
+  <x:cellXfs count="60">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -278,6 +279,15 @@
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -288,12 +298,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -376,7 +380,26 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourceTable" displayName="SourceTable" ref="A4:D16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DraftBoardTable" displayName="DraftBoardTable" ref="A6:K37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="11">
+    <x:tableColumn id="1" name="Pick"/>
+    <x:tableColumn id="2" name="Actual destination"/>
+    <x:tableColumn id="3" name="Actual player"/>
+    <x:tableColumn id="4" name="Actual trade/path"/>
+    <x:tableColumn id="5" name="CF destination"/>
+    <x:tableColumn id="6" name="CF player"/>
+    <x:tableColumn id="7" name="Status"/>
+    <x:tableColumn id="8" name="Incoming displaced"/>
+    <x:tableColumn id="9" name="Decision reason"/>
+    <x:tableColumn id="10" name="Downstream"/>
+    <x:tableColumn id="11" name="Source ID"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourceTable" displayName="SourceTable" ref="A4:D25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Source"/>
@@ -583,7 +606,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="36" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="44" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
@@ -594,7 +617,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="18" t="str">
-        <x:v>ATLANTA 2018-19 — CAUSALITY LEDGER / BASELINE v0.1</x:v>
+        <x:v>ATLANTA 2018-19 — CAUSALITY LEDGER / DRAFT BOARD v0.2</x:v>
       </x:c>
       <x:c r="B1" s="19"/>
       <x:c r="C1" s="19"/>
@@ -629,7 +652,7 @@
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B4" s="20" t="str">
-        <x:v>BASELINE_PASS / COUNTERFACTUAL_HOLD</x:v>
+        <x:v>BASELINE_PASS / SECOND_TEAM_IMPACT_HOLD</x:v>
       </x:c>
       <x:c r="C4" s="20" t="str">
         <x:v>Canon</x:v>
@@ -929,7 +952,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B18" s="22" t="str">
-        <x:v>The 2019 standings/lottery cannot be FINAL until Spellman's new team and that team's season impact are resolved after rerunning 2018 picks 30-60.</x:v>
+        <x:v>Spellman's destination is resolved at San Antonio #49. The 2019 standings/lottery cannot be FINAL until the Spurs' 2018-19 impact is closed.</x:v>
       </x:c>
       <x:c r="C18" s="22"/>
       <x:c r="D18" s="22"/>
@@ -8001,7 +8024,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf909ac086013489a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R187056fa3cab45d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9040,12 +9063,1194 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a13c7de518445bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d4fefc5fb924228"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="48" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>2018 PICKS 30-60 — COMPRESSED COUNTERFACTUAL BOARD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>Scanned picks</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="n">
+        <x:f>COUNTA(A7:A37)</x:f>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>Changed/cascade</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="n">
+        <x:f>COUNTIF(G7:G37,"CHANGED")+COUNTIF(G7:G37,"CASCADE")</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>Unchanged</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="n">
+        <x:f>COUNTIF(G7:G37,"UNCHANGED")</x:f>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>Next blocker</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>Spurs 2018-19 impact</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="str">
+        <x:v>Pick</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>Actual destination</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>Actual player</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>Actual trade/path</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>CF destination</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>CF player</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="str">
+        <x:v>Incoming displaced</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="str">
+        <x:v>Decision reason</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str">
+        <x:v>Downstream</x:v>
+      </x:c>
+      <x:c r="K6" s="11" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="53" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B7" s="53" t="str">
+        <x:v>Atlanta Hawks</x:v>
+      </x:c>
+      <x:c r="C7" s="53" t="str">
+        <x:v>Omari Spellman</x:v>
+      </x:c>
+      <x:c r="D7" s="53" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E7" s="53" t="str">
+        <x:v>Atlanta Hawks</x:v>
+      </x:c>
+      <x:c r="F7" s="53" t="str">
+        <x:v>Fictional protagonist</x:v>
+      </x:c>
+      <x:c r="G7" s="53" t="str">
+        <x:v>CHANGED</x:v>
+      </x:c>
+      <x:c r="H7" s="53" t="str">
+        <x:v>Protagonist</x:v>
+      </x:c>
+      <x:c r="I7" s="53" t="str">
+        <x:v>The new player occupies Atlanta's actual #30 slot.</x:v>
+      </x:c>
+      <x:c r="J7" s="53" t="str">
+        <x:v>Atlanta roster/minutes rerun</x:v>
+      </x:c>
+      <x:c r="K7" s="53" t="str">
+        <x:v>S12/S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="51" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B8" s="51" t="str">
+        <x:v>Phoenix Suns</x:v>
+      </x:c>
+      <x:c r="C8" s="51" t="str">
+        <x:v>Elie Okobo</x:v>
+      </x:c>
+      <x:c r="D8" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E8" s="51" t="str">
+        <x:v>Phoenix Suns</x:v>
+      </x:c>
+      <x:c r="F8" s="51" t="str">
+        <x:v>Elie Okobo</x:v>
+      </x:c>
+      <x:c r="G8" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H8" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I8" s="51" t="str">
+        <x:v>Guard-development choice remains rational.</x:v>
+      </x:c>
+      <x:c r="J8" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K8" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="51" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B9" s="51" t="str">
+        <x:v>Memphis Grizzlies</x:v>
+      </x:c>
+      <x:c r="C9" s="51" t="str">
+        <x:v>Jevon Carter</x:v>
+      </x:c>
+      <x:c r="D9" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E9" s="51" t="str">
+        <x:v>Memphis Grizzlies</x:v>
+      </x:c>
+      <x:c r="F9" s="51" t="str">
+        <x:v>Jevon Carter</x:v>
+      </x:c>
+      <x:c r="G9" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H9" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I9" s="51" t="str">
+        <x:v>Point-of-attack guard need remains distinct.</x:v>
+      </x:c>
+      <x:c r="J9" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K9" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="51" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B10" s="51" t="str">
+        <x:v>Dallas Mavericks</x:v>
+      </x:c>
+      <x:c r="C10" s="51" t="str">
+        <x:v>Jalen Brunson</x:v>
+      </x:c>
+      <x:c r="D10" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E10" s="51" t="str">
+        <x:v>Dallas Mavericks</x:v>
+      </x:c>
+      <x:c r="F10" s="51" t="str">
+        <x:v>Jalen Brunson</x:v>
+      </x:c>
+      <x:c r="G10" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H10" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I10" s="51" t="str">
+        <x:v>Lead-guard depth remains the stronger fit.</x:v>
+      </x:c>
+      <x:c r="J10" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K10" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="51" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B11" s="51" t="str">
+        <x:v>Charlotte Hornets</x:v>
+      </x:c>
+      <x:c r="C11" s="51" t="str">
+        <x:v>Devonte' Graham</x:v>
+      </x:c>
+      <x:c r="D11" s="51" t="str">
+        <x:v>Rights from ATL for 2019 + 2023 seconds</x:v>
+      </x:c>
+      <x:c r="E11" s="51" t="str">
+        <x:v>Charlotte Hornets</x:v>
+      </x:c>
+      <x:c r="F11" s="51" t="str">
+        <x:v>Devonte' Graham</x:v>
+      </x:c>
+      <x:c r="G11" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H11" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I11" s="51" t="str">
+        <x:v>Charlotte paid two future seconds for a directed guard choice.</x:v>
+      </x:c>
+      <x:c r="J11" s="51" t="str">
+        <x:v>ATL asset trade preserved</x:v>
+      </x:c>
+      <x:c r="K11" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="51" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B12" s="51" t="str">
+        <x:v>Orlando Magic</x:v>
+      </x:c>
+      <x:c r="C12" s="51" t="str">
+        <x:v>Melvin Frazier</x:v>
+      </x:c>
+      <x:c r="D12" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E12" s="51" t="str">
+        <x:v>Orlando Magic</x:v>
+      </x:c>
+      <x:c r="F12" s="51" t="str">
+        <x:v>Melvin Frazier</x:v>
+      </x:c>
+      <x:c r="G12" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H12" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I12" s="51" t="str">
+        <x:v>Wing-development lane remains distinct.</x:v>
+      </x:c>
+      <x:c r="J12" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K12" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="51" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B13" s="51" t="str">
+        <x:v>New York Knicks</x:v>
+      </x:c>
+      <x:c r="C13" s="51" t="str">
+        <x:v>Mitchell Robinson</x:v>
+      </x:c>
+      <x:c r="D13" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E13" s="51" t="str">
+        <x:v>New York Knicks</x:v>
+      </x:c>
+      <x:c r="F13" s="51" t="str">
+        <x:v>Mitchell Robinson</x:v>
+      </x:c>
+      <x:c r="G13" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H13" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I13" s="51" t="str">
+        <x:v>Robinson's upside remains the board priority.</x:v>
+      </x:c>
+      <x:c r="J13" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K13" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="51" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B14" s="51" t="str">
+        <x:v>Portland Trail Blazers</x:v>
+      </x:c>
+      <x:c r="C14" s="51" t="str">
+        <x:v>Gary Trent Jr.</x:v>
+      </x:c>
+      <x:c r="D14" s="51" t="str">
+        <x:v>Rights from SAC</x:v>
+      </x:c>
+      <x:c r="E14" s="51" t="str">
+        <x:v>Portland Trail Blazers</x:v>
+      </x:c>
+      <x:c r="F14" s="51" t="str">
+        <x:v>Gary Trent Jr.</x:v>
+      </x:c>
+      <x:c r="G14" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H14" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I14" s="51" t="str">
+        <x:v>Perimeter shooting/development need remains.</x:v>
+      </x:c>
+      <x:c r="J14" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K14" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="51" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B15" s="51" t="str">
+        <x:v>Detroit Pistons</x:v>
+      </x:c>
+      <x:c r="C15" s="51" t="str">
+        <x:v>Khyri Thomas</x:v>
+      </x:c>
+      <x:c r="D15" s="51" t="str">
+        <x:v>Rights from PHI</x:v>
+      </x:c>
+      <x:c r="E15" s="51" t="str">
+        <x:v>Detroit Pistons</x:v>
+      </x:c>
+      <x:c r="F15" s="51" t="str">
+        <x:v>Khyri Thomas</x:v>
+      </x:c>
+      <x:c r="G15" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H15" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I15" s="51" t="str">
+        <x:v>Perimeter defense need remains distinct.</x:v>
+      </x:c>
+      <x:c r="J15" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K15" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="51" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B16" s="51" t="str">
+        <x:v>Los Angeles Lakers</x:v>
+      </x:c>
+      <x:c r="C16" s="51" t="str">
+        <x:v>Isaac Bonga</x:v>
+      </x:c>
+      <x:c r="D16" s="51" t="str">
+        <x:v>Rights from PHI</x:v>
+      </x:c>
+      <x:c r="E16" s="51" t="str">
+        <x:v>Los Angeles Lakers</x:v>
+      </x:c>
+      <x:c r="F16" s="51" t="str">
+        <x:v>Isaac Bonga</x:v>
+      </x:c>
+      <x:c r="G16" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H16" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I16" s="51" t="str">
+        <x:v>Lakers already used #25 on stretch big Moritz Wagner.</x:v>
+      </x:c>
+      <x:c r="J16" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K16" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="51" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B17" s="51" t="str">
+        <x:v>Brooklyn Nets</x:v>
+      </x:c>
+      <x:c r="C17" s="51" t="str">
+        <x:v>Rodions Kurucs</x:v>
+      </x:c>
+      <x:c r="D17" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E17" s="51" t="str">
+        <x:v>Brooklyn Nets</x:v>
+      </x:c>
+      <x:c r="F17" s="51" t="str">
+        <x:v>Rodions Kurucs</x:v>
+      </x:c>
+      <x:c r="G17" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H17" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I17" s="51" t="str">
+        <x:v>Long-running Kurucs scouting interest remains decisive.</x:v>
+      </x:c>
+      <x:c r="J17" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K17" s="51" t="str">
+        <x:v>S17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="51" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B18" s="51" t="str">
+        <x:v>Denver Nuggets</x:v>
+      </x:c>
+      <x:c r="C18" s="51" t="str">
+        <x:v>Jarred Vanderbilt</x:v>
+      </x:c>
+      <x:c r="D18" s="51" t="str">
+        <x:v>Rights from ORL</x:v>
+      </x:c>
+      <x:c r="E18" s="51" t="str">
+        <x:v>Denver Nuggets</x:v>
+      </x:c>
+      <x:c r="F18" s="51" t="str">
+        <x:v>Jarred Vanderbilt</x:v>
+      </x:c>
+      <x:c r="G18" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H18" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I18" s="51" t="str">
+        <x:v>Vanderbilt upside remains the preferred development bet.</x:v>
+      </x:c>
+      <x:c r="J18" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K18" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="51" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B19" s="51" t="str">
+        <x:v>Detroit Pistons</x:v>
+      </x:c>
+      <x:c r="C19" s="51" t="str">
+        <x:v>Bruce Brown</x:v>
+      </x:c>
+      <x:c r="D19" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E19" s="51" t="str">
+        <x:v>Detroit Pistons</x:v>
+      </x:c>
+      <x:c r="F19" s="51" t="str">
+        <x:v>Bruce Brown</x:v>
+      </x:c>
+      <x:c r="G19" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H19" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I19" s="51" t="str">
+        <x:v>Guard/wing role remains distinct.</x:v>
+      </x:c>
+      <x:c r="J19" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K19" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="51" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B20" s="51" t="str">
+        <x:v>Orlando Magic</x:v>
+      </x:c>
+      <x:c r="C20" s="51" t="str">
+        <x:v>Justin Jackson</x:v>
+      </x:c>
+      <x:c r="D20" s="51" t="str">
+        <x:v>Rights from DEN</x:v>
+      </x:c>
+      <x:c r="E20" s="51" t="str">
+        <x:v>Orlando Magic</x:v>
+      </x:c>
+      <x:c r="F20" s="51" t="str">
+        <x:v>Justin Jackson</x:v>
+      </x:c>
+      <x:c r="G20" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H20" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I20" s="51" t="str">
+        <x:v>Wing-development lane remains distinct.</x:v>
+      </x:c>
+      <x:c r="J20" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K20" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="51" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B21" s="51" t="str">
+        <x:v>Washington Wizards</x:v>
+      </x:c>
+      <x:c r="C21" s="51" t="str">
+        <x:v>Issuf Sanon</x:v>
+      </x:c>
+      <x:c r="D21" s="51" t="str">
+        <x:v>Own pick; overseas stash</x:v>
+      </x:c>
+      <x:c r="E21" s="51" t="str">
+        <x:v>Washington Wizards</x:v>
+      </x:c>
+      <x:c r="F21" s="51" t="str">
+        <x:v>Issuf Sanon</x:v>
+      </x:c>
+      <x:c r="G21" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H21" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I21" s="51" t="str">
+        <x:v>Roster/cap plan explicitly favored an overseas stash.</x:v>
+      </x:c>
+      <x:c r="J21" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K21" s="51" t="str">
+        <x:v>S16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="51" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B22" s="51" t="str">
+        <x:v>Oklahoma City Thunder</x:v>
+      </x:c>
+      <x:c r="C22" s="51" t="str">
+        <x:v>Hamidou Diallo</x:v>
+      </x:c>
+      <x:c r="D22" s="51" t="str">
+        <x:v>Rights via BKN/CHA</x:v>
+      </x:c>
+      <x:c r="E22" s="51" t="str">
+        <x:v>Oklahoma City Thunder</x:v>
+      </x:c>
+      <x:c r="F22" s="51" t="str">
+        <x:v>Hamidou Diallo</x:v>
+      </x:c>
+      <x:c r="G22" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H22" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I22" s="51" t="str">
+        <x:v>Athletic guard target remains distinct.</x:v>
+      </x:c>
+      <x:c r="J22" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K22" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="51" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B23" s="51" t="str">
+        <x:v>Houston Rockets</x:v>
+      </x:c>
+      <x:c r="C23" s="51" t="str">
+        <x:v>De'Anthony Melton</x:v>
+      </x:c>
+      <x:c r="D23" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E23" s="51" t="str">
+        <x:v>Houston Rockets</x:v>
+      </x:c>
+      <x:c r="F23" s="51" t="str">
+        <x:v>De'Anthony Melton</x:v>
+      </x:c>
+      <x:c r="G23" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H23" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I23" s="51" t="str">
+        <x:v>Guard asset profile remains distinct.</x:v>
+      </x:c>
+      <x:c r="J23" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K23" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="51" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B24" s="51" t="str">
+        <x:v>Los Angeles Lakers</x:v>
+      </x:c>
+      <x:c r="C24" s="51" t="str">
+        <x:v>Svi Mykhailiuk</x:v>
+      </x:c>
+      <x:c r="D24" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E24" s="51" t="str">
+        <x:v>Los Angeles Lakers</x:v>
+      </x:c>
+      <x:c r="F24" s="51" t="str">
+        <x:v>Svi Mykhailiuk</x:v>
+      </x:c>
+      <x:c r="G24" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H24" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I24" s="51" t="str">
+        <x:v>Shooting role remains distinct.</x:v>
+      </x:c>
+      <x:c r="J24" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K24" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="51" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B25" s="51" t="str">
+        <x:v>Minnesota Timberwolves</x:v>
+      </x:c>
+      <x:c r="C25" s="51" t="str">
+        <x:v>Keita Bates-Diop</x:v>
+      </x:c>
+      <x:c r="D25" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E25" s="51" t="str">
+        <x:v>Minnesota Timberwolves</x:v>
+      </x:c>
+      <x:c r="F25" s="51" t="str">
+        <x:v>Keita Bates-Diop</x:v>
+      </x:c>
+      <x:c r="G25" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H25" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I25" s="51" t="str">
+        <x:v>Wing-forward choice does not require a cascade.</x:v>
+      </x:c>
+      <x:c r="J25" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K25" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="53" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B26" s="53" t="str">
+        <x:v>San Antonio Spurs</x:v>
+      </x:c>
+      <x:c r="C26" s="53" t="str">
+        <x:v>Chimezie Metu</x:v>
+      </x:c>
+      <x:c r="D26" s="53" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E26" s="53" t="str">
+        <x:v>San Antonio Spurs</x:v>
+      </x:c>
+      <x:c r="F26" s="53" t="str">
+        <x:v>Omari Spellman</x:v>
+      </x:c>
+      <x:c r="G26" s="53" t="str">
+        <x:v>CHANGED</x:v>
+      </x:c>
+      <x:c r="H26" s="53" t="str">
+        <x:v>Spellman</x:v>
+      </x:c>
+      <x:c r="I26" s="53" t="str">
+        <x:v>Spellman worked out for San Antonio and fit its spacing/IQ profile.</x:v>
+      </x:c>
+      <x:c r="J26" s="53" t="str">
+        <x:v>Spurs 2018-19 impact HOLD</x:v>
+      </x:c>
+      <x:c r="K26" s="53" t="str">
+        <x:v>S14/S15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="51" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B27" s="51" t="str">
+        <x:v>Indiana Pacers</x:v>
+      </x:c>
+      <x:c r="C27" s="51" t="str">
+        <x:v>Alize Johnson</x:v>
+      </x:c>
+      <x:c r="D27" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E27" s="51" t="str">
+        <x:v>Indiana Pacers</x:v>
+      </x:c>
+      <x:c r="F27" s="51" t="str">
+        <x:v>Alize Johnson</x:v>
+      </x:c>
+      <x:c r="G27" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H27" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I27" s="51" t="str">
+        <x:v>Actual forward choice remains available.</x:v>
+      </x:c>
+      <x:c r="J27" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K27" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="51" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B28" s="51" t="str">
+        <x:v>New Orleans Pelicans</x:v>
+      </x:c>
+      <x:c r="C28" s="51" t="str">
+        <x:v>Tony Carr</x:v>
+      </x:c>
+      <x:c r="D28" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E28" s="51" t="str">
+        <x:v>New Orleans Pelicans</x:v>
+      </x:c>
+      <x:c r="F28" s="51" t="str">
+        <x:v>Tony Carr</x:v>
+      </x:c>
+      <x:c r="G28" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H28" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I28" s="51" t="str">
+        <x:v>Guard-development choice remains distinct.</x:v>
+      </x:c>
+      <x:c r="J28" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K28" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="51" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B29" s="51" t="str">
+        <x:v>Houston Rockets</x:v>
+      </x:c>
+      <x:c r="C29" s="51" t="str">
+        <x:v>Vincent Edwards</x:v>
+      </x:c>
+      <x:c r="D29" s="51" t="str">
+        <x:v>Rights from UTA</x:v>
+      </x:c>
+      <x:c r="E29" s="51" t="str">
+        <x:v>Houston Rockets</x:v>
+      </x:c>
+      <x:c r="F29" s="51" t="str">
+        <x:v>Vincent Edwards</x:v>
+      </x:c>
+      <x:c r="G29" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H29" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I29" s="51" t="str">
+        <x:v>Wing-development choice remains distinct.</x:v>
+      </x:c>
+      <x:c r="J29" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K29" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="51" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B30" s="51" t="str">
+        <x:v>Oklahoma City Thunder</x:v>
+      </x:c>
+      <x:c r="C30" s="51" t="str">
+        <x:v>Devon Hall</x:v>
+      </x:c>
+      <x:c r="D30" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E30" s="51" t="str">
+        <x:v>Oklahoma City Thunder</x:v>
+      </x:c>
+      <x:c r="F30" s="51" t="str">
+        <x:v>Devon Hall</x:v>
+      </x:c>
+      <x:c r="G30" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H30" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I30" s="51" t="str">
+        <x:v>Perimeter/stash route remains distinct.</x:v>
+      </x:c>
+      <x:c r="J30" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K30" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="51" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B31" s="51" t="str">
+        <x:v>Philadelphia 76ers</x:v>
+      </x:c>
+      <x:c r="C31" s="51" t="str">
+        <x:v>Shake Milton</x:v>
+      </x:c>
+      <x:c r="D31" s="51" t="str">
+        <x:v>Rights from DAL</x:v>
+      </x:c>
+      <x:c r="E31" s="51" t="str">
+        <x:v>Philadelphia 76ers</x:v>
+      </x:c>
+      <x:c r="F31" s="51" t="str">
+        <x:v>Shake Milton</x:v>
+      </x:c>
+      <x:c r="G31" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H31" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I31" s="51" t="str">
+        <x:v>Guard target and trade structure remain intact.</x:v>
+      </x:c>
+      <x:c r="J31" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K31" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="51" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B32" s="51" t="str">
+        <x:v>Charlotte Hornets</x:v>
+      </x:c>
+      <x:c r="C32" s="51" t="str">
+        <x:v>Arnoldas Kulboka</x:v>
+      </x:c>
+      <x:c r="D32" s="51" t="str">
+        <x:v>Own pick; overseas stash</x:v>
+      </x:c>
+      <x:c r="E32" s="51" t="str">
+        <x:v>Charlotte Hornets</x:v>
+      </x:c>
+      <x:c r="F32" s="51" t="str">
+        <x:v>Arnoldas Kulboka</x:v>
+      </x:c>
+      <x:c r="G32" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H32" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I32" s="51" t="str">
+        <x:v>Overseas-stash route remains distinct.</x:v>
+      </x:c>
+      <x:c r="J32" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K32" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="53" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B33" s="53" t="str">
+        <x:v>Dallas Mavericks</x:v>
+      </x:c>
+      <x:c r="C33" s="53" t="str">
+        <x:v>Ray Spalding</x:v>
+      </x:c>
+      <x:c r="D33" s="53" t="str">
+        <x:v>Rights from PHI</x:v>
+      </x:c>
+      <x:c r="E33" s="53" t="str">
+        <x:v>Dallas Mavericks</x:v>
+      </x:c>
+      <x:c r="F33" s="53" t="str">
+        <x:v>Chimezie Metu</x:v>
+      </x:c>
+      <x:c r="G33" s="53" t="str">
+        <x:v>CASCADE</x:v>
+      </x:c>
+      <x:c r="H33" s="53" t="str">
+        <x:v>Metu</x:v>
+      </x:c>
+      <x:c r="I33" s="53" t="str">
+        <x:v>Metu is the displaced #49 athletic big and remains above this slot.</x:v>
+      </x:c>
+      <x:c r="J33" s="53" t="str">
+        <x:v>Dallas role/minutes HOLD</x:v>
+      </x:c>
+      <x:c r="K33" s="53" t="str">
+        <x:v>S13/S15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="51" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B34" s="51" t="str">
+        <x:v>Oklahoma City Thunder</x:v>
+      </x:c>
+      <x:c r="C34" s="51" t="str">
+        <x:v>Kevin Hervey</x:v>
+      </x:c>
+      <x:c r="D34" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E34" s="51" t="str">
+        <x:v>Oklahoma City Thunder</x:v>
+      </x:c>
+      <x:c r="F34" s="51" t="str">
+        <x:v>Kevin Hervey</x:v>
+      </x:c>
+      <x:c r="G34" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H34" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I34" s="51" t="str">
+        <x:v>Actual forward choice remains available.</x:v>
+      </x:c>
+      <x:c r="J34" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K34" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="53" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B35" s="53" t="str">
+        <x:v>Denver Nuggets</x:v>
+      </x:c>
+      <x:c r="C35" s="53" t="str">
+        <x:v>Thomas Welsh</x:v>
+      </x:c>
+      <x:c r="D35" s="53" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E35" s="53" t="str">
+        <x:v>Denver Nuggets</x:v>
+      </x:c>
+      <x:c r="F35" s="53" t="str">
+        <x:v>Ray Spalding</x:v>
+      </x:c>
+      <x:c r="G35" s="53" t="str">
+        <x:v>CASCADE</x:v>
+      </x:c>
+      <x:c r="H35" s="53" t="str">
+        <x:v>Spalding</x:v>
+      </x:c>
+      <x:c r="I35" s="53" t="str">
+        <x:v>Spalding was graded in the drafted second-round big tier.</x:v>
+      </x:c>
+      <x:c r="J35" s="53" t="str">
+        <x:v>Denver role/two-way HOLD</x:v>
+      </x:c>
+      <x:c r="K35" s="53" t="str">
+        <x:v>S18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="51" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B36" s="51" t="str">
+        <x:v>Phoenix Suns</x:v>
+      </x:c>
+      <x:c r="C36" s="51" t="str">
+        <x:v>George King</x:v>
+      </x:c>
+      <x:c r="D36" s="51" t="str">
+        <x:v>Own pick</x:v>
+      </x:c>
+      <x:c r="E36" s="51" t="str">
+        <x:v>Phoenix Suns</x:v>
+      </x:c>
+      <x:c r="F36" s="51" t="str">
+        <x:v>George King</x:v>
+      </x:c>
+      <x:c r="G36" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H36" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I36" s="51" t="str">
+        <x:v>Actual wing choice remains available.</x:v>
+      </x:c>
+      <x:c r="J36" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K36" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="51" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B37" s="51" t="str">
+        <x:v>Dallas Mavericks</x:v>
+      </x:c>
+      <x:c r="C37" s="51" t="str">
+        <x:v>Kostas Antetokounmpo</x:v>
+      </x:c>
+      <x:c r="D37" s="51" t="str">
+        <x:v>Rights from PHI</x:v>
+      </x:c>
+      <x:c r="E37" s="51" t="str">
+        <x:v>Dallas Mavericks</x:v>
+      </x:c>
+      <x:c r="F37" s="51" t="str">
+        <x:v>Kostas Antetokounmpo</x:v>
+      </x:c>
+      <x:c r="G37" s="52" t="str">
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="H37" s="51" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="I37" s="51" t="str">
+        <x:v>Second acquired pick and upside bet remain intact.</x:v>
+      </x:c>
+      <x:c r="J37" s="51" t="str">
+        <x:v>Actual path preserved</x:v>
+      </x:c>
+      <x:c r="K37" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:K2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd845085108c84979"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -9111,10 +10316,10 @@
       <x:c r="D5" s="13" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E5" s="51" t="n">
+      <x:c r="E5" s="54" t="n">
         <x:v>0.105</x:v>
       </x:c>
-      <x:c r="F5" s="51" t="n">
+      <x:c r="F5" s="54" t="n">
         <x:v>0.4212</x:v>
       </x:c>
       <x:c r="G5" s="13" t="n">
@@ -9143,10 +10348,10 @@
       <x:c r="D6" s="13" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E6" s="51" t="n">
+      <x:c r="E6" s="54" t="n">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="F6" s="51" t="n">
+      <x:c r="F6" s="54" t="n">
         <x:v>0.263</x:v>
       </x:c>
       <x:c r="G6" s="13" t="n">
@@ -9242,8 +10447,8 @@
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="54" t="str">
-        <x:v>FINAL BLOCKER: rerun the 2018 #30-60 board, resolve Spellman's new team, and close that team's 2018-19 impact.</x:v>
+      <x:c r="A14" s="57" t="str">
+        <x:v>FINAL BLOCKER: Spellman is resolved to San Antonio #49; close the Spurs' 2018-19 rotation and game impact before standings/lottery.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9257,7 +10462,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -9295,225 +10500,225 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="56" t="str">
+      <x:c r="A5" s="51" t="str">
         <x:v>G0</x:v>
       </x:c>
-      <x:c r="B5" s="56" t="str">
+      <x:c r="B5" s="51" t="str">
         <x:v>Spellman destination + second-team impact</x:v>
       </x:c>
-      <x:c r="C5" s="56" t="str">
-        <x:v>Unresolved after 2018 #30</x:v>
-      </x:c>
-      <x:c r="D5" s="57" t="str">
-        <x:v>HOLD</x:v>
-      </x:c>
-      <x:c r="E5" s="56" t="str">
+      <x:c r="C5" s="51" t="str">
+        <x:v>Spellman → Spurs #49; Spurs impact not executed</x:v>
+      </x:c>
+      <x:c r="D5" s="53" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="E5" s="51" t="str">
         <x:v>FINAL standings/lottery</x:v>
       </x:c>
-      <x:c r="F5" s="56" t="str">
-        <x:v>Run 2018 picks 30-60</x:v>
+      <x:c r="F5" s="51" t="str">
+        <x:v>Model Spurs 2018-19</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="56" t="str">
+      <x:c r="A6" s="51" t="str">
         <x:v>G1</x:v>
       </x:c>
-      <x:c r="B6" s="56" t="str">
+      <x:c r="B6" s="51" t="str">
         <x:v>82 unique + 29-53 + score/OT checksum</x:v>
       </x:c>
-      <x:c r="C6" s="56" t="str">
+      <x:c r="C6" s="51" t="str">
         <x:v>82 rows; 29-53; 9,294 pts; 19,855 game-min</x:v>
       </x:c>
-      <x:c r="D6" s="57" t="str">
+      <x:c r="D6" s="53" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="E6" s="56" t="str">
+      <x:c r="E6" s="51" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="F6" s="56" t="str">
+      <x:c r="F6" s="51" t="str">
         <x:v>Preserve immutable baseline</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="56" t="str">
+      <x:c r="A7" s="51" t="str">
         <x:v>G2</x:v>
       </x:c>
-      <x:c r="B7" s="56" t="str">
+      <x:c r="B7" s="51" t="str">
         <x:v>Rotation/assignment/impact priors before results</x:v>
       </x:c>
-      <x:c r="C7" s="56" t="str">
+      <x:c r="C7" s="51" t="str">
         <x:v>Only season range locked</x:v>
       </x:c>
-      <x:c r="D7" s="57" t="str">
-        <x:v>HOLD</x:v>
-      </x:c>
-      <x:c r="E7" s="56" t="str">
+      <x:c r="D7" s="53" t="str">
+        <x:v>HOLD</x:v>
+      </x:c>
+      <x:c r="E7" s="51" t="str">
         <x:v>CF execution</x:v>
       </x:c>
-      <x:c r="F7" s="56" t="str">
+      <x:c r="F7" s="51" t="str">
         <x:v>Build date-specific availability</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="56" t="str">
+      <x:c r="A8" s="51" t="str">
         <x:v>G3</x:v>
       </x:c>
-      <x:c r="B8" s="56" t="str">
+      <x:c r="B8" s="51" t="str">
         <x:v>Every game minute-conserved; no NBA/Erie collision</x:v>
       </x:c>
-      <x:c r="C8" s="56" t="str">
+      <x:c r="C8" s="51" t="str">
         <x:v>Season cap proven; player-game not built</x:v>
       </x:c>
-      <x:c r="D8" s="57" t="str">
-        <x:v>HOLD</x:v>
-      </x:c>
-      <x:c r="E8" s="56" t="str">
+      <x:c r="D8" s="53" t="str">
+        <x:v>HOLD</x:v>
+      </x:c>
+      <x:c r="E8" s="51" t="str">
         <x:v>CF execution</x:v>
       </x:c>
-      <x:c r="F8" s="56" t="str">
+      <x:c r="F8" s="51" t="str">
         <x:v>Create player-game donor vectors</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="56" t="str">
+      <x:c r="A9" s="51" t="str">
         <x:v>G4</x:v>
       </x:c>
-      <x:c r="B9" s="56" t="str">
+      <x:c r="B9" s="51" t="str">
         <x:v>All 82 games contact classified</x:v>
       </x:c>
-      <x:c r="C9" s="56" t="str">
+      <x:c r="C9" s="51" t="str">
         <x:v>82/82 ROSTER</x:v>
       </x:c>
-      <x:c r="D9" s="57" t="str">
+      <x:c r="D9" s="53" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="E9" s="56" t="str">
+      <x:c r="E9" s="51" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="F9" s="56" t="str">
+      <x:c r="F9" s="51" t="str">
         <x:v>Upgrade DIRECT/CASCADE as needed</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="56" t="str">
+      <x:c r="A10" s="51" t="str">
         <x:v>G5</x:v>
       </x:c>
-      <x:c r="B10" s="56" t="str">
+      <x:c r="B10" s="51" t="str">
         <x:v>Pregame-only pB; fixed latent u; no manual flip</x:v>
       </x:c>
-      <x:c r="C10" s="56" t="str">
+      <x:c r="C10" s="51" t="str">
         <x:v>Method selected; inputs absent</x:v>
       </x:c>
-      <x:c r="D10" s="57" t="str">
-        <x:v>HOLD</x:v>
-      </x:c>
-      <x:c r="E10" s="56" t="str">
+      <x:c r="D10" s="53" t="str">
+        <x:v>HOLD</x:v>
+      </x:c>
+      <x:c r="E10" s="51" t="str">
         <x:v>CF result</x:v>
       </x:c>
-      <x:c r="F10" s="56" t="str">
+      <x:c r="F10" s="51" t="str">
         <x:v>Calibrate and preregister</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="56" t="str">
+      <x:c r="A11" s="51" t="str">
         <x:v>G6</x:v>
       </x:c>
-      <x:c r="B11" s="56" t="str">
+      <x:c r="B11" s="51" t="str">
         <x:v>Chronological injury/fatigue/trade updates</x:v>
       </x:c>
-      <x:c r="C11" s="56" t="str">
+      <x:c r="C11" s="51" t="str">
         <x:v>Not executed</x:v>
       </x:c>
-      <x:c r="D11" s="57" t="str">
-        <x:v>HOLD</x:v>
-      </x:c>
-      <x:c r="E11" s="56" t="str">
+      <x:c r="D11" s="53" t="str">
+        <x:v>HOLD</x:v>
+      </x:c>
+      <x:c r="E11" s="51" t="str">
         <x:v>CF result</x:v>
       </x:c>
-      <x:c r="F11" s="56" t="str">
+      <x:c r="F11" s="51" t="str">
         <x:v>Process in date order</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="56" t="str">
+      <x:c r="A12" s="51" t="str">
         <x:v>G7</x:v>
       </x:c>
-      <x:c r="B12" s="56" t="str">
+      <x:c r="B12" s="51" t="str">
         <x:v>No exact score invention; sensitivity isolated</x:v>
       </x:c>
-      <x:c r="C12" s="56" t="str">
+      <x:c r="C12" s="51" t="str">
         <x:v>No CF scores/results created</x:v>
       </x:c>
-      <x:c r="D12" s="57" t="str">
+      <x:c r="D12" s="53" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="E12" s="56" t="str">
+      <x:c r="E12" s="51" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="F12" s="56" t="str">
+      <x:c r="F12" s="51" t="str">
         <x:v>Keep results HOLD until model</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="56" t="str">
+      <x:c r="A13" s="51" t="str">
         <x:v>G8</x:v>
       </x:c>
-      <x:c r="B13" s="56" t="str">
+      <x:c r="B13" s="51" t="str">
         <x:v>Opponent W/L + league standings/tiebreaker</x:v>
       </x:c>
-      <x:c r="C13" s="56" t="str">
+      <x:c r="C13" s="51" t="str">
         <x:v>Not executed</x:v>
       </x:c>
-      <x:c r="D13" s="57" t="str">
-        <x:v>HOLD</x:v>
-      </x:c>
-      <x:c r="E13" s="56" t="str">
+      <x:c r="D13" s="53" t="str">
+        <x:v>HOLD</x:v>
+      </x:c>
+      <x:c r="E13" s="51" t="str">
         <x:v>2019 lottery</x:v>
       </x:c>
-      <x:c r="F13" s="56" t="str">
+      <x:c r="F13" s="51" t="str">
         <x:v>Build league bridge</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="56" t="str">
+      <x:c r="A14" s="51" t="str">
         <x:v>G9</x:v>
       </x:c>
-      <x:c r="B14" s="56" t="str">
+      <x:c r="B14" s="51" t="str">
         <x:v>Raw baseline immutable; run/model/seed logged</x:v>
       </x:c>
-      <x:c r="C14" s="56" t="str">
+      <x:c r="C14" s="51" t="str">
         <x:v>Workbook baseline created</x:v>
       </x:c>
-      <x:c r="D14" s="57" t="str">
+      <x:c r="D14" s="53" t="str">
         <x:v>PARTIAL</x:v>
       </x:c>
-      <x:c r="E14" s="56" t="str">
+      <x:c r="E14" s="51" t="str">
         <x:v>Reproduction</x:v>
       </x:c>
-      <x:c r="F14" s="56" t="str">
+      <x:c r="F14" s="51" t="str">
         <x:v>Add run manifest after preregistration</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="58"/>
-      <x:c r="B15" s="58"/>
-      <x:c r="C15" s="58"/>
-      <x:c r="D15" s="58"/>
-      <x:c r="E15" s="58"/>
-      <x:c r="F15" s="58"/>
+      <x:c r="A15" s="59"/>
+      <x:c r="B15" s="59"/>
+      <x:c r="C15" s="59"/>
+      <x:c r="D15" s="59"/>
+      <x:c r="E15" s="59"/>
+      <x:c r="F15" s="59"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="50" t="str">
         <x:v>OVERALL</x:v>
       </x:c>
       <x:c r="B16" s="50" t="str">
-        <x:v>BASELINE_PASS / COUNTERFACTUAL_HOLD</x:v>
+        <x:v>BASELINE_PASS / SECOND_TEAM_IMPACT_HOLD</x:v>
       </x:c>
       <x:c r="C16" s="50"/>
       <x:c r="D16" s="50"/>
       <x:c r="E16" s="50"/>
       <x:c r="F16" s="50" t="str">
-        <x:v>Atlanta-local PROVISIONAL_PASS not yet claimed</x:v>
+        <x:v>Draft path closed; Spurs season bridge remains</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9524,7 +10729,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -9554,171 +10759,297 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="56" t="str">
+      <x:c r="A5" s="51" t="str">
         <x:v>S01</x:v>
       </x:c>
-      <x:c r="B5" s="56" t="str">
+      <x:c r="B5" s="51" t="str">
         <x:v>NBA Stats — Atlanta schedule</x:v>
       </x:c>
-      <x:c r="C5" s="56" t="str">
+      <x:c r="C5" s="51" t="str">
         <x:v>82-game official schedule baseline</x:v>
       </x:c>
-      <x:c r="D5" s="56" t="str">
+      <x:c r="D5" s="51" t="str">
         <x:v>https://www.nba.com/stats/team/1610612737/schedule?Season=2018-19</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="56" t="str">
+      <x:c r="A6" s="51" t="str">
         <x:v>S02</x:v>
       </x:c>
-      <x:c r="B6" s="56" t="str">
+      <x:c r="B6" s="51" t="str">
         <x:v>ESPN — Atlanta schedule</x:v>
       </x:c>
-      <x:c r="C6" s="56" t="str">
+      <x:c r="C6" s="51" t="str">
         <x:v>Scores/order cross-check; timezone dates not authoritative</x:v>
       </x:c>
-      <x:c r="D6" s="56" t="str">
+      <x:c r="D6" s="51" t="str">
         <x:v>https://www.espn.com/nba/team/schedule?name=ATL&amp;season=2019&amp;seasontype=2</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="56" t="str">
+      <x:c r="A7" s="51" t="str">
         <x:v>S03</x:v>
       </x:c>
-      <x:c r="B7" s="56" t="str">
+      <x:c r="B7" s="51" t="str">
         <x:v>Basketball-Reference — Atlanta schedule</x:v>
       </x:c>
-      <x:c r="C7" s="56" t="str">
+      <x:c r="C7" s="51" t="str">
         <x:v>29-53 and game-log cross-check</x:v>
       </x:c>
-      <x:c r="D7" s="56" t="str">
+      <x:c r="D7" s="51" t="str">
         <x:v>https://www.basketball-reference.com/teams/ATL/2019_games.html</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="56" t="str">
+      <x:c r="A8" s="51" t="str">
         <x:v>S04</x:v>
       </x:c>
-      <x:c r="B8" s="56" t="str">
+      <x:c r="B8" s="51" t="str">
         <x:v>NBA Stats — Atlanta player totals</x:v>
       </x:c>
-      <x:c r="C8" s="56" t="str">
+      <x:c r="C8" s="51" t="str">
         <x:v>Roster GP/GS/minutes baseline</x:v>
       </x:c>
-      <x:c r="D8" s="56" t="str">
+      <x:c r="D8" s="51" t="str">
         <x:v>https://www.nba.com/stats/players/traditional?Season=2018-19&amp;SeasonType=Regular%20Season&amp;TeamID=1610612737&amp;PerMode=Totals</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="56" t="str">
+      <x:c r="A9" s="51" t="str">
         <x:v>S05</x:v>
       </x:c>
-      <x:c r="B9" s="56" t="str">
+      <x:c r="B9" s="51" t="str">
         <x:v>Hawks — Spellman injury update</x:v>
       </x:c>
-      <x:c r="C9" s="56" t="str">
+      <x:c r="C9" s="51" t="str">
         <x:v>March 1 high ankle sprain; not copied to protagonist</x:v>
       </x:c>
-      <x:c r="D9" s="56" t="str">
+      <x:c r="D9" s="51" t="str">
         <x:v>https://www.nba.com/hawks/news/omari-spellman-injury-update</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="56" t="str">
+      <x:c r="A10" s="51" t="str">
         <x:v>S06</x:v>
       </x:c>
-      <x:c r="B10" s="56" t="str">
+      <x:c r="B10" s="51" t="str">
         <x:v>NBA G League — Spellman</x:v>
       </x:c>
-      <x:c r="C10" s="56" t="str">
+      <x:c r="C10" s="51" t="str">
         <x:v>2018-19: 3 starts, 32.7 MPG</x:v>
       </x:c>
-      <x:c r="D10" s="56" t="str">
+      <x:c r="D10" s="51" t="str">
         <x:v>https://gleague.nba.com/player/1629016</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="56" t="str">
+      <x:c r="A11" s="51" t="str">
         <x:v>S07</x:v>
       </x:c>
-      <x:c r="B11" s="56" t="str">
+      <x:c r="B11" s="51" t="str">
         <x:v>Hawks — 2019 lottery odds explained</x:v>
       </x:c>
-      <x:c r="C11" s="56" t="str">
+      <x:c r="C11" s="51" t="str">
         <x:v>Atlanta/Dallas pick protection and odds baseline</x:v>
       </x:c>
-      <x:c r="D11" s="56" t="str">
+      <x:c r="D11" s="51" t="str">
         <x:v>https://www.nba.com/hawks/features/hawks-lottery-odds-explained</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="56" t="str">
+      <x:c r="A12" s="51" t="str">
         <x:v>S08</x:v>
       </x:c>
-      <x:c r="B12" s="56" t="str">
+      <x:c r="B12" s="51" t="str">
         <x:v>NBA Communications — 2019 tiebreakers</x:v>
       </x:c>
-      <x:c r="C12" s="56" t="str">
+      <x:c r="C12" s="51" t="str">
         <x:v>Lottery teams, inverse order, tied combinations</x:v>
       </x:c>
-      <x:c r="D12" s="56" t="str">
+      <x:c r="D12" s="51" t="str">
         <x:v>https://pr.nba.com/2019-nba-draft-tiebreakers/</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="56" t="str">
+      <x:c r="A13" s="51" t="str">
         <x:v>S09</x:v>
       </x:c>
-      <x:c r="B13" s="56" t="str">
+      <x:c r="B13" s="51" t="str">
         <x:v>NBA — 2019 lottery result</x:v>
       </x:c>
-      <x:c r="C13" s="56" t="str">
+      <x:c r="C13" s="51" t="str">
         <x:v>Actual draw baseline only</x:v>
       </x:c>
-      <x:c r="D13" s="56" t="str">
+      <x:c r="D13" s="51" t="str">
         <x:v>https://www.nba.com/news/pelicans-win-nba-draft-lottery</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="56" t="str">
+      <x:c r="A14" s="51" t="str">
         <x:v>S10</x:v>
       </x:c>
-      <x:c r="B14" s="56" t="str">
+      <x:c r="B14" s="51" t="str">
         <x:v>Hawks — Oct. 24 Dallas game</x:v>
       </x:c>
-      <x:c r="C14" s="56" t="str">
+      <x:c r="C14" s="51" t="str">
         <x:v>Atlanta 111-104 Dallas official game page</x:v>
       </x:c>
-      <x:c r="D14" s="56" t="str">
+      <x:c r="D14" s="51" t="str">
         <x:v>https://www.nba.com/hawks/game/0021800052-mavericks-vs-hawks-atlanta-ga-10-24-2018</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="56" t="str">
+      <x:c r="A15" s="51" t="str">
         <x:v>S11</x:v>
       </x:c>
-      <x:c r="B15" s="56" t="str">
+      <x:c r="B15" s="51" t="str">
         <x:v>Mavericks — Dec. 12 Atlanta game</x:v>
       </x:c>
-      <x:c r="C15" s="56" t="str">
+      <x:c r="C15" s="51" t="str">
         <x:v>Dallas 114-107 Atlanta official recap</x:v>
       </x:c>
-      <x:c r="D15" s="56" t="str">
+      <x:c r="D15" s="51" t="str">
         <x:v>https://www.nba.com/mavs/mavs-get-a-spark-from-carlisle-and-rallied-for-a-114-107-victory-over-the-hawks</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="56" t="str">
+      <x:c r="A16" s="51" t="str">
         <x:v>S12</x:v>
       </x:c>
-      <x:c r="B16" s="56" t="str">
+      <x:c r="B16" s="51" t="str">
         <x:v>NBA — 2018 Atlanta draft</x:v>
       </x:c>
-      <x:c r="C16" s="56" t="str">
+      <x:c r="C16" s="51" t="str">
         <x:v>Actual 30th pick was Spellman</x:v>
       </x:c>
-      <x:c r="D16" s="56" t="str">
+      <x:c r="D16" s="51" t="str">
         <x:v>https://www.nba.com/hawks/news/hawks-acquire-trae-young-select-kevin-huerter-omari-spellman-2018-nba-draft</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="51" t="str">
+        <x:v>S13</x:v>
+      </x:c>
+      <x:c r="B17" s="51" t="str">
+        <x:v>NBA — 2018 Draft Trade Tracker</x:v>
+      </x:c>
+      <x:c r="C17" s="51" t="str">
+        <x:v>Actual picks, rights trades, and destination teams</x:v>
+      </x:c>
+      <x:c r="D17" s="51" t="str">
+        <x:v>https://www.nba.com/2018-draft-trade-tracker</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="51" t="str">
+        <x:v>S14</x:v>
+      </x:c>
+      <x:c r="B18" s="51" t="str">
+        <x:v>San Antonio Express-News — Spurs workout target</x:v>
+      </x:c>
+      <x:c r="C18" s="51" t="str">
+        <x:v>Spellman worked out for Spurs; second workout interest</x:v>
+      </x:c>
+      <x:c r="D18" s="51" t="str">
+        <x:v>https://www.expressnews.com/spurs-nation/article/Spurs-target-Villanova-s-Spellman-others-for-12994749.php</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="51" t="str">
+        <x:v>S15</x:v>
+      </x:c>
+      <x:c r="B19" s="51" t="str">
+        <x:v>Sports Illustrated — final 2018 mock</x:v>
+      </x:c>
+      <x:c r="C19" s="51" t="str">
+        <x:v>Spellman #44 range; Spurs fit; Metu second-round range</x:v>
+      </x:c>
+      <x:c r="D19" s="51" t="str">
+        <x:v>https://www.si.com/nba/2018/06/21/nba-mock-draft-2018-trade-rumors-final-picks-deandre-ayton-trae-young</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="51" t="str">
+        <x:v>S16</x:v>
+      </x:c>
+      <x:c r="B20" s="51" t="str">
+        <x:v>Wizards — Issuf Sanon plan</x:v>
+      </x:c>
+      <x:c r="C20" s="51" t="str">
+        <x:v>Washington explicitly preferred an overseas stash</x:v>
+      </x:c>
+      <x:c r="D20" s="51" t="str">
+        <x:v>https://www.nba.com/wizards/wizards-plan-second-round-pick-issuf-sanon</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="51" t="str">
+        <x:v>S17</x:v>
+      </x:c>
+      <x:c r="B21" s="51" t="str">
+        <x:v>Nets — Rodions Kurucs scouting history</x:v>
+      </x:c>
+      <x:c r="C21" s="51" t="str">
+        <x:v>Brooklyn's long-running Kurucs evaluation</x:v>
+      </x:c>
+      <x:c r="D21" s="51" t="str">
+        <x:v>https://www.nba.com/nets/news/feature/2018/12/28/brooklyn-nets-rookie-rodions-kurucs-had-a-breakout-month-in-december</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="51" t="str">
+        <x:v>S18</x:v>
+      </x:c>
+      <x:c r="B22" s="51" t="str">
+        <x:v>NBA — 2018 big-board tiers</x:v>
+      </x:c>
+      <x:c r="C22" s="51" t="str">
+        <x:v>Spalding in drafted second-round tier; Welsh in the mix</x:v>
+      </x:c>
+      <x:c r="D22" s="51" t="str">
+        <x:v>https://www.nba.com/da-big-board-bigs-2018-draft</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="51" t="str">
+        <x:v>S19</x:v>
+      </x:c>
+      <x:c r="B23" s="51" t="str">
+        <x:v>Nuggets — Thomas Welsh two-way</x:v>
+      </x:c>
+      <x:c r="C23" s="51" t="str">
+        <x:v>Actual Welsh two-way destination used as role-preservation baseline</x:v>
+      </x:c>
+      <x:c r="D23" s="51" t="str">
+        <x:v>https://www.nba.com/nuggets/news/thomas-welsh-signs-two-way-contract-071918</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="51" t="str">
+        <x:v>S20</x:v>
+      </x:c>
+      <x:c r="B24" s="51" t="str">
+        <x:v>Basketball-Reference — Chimezie Metu</x:v>
+      </x:c>
+      <x:c r="C24" s="51" t="str">
+        <x:v>2018-19 San Antonio: 29 games, 5.0 MPG (145 minutes)</x:v>
+      </x:c>
+      <x:c r="D24" s="51" t="str">
+        <x:v>https://www.basketball-reference.com/players/m/metuch01.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="51" t="str">
+        <x:v>S21</x:v>
+      </x:c>
+      <x:c r="B25" s="51" t="str">
+        <x:v>Pounding the Rock — Metu season review</x:v>
+      </x:c>
+      <x:c r="C25" s="51" t="str">
+        <x:v>Most rookie NBA minutes came in garbage time; Austin was primary development venue</x:v>
+      </x:c>
+      <x:c r="D25" s="51" t="str">
+        <x:v>https://www.poundingtherock.com/2019/5/4/18523491/2018-2019-spurs-player-reviews-chimezie-metu</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9727,7 +11058,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re135e721277e4331"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa46802df9134e72"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/simulation/ATLANTA_2018_19_CAUSALITY_LEDGER.xlsx
+++ b/simulation/ATLANTA_2018_19_CAUSALITY_LEDGER.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R243ec70f0c2544d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Ledger" sheetId="2" r:id="R004ae6c0cc164082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season Minutes" sheetId="3" r:id="R89934bb09586473b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2018 Draft Board" sheetId="4" r:id="R4a11c7dc755f4e8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft Bridge" sheetId="5" r:id="Rdfaeae280acc4ad5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gate Audit" sheetId="6" r:id="Ra5b8f023a20e46c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="7" r:id="R41ecceb893434cf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R366e1f9bc1784d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Ledger" sheetId="2" r:id="Rac03984f160d43c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season Minutes" sheetId="3" r:id="Ra5b04d9f3a924551"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2018 Draft Board" sheetId="4" r:id="R3e5d45d21e1545b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spurs Impact" sheetId="5" r:id="R60f9cfc284d9453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft Bridge" sheetId="6" r:id="Ra11d836a74e4428d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gate Audit" sheetId="7" r:id="Rc70dc5e77334451b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R342fc8719a2a4474"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -25,7 +26,7 @@
     <x:numFmt numFmtId="202" formatCode="0.0"/>
     <x:numFmt numFmtId="203" formatCode="0.0%"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -84,6 +85,12 @@
     </x:font>
     <x:font>
       <x:sz val="9"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF17223B"/>
       <x:name val="Aptos"/>
     </x:font>
     <x:font>
@@ -175,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="60">
+  <x:cellXfs count="67">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -288,12 +295,27 @@
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -399,7 +421,23 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourceTable" displayName="SourceTable" ref="A4:D25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SpursAssignmentTable" displayName="SpursAssignmentTable" ref="A15:H34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="Window"/>
+    <x:tableColumn id="2" name="Assign date"/>
+    <x:tableColumn id="3" name="Recall date"/>
+    <x:tableColumn id="4" name="Calendar days"/>
+    <x:tableColumn id="5" name="Entry"/>
+    <x:tableColumn id="6" name="Exit"/>
+    <x:tableColumn id="7" name="Contract/status"/>
+    <x:tableColumn id="8" name="Source ID"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="SourceTable" displayName="SourceTable" ref="A4:D31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Source"/>
@@ -617,7 +655,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="18" t="str">
-        <x:v>ATLANTA 2018-19 — CAUSALITY LEDGER / DRAFT BOARD v0.2</x:v>
+        <x:v>ATLANTA 2018-19 — CAUSALITY LEDGER / DRAFT BOARD v0.3</x:v>
       </x:c>
       <x:c r="B1" s="19"/>
       <x:c r="C1" s="19"/>
@@ -652,7 +690,7 @@
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B4" s="20" t="str">
-        <x:v>BASELINE_PASS / SECOND_TEAM_IMPACT_HOLD</x:v>
+        <x:v>SECOND_TEAM_BASELINE_PASS / OUTCOME_HOLD</x:v>
       </x:c>
       <x:c r="C4" s="20" t="str">
         <x:v>Canon</x:v>
@@ -952,7 +990,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B18" s="22" t="str">
-        <x:v>Spellman's destination is resolved at San Antonio #49. The 2019 standings/lottery cannot be FINAL until the Spurs' 2018-19 impact is closed.</x:v>
+        <x:v>Spellman's San Antonio #49 baseline role is closed at Metu's low-leverage slot. Any minutes above 145.4 need a dated donor; competitive stints trigger outcome review.</x:v>
       </x:c>
       <x:c r="C18" s="22"/>
       <x:c r="D18" s="22"/>
@@ -8024,7 +8062,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R187056fa3cab45d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70e1b02e502342a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9063,7 +9101,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d4fefc5fb924228"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0edad3bb7357419f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9116,7 +9154,7 @@
         <x:v>Next blocker</x:v>
       </x:c>
       <x:c r="H4" s="6" t="str">
-        <x:v>Spurs 2018-19 impact</x:v>
+        <x:v>Dallas/Denver contracts</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -9848,10 +9886,10 @@
         <x:v>Spellman worked out for San Antonio and fit its spacing/IQ profile.</x:v>
       </x:c>
       <x:c r="J26" s="53" t="str">
-        <x:v>Spurs 2018-19 impact HOLD</x:v>
+        <x:v>Spurs baseline role PASS; outcomes HOLD</x:v>
       </x:c>
       <x:c r="K26" s="53" t="str">
-        <x:v>S14/S15</x:v>
+        <x:v>S14/S15/S22</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -10245,12 +10283,1017 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd845085108c84979"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb23b2dbd43ef4286"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="27" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="27" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>SAN ANTONIO 2018-19 — SECOND-TEAM IMPACT FIREWALL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="56" t="str">
+        <x:v>Actual Spurs</x:v>
+      </x:c>
+      <x:c r="B4" s="56" t="str">
+        <x:v>48-34</x:v>
+      </x:c>
+      <x:c r="C4" s="56" t="str">
+        <x:v>Metu NBA</x:v>
+      </x:c>
+      <x:c r="D4" s="56" t="str">
+        <x:v>29 G / 145.4 MIN</x:v>
+      </x:c>
+      <x:c r="E4" s="56" t="str">
+        <x:v>Metu Austin</x:v>
+      </x:c>
+      <x:c r="F4" s="56" t="str">
+        <x:v>26 G / 710.4 MIN</x:v>
+      </x:c>
+      <x:c r="G4" s="56" t="str">
+        <x:v>CF base</x:v>
+      </x:c>
+      <x:c r="H4" s="56" t="str">
+        <x:v>29 G / 145.4 MIN</x:v>
+      </x:c>
+      <x:c r="I4" s="56" t="str">
+        <x:v>ATL series</x:v>
+      </x:c>
+      <x:c r="J4" s="56" t="str">
+        <x:v>2 G / 0 MIN</x:v>
+      </x:c>
+      <x:c r="K4" s="56" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="L4" s="56" t="str">
+        <x:v>BASELINE_ROLE_PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="57"/>
+      <x:c r="B5" s="57"/>
+      <x:c r="C5" s="57"/>
+      <x:c r="D5" s="57"/>
+      <x:c r="E5" s="57"/>
+      <x:c r="F5" s="57"/>
+      <x:c r="G5" s="57"/>
+      <x:c r="H5" s="57"/>
+      <x:c r="I5" s="57"/>
+      <x:c r="J5" s="57"/>
+      <x:c r="K5" s="57"/>
+      <x:c r="L5" s="57"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="40" t="str">
+        <x:v>Scenario</x:v>
+      </x:c>
+      <x:c r="B6" s="40" t="str">
+        <x:v>NBA GP</x:v>
+      </x:c>
+      <x:c r="C6" s="40" t="str">
+        <x:v>NBA MPG</x:v>
+      </x:c>
+      <x:c r="D6" s="40" t="str">
+        <x:v>NBA MIN</x:v>
+      </x:c>
+      <x:c r="E6" s="40" t="str">
+        <x:v>Starts</x:v>
+      </x:c>
+      <x:c r="F6" s="40" t="str">
+        <x:v>Austin GP</x:v>
+      </x:c>
+      <x:c r="G6" s="40" t="str">
+        <x:v>Result rule</x:v>
+      </x:c>
+      <x:c r="H6" s="40" t="str">
+        <x:v>Required evidence</x:v>
+      </x:c>
+      <x:c r="I6" s="57"/>
+      <x:c r="J6" s="57"/>
+      <x:c r="K6" s="57"/>
+      <x:c r="L6" s="57"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="58" t="str">
+        <x:v>LOW</x:v>
+      </x:c>
+      <x:c r="B7" s="58" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C7" s="58" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D7" s="58" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E7" s="58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="58" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G7" s="58" t="str">
+        <x:v>No automatic game changes</x:v>
+      </x:c>
+      <x:c r="H7" s="58" t="str">
+        <x:v>Stay inside Metu/deep-reserve slot</x:v>
+      </x:c>
+      <x:c r="I7" s="57"/>
+      <x:c r="J7" s="57"/>
+      <x:c r="K7" s="57"/>
+      <x:c r="L7" s="57"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="58" t="str">
+        <x:v>BASE</x:v>
+      </x:c>
+      <x:c r="B8" s="58" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C8" s="58" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D8" s="58" t="n">
+        <x:v>145.4</x:v>
+      </x:c>
+      <x:c r="E8" s="58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="58" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G8" s="58" t="str">
+        <x:v>No automatic game changes</x:v>
+      </x:c>
+      <x:c r="H8" s="58" t="str">
+        <x:v>Metu actual role baseline</x:v>
+      </x:c>
+      <x:c r="I8" s="57"/>
+      <x:c r="J8" s="57"/>
+      <x:c r="K8" s="57"/>
+      <x:c r="L8" s="57"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="58" t="str">
+        <x:v>HIGH</x:v>
+      </x:c>
+      <x:c r="B9" s="58" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C9" s="58" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D9" s="58" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="E9" s="58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="58" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G9" s="58" t="str">
+        <x:v>GAME_REVIEW if competitive</x:v>
+      </x:c>
+      <x:c r="H9" s="58" t="str">
+        <x:v>Dated donor required above 145.4</x:v>
+      </x:c>
+      <x:c r="I9" s="57"/>
+      <x:c r="J9" s="57"/>
+      <x:c r="K9" s="57"/>
+      <x:c r="L9" s="57"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="57"/>
+      <x:c r="B10" s="57"/>
+      <x:c r="C10" s="57"/>
+      <x:c r="D10" s="57"/>
+      <x:c r="E10" s="57"/>
+      <x:c r="F10" s="57"/>
+      <x:c r="G10" s="57"/>
+      <x:c r="H10" s="57"/>
+      <x:c r="I10" s="57"/>
+      <x:c r="J10" s="57"/>
+      <x:c r="K10" s="57"/>
+      <x:c r="L10" s="57"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="40" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="B11" s="40" t="str">
+        <x:v>Site</x:v>
+      </x:c>
+      <x:c r="C11" s="40" t="str">
+        <x:v>Opponent</x:v>
+      </x:c>
+      <x:c r="D11" s="40" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="E11" s="40" t="str">
+        <x:v>SAS Pts</x:v>
+      </x:c>
+      <x:c r="F11" s="40" t="str">
+        <x:v>ATL Pts</x:v>
+      </x:c>
+      <x:c r="G11" s="40" t="str">
+        <x:v>Margin</x:v>
+      </x:c>
+      <x:c r="H11" s="40" t="str">
+        <x:v>Metu roster</x:v>
+      </x:c>
+      <x:c r="I11" s="40" t="str">
+        <x:v>Metu status</x:v>
+      </x:c>
+      <x:c r="J11" s="40" t="str">
+        <x:v>Spurs-side CF contact</x:v>
+      </x:c>
+      <x:c r="K11" s="40" t="str">
+        <x:v>Outcome status</x:v>
+      </x:c>
+      <x:c r="L11" s="40" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="59" t="n">
+        <x:v>43530.5</x:v>
+      </x:c>
+      <x:c r="B12" s="58" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="C12" s="58" t="str">
+        <x:v>Atlanta Hawks</x:v>
+      </x:c>
+      <x:c r="D12" s="58" t="str">
+        <x:v>W</x:v>
+      </x:c>
+      <x:c r="E12" s="58" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F12" s="58" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G12" s="58" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H12" s="58" t="str">
+        <x:v>NBA roster</x:v>
+      </x:c>
+      <x:c r="I12" s="58" t="str">
+        <x:v>DNP-CD / 0</x:v>
+      </x:c>
+      <x:c r="J12" s="58" t="str">
+        <x:v>NO_DIRECT_MINUTES</x:v>
+      </x:c>
+      <x:c r="K12" s="58" t="str">
+        <x:v>ATL-side execution HOLD</x:v>
+      </x:c>
+      <x:c r="L12" s="58" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="59" t="n">
+        <x:v>43557.5</x:v>
+      </x:c>
+      <x:c r="B13" s="58" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="C13" s="58" t="str">
+        <x:v>Atlanta Hawks</x:v>
+      </x:c>
+      <x:c r="D13" s="58" t="str">
+        <x:v>W</x:v>
+      </x:c>
+      <x:c r="E13" s="58" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F13" s="58" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G13" s="58" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H13" s="58" t="str">
+        <x:v>NBA roster</x:v>
+      </x:c>
+      <x:c r="I13" s="58" t="str">
+        <x:v>Inactive/0</x:v>
+      </x:c>
+      <x:c r="J13" s="58" t="str">
+        <x:v>NO_DIRECT_MINUTES</x:v>
+      </x:c>
+      <x:c r="K13" s="58" t="str">
+        <x:v>ATL-side execution HOLD</x:v>
+      </x:c>
+      <x:c r="L13" s="58" t="str">
+        <x:v>S26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="57"/>
+      <x:c r="B14" s="57"/>
+      <x:c r="C14" s="57"/>
+      <x:c r="D14" s="57"/>
+      <x:c r="E14" s="57"/>
+      <x:c r="F14" s="57"/>
+      <x:c r="G14" s="57"/>
+      <x:c r="H14" s="57"/>
+      <x:c r="I14" s="57"/>
+      <x:c r="J14" s="57"/>
+      <x:c r="K14" s="57"/>
+      <x:c r="L14" s="57"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="40" t="str">
+        <x:v>Window</x:v>
+      </x:c>
+      <x:c r="B15" s="40" t="str">
+        <x:v>Assign date</x:v>
+      </x:c>
+      <x:c r="C15" s="40" t="str">
+        <x:v>Recall date</x:v>
+      </x:c>
+      <x:c r="D15" s="40" t="str">
+        <x:v>Calendar days</x:v>
+      </x:c>
+      <x:c r="E15" s="40" t="str">
+        <x:v>Entry</x:v>
+      </x:c>
+      <x:c r="F15" s="40" t="str">
+        <x:v>Exit</x:v>
+      </x:c>
+      <x:c r="G15" s="40" t="str">
+        <x:v>Contract/status</x:v>
+      </x:c>
+      <x:c r="H15" s="40" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="I15" s="57"/>
+      <x:c r="J15" s="40" t="str">
+        <x:v>Audit</x:v>
+      </x:c>
+      <x:c r="K15" s="40" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="L15" s="40" t="str">
+        <x:v>Check</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B16" s="59" t="n">
+        <x:v>43398.5</x:v>
+      </x:c>
+      <x:c r="C16" s="59" t="n">
+        <x:v>43400.5</x:v>
+      </x:c>
+      <x:c r="D16" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E16" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F16" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G16" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H16" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I16" s="57"/>
+      <x:c r="J16" s="58" t="str">
+        <x:v>Assignment windows</x:v>
+      </x:c>
+      <x:c r="K16" s="58" t="n">
+        <x:f>COUNTA(A16:A34)</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L16" s="58" t="str">
+        <x:f>IF(K16=19,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B17" s="59" t="n">
+        <x:v>43409.5</x:v>
+      </x:c>
+      <x:c r="C17" s="59" t="n">
+        <x:v>43409.5</x:v>
+      </x:c>
+      <x:c r="D17" s="58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F17" s="58" t="str">
+        <x:v>Same-day recall</x:v>
+      </x:c>
+      <x:c r="G17" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H17" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I17" s="57"/>
+      <x:c r="J17" s="58" t="str">
+        <x:v>Direct games</x:v>
+      </x:c>
+      <x:c r="K17" s="58" t="n">
+        <x:f>COUNTA(A12:A13)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L17" s="58" t="str">
+        <x:f>IF(K17=2,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B18" s="59" t="n">
+        <x:v>43412.5</x:v>
+      </x:c>
+      <x:c r="C18" s="59" t="n">
+        <x:v>43412.5</x:v>
+      </x:c>
+      <x:c r="D18" s="58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F18" s="58" t="str">
+        <x:v>Same-day recall</x:v>
+      </x:c>
+      <x:c r="G18" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H18" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I18" s="57"/>
+      <x:c r="J18" s="58" t="str">
+        <x:v>Direct Metu minutes</x:v>
+      </x:c>
+      <x:c r="K18" s="58" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="58" t="str">
+        <x:f>IF(K18=0,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="58" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B19" s="59" t="n">
+        <x:v>43424.5</x:v>
+      </x:c>
+      <x:c r="C19" s="59" t="n">
+        <x:v>43425.5</x:v>
+      </x:c>
+      <x:c r="D19" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E19" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F19" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G19" s="58" t="str">
+        <x:v>Second reported assignment</x:v>
+      </x:c>
+      <x:c r="H19" s="58" t="str">
+        <x:v>S22/S24</x:v>
+      </x:c>
+      <x:c r="I19" s="57"/>
+      <x:c r="J19" s="58" t="str">
+        <x:v>Base minutes</x:v>
+      </x:c>
+      <x:c r="K19" s="58" t="n">
+        <x:f>D8</x:f>
+        <x:v>145.4</x:v>
+      </x:c>
+      <x:c r="L19" s="58" t="str">
+        <x:f>IF(ABS(K19-145.4)&lt;0.01,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="58" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B20" s="59" t="n">
+        <x:v>43435.5</x:v>
+      </x:c>
+      <x:c r="C20" s="59" t="n">
+        <x:v>43436.5</x:v>
+      </x:c>
+      <x:c r="D20" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E20" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F20" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G20" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H20" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I20" s="57"/>
+      <x:c r="J20" s="58" t="str">
+        <x:v>High-base excess</x:v>
+      </x:c>
+      <x:c r="K20" s="58" t="n">
+        <x:f>D9-D8</x:f>
+        <x:v>34.599999999999994</x:v>
+      </x:c>
+      <x:c r="L20" s="58" t="str">
+        <x:f>IF(ABS(K20-34.6)&lt;0.01,"DONOR REQUIRED","CHECK")</x:f>
+        <x:v>DONOR REQUIRED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="58" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B21" s="59" t="n">
+        <x:v>43442.5</x:v>
+      </x:c>
+      <x:c r="C21" s="59" t="n">
+        <x:v>43443.5</x:v>
+      </x:c>
+      <x:c r="D21" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F21" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G21" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H21" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I21" s="57"/>
+      <x:c r="J21" s="58" t="str">
+        <x:v>Outcome lock</x:v>
+      </x:c>
+      <x:c r="K21" s="58" t="str">
+        <x:f>IF(K18=0,"SPURS-SIDE DIRECT PASS","REVIEW")</x:f>
+        <x:v>SPURS-SIDE DIRECT PASS</x:v>
+      </x:c>
+      <x:c r="L21" s="58" t="str">
+        <x:f>IF(K21="SPURS-SIDE DIRECT PASS","PASS","HOLD")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="58" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B22" s="59" t="n">
+        <x:v>43448.5</x:v>
+      </x:c>
+      <x:c r="C22" s="59" t="n">
+        <x:v>43457.5</x:v>
+      </x:c>
+      <x:c r="D22" s="58" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E22" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F22" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G22" s="58" t="str">
+        <x:v>Development window</x:v>
+      </x:c>
+      <x:c r="H22" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I22" s="57"/>
+      <x:c r="J22" s="57"/>
+      <x:c r="K22" s="57"/>
+      <x:c r="L22" s="57"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="58" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B23" s="59" t="n">
+        <x:v>43461.5</x:v>
+      </x:c>
+      <x:c r="C23" s="59" t="n">
+        <x:v>43468.5</x:v>
+      </x:c>
+      <x:c r="D23" s="58" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E23" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F23" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G23" s="58" t="str">
+        <x:v>Development window</x:v>
+      </x:c>
+      <x:c r="H23" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I23" s="57"/>
+      <x:c r="J23" s="60" t="str">
+        <x:v>48-34 remains BASELINE, not a locked counterfactual result. Atlanta-side player impact is still HOLD.</x:v>
+      </x:c>
+      <x:c r="K23" s="60"/>
+      <x:c r="L23" s="60"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="58" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B24" s="59" t="n">
+        <x:v>43470.5</x:v>
+      </x:c>
+      <x:c r="C24" s="59" t="n">
+        <x:v>43470.5</x:v>
+      </x:c>
+      <x:c r="D24" s="58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F24" s="58" t="str">
+        <x:v>Same-day recall</x:v>
+      </x:c>
+      <x:c r="G24" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H24" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I24" s="57"/>
+      <x:c r="J24" s="57"/>
+      <x:c r="K24" s="57"/>
+      <x:c r="L24" s="57"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="58" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B25" s="59" t="n">
+        <x:v>43472.5</x:v>
+      </x:c>
+      <x:c r="C25" s="59" t="n">
+        <x:v>43482.5</x:v>
+      </x:c>
+      <x:c r="D25" s="58" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E25" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F25" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G25" s="58" t="str">
+        <x:v>Development window</x:v>
+      </x:c>
+      <x:c r="H25" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I25" s="57"/>
+      <x:c r="J25" s="57"/>
+      <x:c r="K25" s="57"/>
+      <x:c r="L25" s="57"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="58" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B26" s="59" t="n">
+        <x:v>43484.5</x:v>
+      </x:c>
+      <x:c r="C26" s="59" t="n">
+        <x:v>43485.5</x:v>
+      </x:c>
+      <x:c r="D26" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F26" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G26" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H26" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I26" s="57"/>
+      <x:c r="J26" s="57"/>
+      <x:c r="K26" s="57"/>
+      <x:c r="L26" s="57"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="58" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B27" s="59" t="n">
+        <x:v>43490.5</x:v>
+      </x:c>
+      <x:c r="C27" s="59" t="n">
+        <x:v>43491.5</x:v>
+      </x:c>
+      <x:c r="D27" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F27" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G27" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H27" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I27" s="57"/>
+      <x:c r="J27" s="57"/>
+      <x:c r="K27" s="57"/>
+      <x:c r="L27" s="57"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="58" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B28" s="59" t="n">
+        <x:v>43497.5</x:v>
+      </x:c>
+      <x:c r="C28" s="59" t="n">
+        <x:v>43498.5</x:v>
+      </x:c>
+      <x:c r="D28" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E28" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F28" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G28" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H28" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I28" s="57"/>
+      <x:c r="J28" s="57"/>
+      <x:c r="K28" s="57"/>
+      <x:c r="L28" s="57"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="58" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B29" s="59" t="n">
+        <x:v>43506.5</x:v>
+      </x:c>
+      <x:c r="C29" s="59" t="n">
+        <x:v>43507.5</x:v>
+      </x:c>
+      <x:c r="D29" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E29" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F29" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G29" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H29" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I29" s="57"/>
+      <x:c r="J29" s="57"/>
+      <x:c r="K29" s="57"/>
+      <x:c r="L29" s="57"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="58" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B30" s="59" t="n">
+        <x:v>43524.5</x:v>
+      </x:c>
+      <x:c r="C30" s="59" t="n">
+        <x:v>43525.5</x:v>
+      </x:c>
+      <x:c r="D30" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E30" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F30" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G30" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H30" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I30" s="57"/>
+      <x:c r="J30" s="57"/>
+      <x:c r="K30" s="57"/>
+      <x:c r="L30" s="57"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="58" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B31" s="59" t="n">
+        <x:v>43531.5</x:v>
+      </x:c>
+      <x:c r="C31" s="59" t="n">
+        <x:v>43534.5</x:v>
+      </x:c>
+      <x:c r="D31" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E31" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F31" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G31" s="58" t="str">
+        <x:v>After Atlanta game</x:v>
+      </x:c>
+      <x:c r="H31" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I31" s="57"/>
+      <x:c r="J31" s="57"/>
+      <x:c r="K31" s="57"/>
+      <x:c r="L31" s="57"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="58" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B32" s="59" t="n">
+        <x:v>43537.5</x:v>
+      </x:c>
+      <x:c r="C32" s="59" t="n">
+        <x:v>43539.5</x:v>
+      </x:c>
+      <x:c r="D32" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E32" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F32" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G32" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H32" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I32" s="57"/>
+      <x:c r="J32" s="57"/>
+      <x:c r="K32" s="57"/>
+      <x:c r="L32" s="57"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="58" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B33" s="59" t="n">
+        <x:v>43543.5</x:v>
+      </x:c>
+      <x:c r="C33" s="59" t="n">
+        <x:v>43544.5</x:v>
+      </x:c>
+      <x:c r="D33" s="58" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E33" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F33" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G33" s="58" t="str">
+        <x:v>NBA contract retained</x:v>
+      </x:c>
+      <x:c r="H33" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I33" s="57"/>
+      <x:c r="J33" s="57"/>
+      <x:c r="K33" s="57"/>
+      <x:c r="L33" s="57"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="58" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B34" s="59" t="n">
+        <x:v>43545.5</x:v>
+      </x:c>
+      <x:c r="C34" s="59" t="n">
+        <x:v>43548.5</x:v>
+      </x:c>
+      <x:c r="D34" s="58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E34" s="58" t="str">
+        <x:v>Austin assignment</x:v>
+      </x:c>
+      <x:c r="F34" s="58" t="str">
+        <x:v>Recall</x:v>
+      </x:c>
+      <x:c r="G34" s="58" t="str">
+        <x:v>Final logged window</x:v>
+      </x:c>
+      <x:c r="H34" s="58" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="I34" s="57"/>
+      <x:c r="J34" s="57"/>
+      <x:c r="K34" s="57"/>
+      <x:c r="L34" s="57"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:L2"/>
+    <x:mergeCell ref="J23:L23"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R678b9e0485934009"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -10316,10 +11359,10 @@
       <x:c r="D5" s="13" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E5" s="54" t="n">
+      <x:c r="E5" s="61" t="n">
         <x:v>0.105</x:v>
       </x:c>
-      <x:c r="F5" s="54" t="n">
+      <x:c r="F5" s="61" t="n">
         <x:v>0.4212</x:v>
       </x:c>
       <x:c r="G5" s="13" t="n">
@@ -10348,10 +11391,10 @@
       <x:c r="D6" s="13" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E6" s="54" t="n">
+      <x:c r="E6" s="61" t="n">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="F6" s="54" t="n">
+      <x:c r="F6" s="61" t="n">
         <x:v>0.263</x:v>
       </x:c>
       <x:c r="G6" s="13" t="n">
@@ -10447,8 +11490,8 @@
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="57" t="str">
-        <x:v>FINAL BLOCKER: Spellman is resolved to San Antonio #49; close the Spurs' 2018-19 rotation and game impact before standings/lottery.</x:v>
+      <x:c r="A14" s="64" t="str">
+        <x:v>FINAL BLOCKER: Spurs baseline role is closed. Execute Atlanta player-game impacts and review any Spellman competitive stints before standings/lottery.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10462,7 +11505,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -10504,19 +11547,19 @@
         <x:v>G0</x:v>
       </x:c>
       <x:c r="B5" s="51" t="str">
-        <x:v>Spellman destination + second-team impact</x:v>
+        <x:v>Spellman destination + second-team baseline</x:v>
       </x:c>
       <x:c r="C5" s="51" t="str">
-        <x:v>Spellman → Spurs #49; Spurs impact not executed</x:v>
+        <x:v>Spurs #49; base 29 G/145.4 min; ATL series 0 min</x:v>
       </x:c>
       <x:c r="D5" s="53" t="str">
-        <x:v>PARTIAL</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="E5" s="51" t="str">
-        <x:v>FINAL standings/lottery</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="F5" s="51" t="str">
-        <x:v>Model Spurs 2018-19</x:v>
+        <x:v>Preserve role cap and donor trigger</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -10700,25 +11743,25 @@
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="59"/>
-      <x:c r="B15" s="59"/>
-      <x:c r="C15" s="59"/>
-      <x:c r="D15" s="59"/>
-      <x:c r="E15" s="59"/>
-      <x:c r="F15" s="59"/>
+      <x:c r="A15" s="66"/>
+      <x:c r="B15" s="66"/>
+      <x:c r="C15" s="66"/>
+      <x:c r="D15" s="66"/>
+      <x:c r="E15" s="66"/>
+      <x:c r="F15" s="66"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="50" t="str">
         <x:v>OVERALL</x:v>
       </x:c>
       <x:c r="B16" s="50" t="str">
-        <x:v>BASELINE_PASS / SECOND_TEAM_IMPACT_HOLD</x:v>
+        <x:v>SECOND_TEAM_BASELINE_PASS / OUTCOME_HOLD</x:v>
       </x:c>
       <x:c r="C16" s="50"/>
       <x:c r="D16" s="50"/>
       <x:c r="E16" s="50"/>
       <x:c r="F16" s="50" t="str">
-        <x:v>Draft path closed; Spurs season bridge remains</x:v>
+        <x:v>Atlanta player-game and competitive-stint outcomes remain</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10729,7 +11772,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -11052,13 +12095,97 @@
         <x:v>https://www.poundingtherock.com/2019/5/4/18523491/2018-2019-spurs-player-reviews-chimezie-metu</x:v>
       </x:c>
     </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="51" t="str">
+        <x:v>S22</x:v>
+      </x:c>
+      <x:c r="B26" s="51" t="str">
+        <x:v>RealGM — Chimezie Metu profile</x:v>
+      </x:c>
+      <x:c r="C26" s="51" t="str">
+        <x:v>2018-19 NBA totals, Austin totals, and assignment/recall transaction log</x:v>
+      </x:c>
+      <x:c r="D26" s="51" t="str">
+        <x:v>https://basketball.realgm.com/player/Chimezie-Metu/Summary/76976</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="51" t="str">
+        <x:v>S23</x:v>
+      </x:c>
+      <x:c r="B27" s="51" t="str">
+        <x:v>Spurs — Metu signing</x:v>
+      </x:c>
+      <x:c r="C27" s="51" t="str">
+        <x:v>Second-round pick signed to an NBA multi-year contract, not a two-way</x:v>
+      </x:c>
+      <x:c r="D27" s="51" t="str">
+        <x:v>https://www.nba.com/spurs/news/spurs-sign-2018-second-round-pick-chimezie-metu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="51" t="str">
+        <x:v>S24</x:v>
+      </x:c>
+      <x:c r="B28" s="51" t="str">
+        <x:v>Fox San Antonio — Nov. 20 assignment</x:v>
+      </x:c>
+      <x:c r="C28" s="51" t="str">
+        <x:v>Contemporary report identifies Metu's second Austin assignment and NBA baseline</x:v>
+      </x:c>
+      <x:c r="D28" s="51" t="str">
+        <x:v>https://foxsanantonio.com/sports/max-sports/spurs-assign-rookie-metu-to-g-league</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="51" t="str">
+        <x:v>S25</x:v>
+      </x:c>
+      <x:c r="B29" s="51" t="str">
+        <x:v>ESPN — 2019-03-06 Spurs at Atlanta</x:v>
+      </x:c>
+      <x:c r="C29" s="51" t="str">
+        <x:v>Spurs 111-104; Metu DNP-Coach's Decision</x:v>
+      </x:c>
+      <x:c r="D29" s="51" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071641</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="51" t="str">
+        <x:v>S26</x:v>
+      </x:c>
+      <x:c r="B30" s="51" t="str">
+        <x:v>NBA Hawks — 2019-04-02 Atlanta at Spurs</x:v>
+      </x:c>
+      <x:c r="C30" s="51" t="str">
+        <x:v>Spurs 117-111; Metu recorded no minutes</x:v>
+      </x:c>
+      <x:c r="D30" s="51" t="str">
+        <x:v>https://www.nba.com/hawks/game/0021801162-hawks-vs-spurs-san-antonio-tx-04-02-2019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="51" t="str">
+        <x:v>S27</x:v>
+      </x:c>
+      <x:c r="B31" s="51" t="str">
+        <x:v>Spurs — 2019 Metu Austin recap</x:v>
+      </x:c>
+      <x:c r="C31" s="51" t="str">
+        <x:v>2018-19 Austin: 26 games, 14.0/7.4/2.3 in 27.3 MPG</x:v>
+      </x:c>
+      <x:c r="D31" s="51" t="str">
+        <x:v>https://www.nba.com/spurs/news/san-antonio-assigns-chimezie-metu-austin-spurs-8</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa46802df9134e72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31c25f5cf78044f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/simulation/ATLANTA_2018_19_CAUSALITY_LEDGER.xlsx
+++ b/simulation/ATLANTA_2018_19_CAUSALITY_LEDGER.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R366e1f9bc1784d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Ledger" sheetId="2" r:id="Rac03984f160d43c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season Minutes" sheetId="3" r:id="Ra5b04d9f3a924551"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2018 Draft Board" sheetId="4" r:id="R3e5d45d21e1545b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spurs Impact" sheetId="5" r:id="R60f9cfc284d9453b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft Bridge" sheetId="6" r:id="Ra11d836a74e4428d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gate Audit" sheetId="7" r:id="Rc70dc5e77334451b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R342fc8719a2a4474"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R68f787c966524bf9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Ledger" sheetId="2" r:id="R0da9e4168273453e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season Minutes" sheetId="3" r:id="R9235d60d1db24783"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2018 Draft Board" sheetId="4" r:id="R66f8d0ab790c4c78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spurs Impact" sheetId="5" r:id="R30ddbd1fb9b245ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cascade Impact" sheetId="6" r:id="Rc3254edf00a34c83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft Bridge" sheetId="7" r:id="R880401c26dbd44e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gate Audit" sheetId="8" r:id="Rc96c56130c3c4d65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R5bb35b2c8e9a47f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -182,7 +183,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="67">
+  <x:cellXfs count="68">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -309,6 +310,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -437,7 +441,48 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="SourceTable" displayName="SourceTable" ref="A4:D31" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="CascadeContractTable" displayName="CascadeContractTable" ref="A6:M12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="13">
+    <x:tableColumn id="1" name="Team"/>
+    <x:tableColumn id="2" name="World"/>
+    <x:tableColumn id="3" name="Player"/>
+    <x:tableColumn id="4" name="Pick"/>
+    <x:tableColumn id="5" name="Contract layer"/>
+    <x:tableColumn id="6" name="Development path"/>
+    <x:tableColumn id="7" name="NBA GP"/>
+    <x:tableColumn id="8" name="NBA MIN"/>
+    <x:tableColumn id="9" name="G League GP"/>
+    <x:tableColumn id="10" name="Transaction"/>
+    <x:tableColumn id="11" name="Role status"/>
+    <x:tableColumn id="12" name="Escalation trigger"/>
+    <x:tableColumn id="13" name="Source ID"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CascadeDirectGameTable" displayName="CascadeDirectGameTable" ref="A15:L19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
+    <x:tableColumn id="1" name="Team"/>
+    <x:tableColumn id="2" name="Date"/>
+    <x:tableColumn id="3" name="Site"/>
+    <x:tableColumn id="4" name="Actual"/>
+    <x:tableColumn id="5" name="Team pts"/>
+    <x:tableColumn id="6" name="ATL pts"/>
+    <x:tableColumn id="7" name="Margin"/>
+    <x:tableColumn id="8" name="Replaced player"/>
+    <x:tableColumn id="9" name="Replaced MIN"/>
+    <x:tableColumn id="10" name="CF contact"/>
+    <x:tableColumn id="11" name="Outcome status"/>
+    <x:tableColumn id="12" name="Source ID"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="SourceTable" displayName="SourceTable" ref="A4:D43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Source"/>
@@ -655,7 +700,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="18" t="str">
-        <x:v>ATLANTA 2018-19 — CAUSALITY LEDGER / DRAFT BOARD v0.3</x:v>
+        <x:v>ATLANTA 2018-19 — CAUSALITY LEDGER / DRAFT BOARD v0.4</x:v>
       </x:c>
       <x:c r="B1" s="19"/>
       <x:c r="C1" s="19"/>
@@ -690,13 +735,13 @@
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B4" s="20" t="str">
-        <x:v>SECOND_TEAM_BASELINE_PASS / OUTCOME_HOLD</x:v>
+        <x:v>CASCADE_CONTRACT_PASS / OUTCOME_HOLD</x:v>
       </x:c>
       <x:c r="C4" s="20" t="str">
         <x:v>Canon</x:v>
       </x:c>
       <x:c r="D4" s="20" t="str">
-        <x:v>PROVISIONAL</x:v>
+        <x:v>v0.22 PARTIAL</x:v>
       </x:c>
       <x:c r="E4" s="20" t="str">
         <x:v>Manuscript</x:v>
@@ -990,7 +1035,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B18" s="22" t="str">
-        <x:v>Spellman's San Antonio #49 baseline role is closed at Metu's low-leverage slot. Any minutes above 145.4 need a dated donor; competitive stints trigger outcome review.</x:v>
+        <x:v>The San Antonio, Dallas, and Denver replacement contract layers are closed. Each CF rookie starts inside the displaced player's team-specific role, not his old-team minutes.</x:v>
       </x:c>
       <x:c r="C18" s="22"/>
       <x:c r="D18" s="22"/>
@@ -1004,7 +1049,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B19" s="22" t="str">
-        <x:v>No counterfactual scores or results have been generated. Manual flips and close-game cherry-picking are prohibited.</x:v>
+        <x:v>Welsh cannot duplicate Denver's occupied two-way slot. His undrafted free-agent destination remains HOLD; no counterfactual scores or results have been generated.</x:v>
       </x:c>
       <x:c r="C19" s="22"/>
       <x:c r="D19" s="22"/>
@@ -8062,7 +8107,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70e1b02e502342a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a1e5b9d80d449ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9101,7 +9146,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0edad3bb7357419f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d537aa0b8ad4ad9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9154,7 +9199,7 @@
         <x:v>Next blocker</x:v>
       </x:c>
       <x:c r="H4" s="6" t="str">
-        <x:v>Dallas/Denver contracts</x:v>
+        <x:v>Atlanta donor vector</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -10131,10 +10176,10 @@
         <x:v>Metu is the displaced #49 athletic big and remains above this slot.</x:v>
       </x:c>
       <x:c r="J33" s="53" t="str">
-        <x:v>Dallas role/minutes HOLD</x:v>
+        <x:v>Dallas contract layer PASS; outcomes HOLD</x:v>
       </x:c>
       <x:c r="K33" s="53" t="str">
-        <x:v>S13/S15</x:v>
+        <x:v>S13/S15/S28/S29/S30</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -10201,10 +10246,10 @@
         <x:v>Spalding was graded in the drafted second-round big tier.</x:v>
       </x:c>
       <x:c r="J35" s="53" t="str">
-        <x:v>Denver role/two-way HOLD</x:v>
+        <x:v>Denver contract layer PASS; Welsh market HOLD</x:v>
       </x:c>
       <x:c r="K35" s="53" t="str">
-        <x:v>S18</x:v>
+        <x:v>S18/S31/S32/S33/S34</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -10283,7 +10328,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb23b2dbd43ef4286"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6d353ac21e5413d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11288,12 +11333,777 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R678b9e0485934009"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e5c86b37a184f22"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="23" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="25" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="46" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>DALLAS / DENVER 2018-19 — CASCADE CONTRACT FIREWALL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="56" t="str">
+        <x:v>Dallas base</x:v>
+      </x:c>
+      <x:c r="B4" s="56" t="str">
+        <x:v>1 G / 1 MIN</x:v>
+      </x:c>
+      <x:c r="C4" s="56"/>
+      <x:c r="D4" s="56" t="str">
+        <x:v>Texas</x:v>
+      </x:c>
+      <x:c r="E4" s="56" t="str">
+        <x:v>29 G / 30.1 MPG</x:v>
+      </x:c>
+      <x:c r="F4" s="56"/>
+      <x:c r="G4" s="56" t="str">
+        <x:v>Denver base</x:v>
+      </x:c>
+      <x:c r="H4" s="56" t="str">
+        <x:v>11 G / 36 MIN</x:v>
+      </x:c>
+      <x:c r="I4" s="56"/>
+      <x:c r="J4" s="56" t="str">
+        <x:v>ATL series</x:v>
+      </x:c>
+      <x:c r="K4" s="56" t="str">
+        <x:v>4 G / 0 MIN</x:v>
+      </x:c>
+      <x:c r="L4" s="56" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="M4" s="56" t="str">
+        <x:v>CONTRACT_LAYER_PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="57"/>
+      <x:c r="B5" s="57"/>
+      <x:c r="C5" s="57"/>
+      <x:c r="D5" s="57"/>
+      <x:c r="E5" s="57"/>
+      <x:c r="F5" s="57"/>
+      <x:c r="G5" s="57"/>
+      <x:c r="H5" s="57"/>
+      <x:c r="I5" s="57"/>
+      <x:c r="J5" s="57"/>
+      <x:c r="K5" s="57"/>
+      <x:c r="L5" s="57"/>
+      <x:c r="M5" s="57"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="40" t="str">
+        <x:v>Team</x:v>
+      </x:c>
+      <x:c r="B6" s="40" t="str">
+        <x:v>World</x:v>
+      </x:c>
+      <x:c r="C6" s="40" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="D6" s="40" t="str">
+        <x:v>Pick</x:v>
+      </x:c>
+      <x:c r="E6" s="40" t="str">
+        <x:v>Contract layer</x:v>
+      </x:c>
+      <x:c r="F6" s="40" t="str">
+        <x:v>Development path</x:v>
+      </x:c>
+      <x:c r="G6" s="40" t="str">
+        <x:v>NBA GP</x:v>
+      </x:c>
+      <x:c r="H6" s="40" t="str">
+        <x:v>NBA MIN</x:v>
+      </x:c>
+      <x:c r="I6" s="40" t="str">
+        <x:v>G League GP</x:v>
+      </x:c>
+      <x:c r="J6" s="40" t="str">
+        <x:v>Transaction</x:v>
+      </x:c>
+      <x:c r="K6" s="40" t="str">
+        <x:v>Role status</x:v>
+      </x:c>
+      <x:c r="L6" s="40" t="str">
+        <x:v>Escalation trigger</x:v>
+      </x:c>
+      <x:c r="M6" s="40" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="61" t="str">
+        <x:v>Dallas</x:v>
+      </x:c>
+      <x:c r="B7" s="61" t="str">
+        <x:v>ACTUAL</x:v>
+      </x:c>
+      <x:c r="C7" s="61" t="str">
+        <x:v>Ray Spalding</x:v>
+      </x:c>
+      <x:c r="D7" s="61" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E7" s="61" t="str">
+        <x:v>Standard NBA</x:v>
+      </x:c>
+      <x:c r="F7" s="61" t="str">
+        <x:v>Texas assignment</x:v>
+      </x:c>
+      <x:c r="G7" s="61" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="61" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I7" s="61" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J7" s="61" t="str">
+        <x:v>Waived 2019-01-31</x:v>
+      </x:c>
+      <x:c r="K7" s="61" t="str">
+        <x:v>ACTUAL_REPLACED</x:v>
+      </x:c>
+      <x:c r="L7" s="61" t="str">
+        <x:v>Reference only</x:v>
+      </x:c>
+      <x:c r="M7" s="61" t="str">
+        <x:v>S28/S29/S30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="61" t="str">
+        <x:v>Dallas</x:v>
+      </x:c>
+      <x:c r="B8" s="61" t="str">
+        <x:v>CF</x:v>
+      </x:c>
+      <x:c r="C8" s="61" t="str">
+        <x:v>Chimezie Metu</x:v>
+      </x:c>
+      <x:c r="D8" s="61" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E8" s="61" t="str">
+        <x:v>Standard NBA layer</x:v>
+      </x:c>
+      <x:c r="F8" s="61" t="str">
+        <x:v>Texas assignment baseline</x:v>
+      </x:c>
+      <x:c r="G8" s="61" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="61" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I8" s="61" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J8" s="61" t="str">
+        <x:v>Jan. 31 waiver choice HOLD</x:v>
+      </x:c>
+      <x:c r="K8" s="61" t="str">
+        <x:v>CF_CHANGED_STANDARD</x:v>
+      </x:c>
+      <x:c r="L8" s="61" t="str">
+        <x:v>&gt;1 NBA MIN or a different waiver opens Dallas player-game review</x:v>
+      </x:c>
+      <x:c r="M8" s="61" t="str">
+        <x:v>S28/S29/S30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="61" t="str">
+        <x:v>Denver</x:v>
+      </x:c>
+      <x:c r="B9" s="61" t="str">
+        <x:v>ACTUAL</x:v>
+      </x:c>
+      <x:c r="C9" s="61" t="str">
+        <x:v>Thomas Welsh</x:v>
+      </x:c>
+      <x:c r="D9" s="61" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E9" s="61" t="str">
+        <x:v>Two-way</x:v>
+      </x:c>
+      <x:c r="F9" s="61" t="str">
+        <x:v>Capital City / Iowa</x:v>
+      </x:c>
+      <x:c r="G9" s="61" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H9" s="61" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I9" s="61" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J9" s="61" t="str">
+        <x:v>Two-way ended 2019-07-30</x:v>
+      </x:c>
+      <x:c r="K9" s="61" t="str">
+        <x:v>ACTUAL_REPLACED</x:v>
+      </x:c>
+      <x:c r="L9" s="61" t="str">
+        <x:v>Reference only</x:v>
+      </x:c>
+      <x:c r="M9" s="61" t="str">
+        <x:v>S31/S34/S35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="61" t="str">
+        <x:v>Denver</x:v>
+      </x:c>
+      <x:c r="B10" s="61" t="str">
+        <x:v>CF</x:v>
+      </x:c>
+      <x:c r="C10" s="61" t="str">
+        <x:v>Ray Spalding</x:v>
+      </x:c>
+      <x:c r="D10" s="61" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E10" s="61" t="str">
+        <x:v>Two-way (Welsh slot)</x:v>
+      </x:c>
+      <x:c r="F10" s="61" t="str">
+        <x:v>External G League assignment class</x:v>
+      </x:c>
+      <x:c r="G10" s="61" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H10" s="61" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I10" s="61" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J10" s="61" t="str">
+        <x:v>Season role baseline</x:v>
+      </x:c>
+      <x:c r="K10" s="61" t="str">
+        <x:v>CF_CHANGED_TWO_WAY</x:v>
+      </x:c>
+      <x:c r="L10" s="61" t="str">
+        <x:v>&gt;36 NBA MIN or different dates opens Denver player-game review</x:v>
+      </x:c>
+      <x:c r="M10" s="61" t="str">
+        <x:v>S31/S32/S33/S34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="61" t="str">
+        <x:v>Denver</x:v>
+      </x:c>
+      <x:c r="B11" s="61" t="str">
+        <x:v>CF</x:v>
+      </x:c>
+      <x:c r="C11" s="61" t="str">
+        <x:v>DeVaughn Akoon-Purcell</x:v>
+      </x:c>
+      <x:c r="D11" s="61"/>
+      <x:c r="E11" s="61" t="str">
+        <x:v>Two-way</x:v>
+      </x:c>
+      <x:c r="F11" s="61" t="str">
+        <x:v>G League development</x:v>
+      </x:c>
+      <x:c r="G11" s="61"/>
+      <x:c r="H11" s="61"/>
+      <x:c r="I11" s="61"/>
+      <x:c r="J11" s="61" t="str">
+        <x:v>Actual second slot preserved</x:v>
+      </x:c>
+      <x:c r="K11" s="61" t="str">
+        <x:v>CF_PROTECTED_TWO_WAY</x:v>
+      </x:c>
+      <x:c r="L11" s="61" t="str">
+        <x:v>Do not displace without a new transaction cause</x:v>
+      </x:c>
+      <x:c r="M11" s="61" t="str">
+        <x:v>S32/S33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="61" t="str">
+        <x:v>Denver</x:v>
+      </x:c>
+      <x:c r="B12" s="61" t="str">
+        <x:v>CF</x:v>
+      </x:c>
+      <x:c r="C12" s="61" t="str">
+        <x:v>Thomas Welsh</x:v>
+      </x:c>
+      <x:c r="D12" s="61"/>
+      <x:c r="E12" s="61" t="str">
+        <x:v>No Denver slot</x:v>
+      </x:c>
+      <x:c r="F12" s="61" t="str">
+        <x:v>Undrafted free-agent market</x:v>
+      </x:c>
+      <x:c r="G12" s="61" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="61" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="61" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="61" t="str">
+        <x:v>Destination unresolved</x:v>
+      </x:c>
+      <x:c r="K12" s="61" t="str">
+        <x:v>CF_OUT_NO_SLOT</x:v>
+      </x:c>
+      <x:c r="L12" s="61" t="str">
+        <x:v>Any NBA signing creates a new team-impact branch</x:v>
+      </x:c>
+      <x:c r="M12" s="61" t="str">
+        <x:v>S31/S32/S33/S35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="57"/>
+      <x:c r="B13" s="57"/>
+      <x:c r="C13" s="57"/>
+      <x:c r="D13" s="57"/>
+      <x:c r="E13" s="57"/>
+      <x:c r="F13" s="57"/>
+      <x:c r="G13" s="57"/>
+      <x:c r="H13" s="57"/>
+      <x:c r="I13" s="57"/>
+      <x:c r="J13" s="57"/>
+      <x:c r="K13" s="57"/>
+      <x:c r="L13" s="57"/>
+      <x:c r="M13" s="57"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="57"/>
+      <x:c r="B14" s="57"/>
+      <x:c r="C14" s="57"/>
+      <x:c r="D14" s="57"/>
+      <x:c r="E14" s="57"/>
+      <x:c r="F14" s="57"/>
+      <x:c r="G14" s="57"/>
+      <x:c r="H14" s="57"/>
+      <x:c r="I14" s="57"/>
+      <x:c r="J14" s="57"/>
+      <x:c r="K14" s="57"/>
+      <x:c r="L14" s="57"/>
+      <x:c r="M14" s="57"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="40" t="str">
+        <x:v>Team</x:v>
+      </x:c>
+      <x:c r="B15" s="40" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="C15" s="40" t="str">
+        <x:v>Site</x:v>
+      </x:c>
+      <x:c r="D15" s="40" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="E15" s="40" t="str">
+        <x:v>Team pts</x:v>
+      </x:c>
+      <x:c r="F15" s="40" t="str">
+        <x:v>ATL pts</x:v>
+      </x:c>
+      <x:c r="G15" s="40" t="str">
+        <x:v>Margin</x:v>
+      </x:c>
+      <x:c r="H15" s="40" t="str">
+        <x:v>Replaced player</x:v>
+      </x:c>
+      <x:c r="I15" s="40" t="str">
+        <x:v>Replaced MIN</x:v>
+      </x:c>
+      <x:c r="J15" s="40" t="str">
+        <x:v>CF contact</x:v>
+      </x:c>
+      <x:c r="K15" s="40" t="str">
+        <x:v>Outcome status</x:v>
+      </x:c>
+      <x:c r="L15" s="40" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="M15" s="57"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="58" t="str">
+        <x:v>Dallas</x:v>
+      </x:c>
+      <x:c r="B16" s="59" t="n">
+        <x:v>43397.5</x:v>
+      </x:c>
+      <x:c r="C16" s="58" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="D16" s="58" t="str">
+        <x:v>L</x:v>
+      </x:c>
+      <x:c r="E16" s="58" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F16" s="58" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="G16" s="58" t="n">
+        <x:v>-7</x:v>
+      </x:c>
+      <x:c r="H16" s="58" t="str">
+        <x:v>Ray Spalding</x:v>
+      </x:c>
+      <x:c r="I16" s="58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="58" t="str">
+        <x:v>NO_DIRECT_MINUTES</x:v>
+      </x:c>
+      <x:c r="K16" s="58" t="str">
+        <x:v>ATL-side execution HOLD</x:v>
+      </x:c>
+      <x:c r="L16" s="58" t="str">
+        <x:v>S10/S29</x:v>
+      </x:c>
+      <x:c r="M16" s="57"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="58" t="str">
+        <x:v>Dallas</x:v>
+      </x:c>
+      <x:c r="B17" s="59" t="n">
+        <x:v>43446.5</x:v>
+      </x:c>
+      <x:c r="C17" s="58" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="D17" s="58" t="str">
+        <x:v>W</x:v>
+      </x:c>
+      <x:c r="E17" s="58" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F17" s="58" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G17" s="58" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H17" s="58" t="str">
+        <x:v>Ray Spalding</x:v>
+      </x:c>
+      <x:c r="I17" s="58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="58" t="str">
+        <x:v>NO_DIRECT_MINUTES</x:v>
+      </x:c>
+      <x:c r="K17" s="58" t="str">
+        <x:v>ATL-side execution HOLD</x:v>
+      </x:c>
+      <x:c r="L17" s="58" t="str">
+        <x:v>S11/S29</x:v>
+      </x:c>
+      <x:c r="M17" s="57"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="58" t="str">
+        <x:v>Denver</x:v>
+      </x:c>
+      <x:c r="B18" s="59" t="n">
+        <x:v>43419.5</x:v>
+      </x:c>
+      <x:c r="C18" s="58" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="D18" s="58" t="str">
+        <x:v>W</x:v>
+      </x:c>
+      <x:c r="E18" s="58" t="n">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F18" s="58" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="G18" s="58" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H18" s="58" t="str">
+        <x:v>Thomas Welsh</x:v>
+      </x:c>
+      <x:c r="I18" s="58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="58" t="str">
+        <x:v>NO_DIRECT_MINUTES</x:v>
+      </x:c>
+      <x:c r="K18" s="58" t="str">
+        <x:v>ATL-side execution HOLD</x:v>
+      </x:c>
+      <x:c r="L18" s="58" t="str">
+        <x:v>S36/S37</x:v>
+      </x:c>
+      <x:c r="M18" s="57"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="58" t="str">
+        <x:v>Denver</x:v>
+      </x:c>
+      <x:c r="B19" s="59" t="n">
+        <x:v>43442.5</x:v>
+      </x:c>
+      <x:c r="C19" s="58" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="D19" s="58" t="str">
+        <x:v>L</x:v>
+      </x:c>
+      <x:c r="E19" s="58" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F19" s="58" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G19" s="58" t="n">
+        <x:v>-8</x:v>
+      </x:c>
+      <x:c r="H19" s="58" t="str">
+        <x:v>Thomas Welsh</x:v>
+      </x:c>
+      <x:c r="I19" s="58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="58" t="str">
+        <x:v>NO_DIRECT_MINUTES</x:v>
+      </x:c>
+      <x:c r="K19" s="58" t="str">
+        <x:v>ATL-side execution HOLD</x:v>
+      </x:c>
+      <x:c r="L19" s="58" t="str">
+        <x:v>S38/S39</x:v>
+      </x:c>
+      <x:c r="M19" s="57"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="57"/>
+      <x:c r="B20" s="57"/>
+      <x:c r="C20" s="57"/>
+      <x:c r="D20" s="57"/>
+      <x:c r="E20" s="57"/>
+      <x:c r="F20" s="57"/>
+      <x:c r="G20" s="57"/>
+      <x:c r="H20" s="57"/>
+      <x:c r="I20" s="57"/>
+      <x:c r="J20" s="57"/>
+      <x:c r="K20" s="57"/>
+      <x:c r="L20" s="57"/>
+      <x:c r="M20" s="57"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="60" t="str">
+        <x:v>Dallas: Metu begins inside Spalding's standard-contract / Texas assignment slot; a different Jan. 31 waiver choice remains HOLD. Denver: Spalding takes Welsh's two-way slot, Akoon-Purcell keeps the other, and Welsh moves to the undrafted free-agent market. Any minutes above the displaced-player base reopen player-game review.</x:v>
+      </x:c>
+      <x:c r="B21" s="60"/>
+      <x:c r="C21" s="60"/>
+      <x:c r="D21" s="60"/>
+      <x:c r="E21" s="60"/>
+      <x:c r="F21" s="60"/>
+      <x:c r="G21" s="60"/>
+      <x:c r="H21" s="60"/>
+      <x:c r="I21" s="57"/>
+      <x:c r="J21" s="40" t="str">
+        <x:v>Audit</x:v>
+      </x:c>
+      <x:c r="K21" s="40" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="L21" s="40" t="str">
+        <x:v>Check</x:v>
+      </x:c>
+      <x:c r="M21" s="57"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="60"/>
+      <x:c r="B22" s="60"/>
+      <x:c r="C22" s="60"/>
+      <x:c r="D22" s="60"/>
+      <x:c r="E22" s="60"/>
+      <x:c r="F22" s="60"/>
+      <x:c r="G22" s="60"/>
+      <x:c r="H22" s="60"/>
+      <x:c r="I22" s="57"/>
+      <x:c r="J22" s="58" t="str">
+        <x:v>Changed contract chains</x:v>
+      </x:c>
+      <x:c r="K22" s="58" t="n">
+        <x:f>COUNTIF(K7:K12,"CF_CHANGED_STANDARD")+COUNTIF(K7:K12,"CF_CHANGED_TWO_WAY")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L22" s="58" t="str">
+        <x:f>IF(K22=2,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="M22" s="57"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="60"/>
+      <x:c r="B23" s="60"/>
+      <x:c r="C23" s="60"/>
+      <x:c r="D23" s="60"/>
+      <x:c r="E23" s="60"/>
+      <x:c r="F23" s="60"/>
+      <x:c r="G23" s="60"/>
+      <x:c r="H23" s="60"/>
+      <x:c r="I23" s="57"/>
+      <x:c r="J23" s="58" t="str">
+        <x:v>Direct games</x:v>
+      </x:c>
+      <x:c r="K23" s="58" t="n">
+        <x:f>COUNTA(A16:A19)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L23" s="58" t="str">
+        <x:f>IF(K23=4,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="M23" s="57"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="57"/>
+      <x:c r="B24" s="57"/>
+      <x:c r="C24" s="57"/>
+      <x:c r="D24" s="57"/>
+      <x:c r="E24" s="57"/>
+      <x:c r="F24" s="57"/>
+      <x:c r="G24" s="57"/>
+      <x:c r="H24" s="57"/>
+      <x:c r="I24" s="57"/>
+      <x:c r="J24" s="58" t="str">
+        <x:v>Direct replaced minutes</x:v>
+      </x:c>
+      <x:c r="K24" s="58" t="n">
+        <x:f>SUM(I16:I19)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L24" s="58" t="str">
+        <x:f>IF(K24=0,"PASS","REVIEW")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="M24" s="57"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="57"/>
+      <x:c r="B25" s="57"/>
+      <x:c r="C25" s="57"/>
+      <x:c r="D25" s="57"/>
+      <x:c r="E25" s="57"/>
+      <x:c r="F25" s="57"/>
+      <x:c r="G25" s="57"/>
+      <x:c r="H25" s="57"/>
+      <x:c r="I25" s="57"/>
+      <x:c r="J25" s="58" t="str">
+        <x:v>Denver CF two-way slots</x:v>
+      </x:c>
+      <x:c r="K25" s="58" t="n">
+        <x:f>COUNTIF(K7:K12,"CF_CHANGED_TWO_WAY")+COUNTIF(K7:K12,"CF_PROTECTED_TWO_WAY")</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L25" s="58" t="str">
+        <x:f>IF(K25=2,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="M25" s="57"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="57"/>
+      <x:c r="B26" s="57"/>
+      <x:c r="C26" s="57"/>
+      <x:c r="D26" s="57"/>
+      <x:c r="E26" s="57"/>
+      <x:c r="F26" s="57"/>
+      <x:c r="G26" s="57"/>
+      <x:c r="H26" s="57"/>
+      <x:c r="I26" s="57"/>
+      <x:c r="J26" s="58" t="str">
+        <x:v>Welsh duplicate blocked</x:v>
+      </x:c>
+      <x:c r="K26" s="58" t="n">
+        <x:f>COUNTIF(K7:K12,"CF_OUT_NO_SLOT")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L26" s="58" t="str">
+        <x:f>IF(K26=1,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="M26" s="57"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="57"/>
+      <x:c r="B27" s="57"/>
+      <x:c r="C27" s="57"/>
+      <x:c r="D27" s="57"/>
+      <x:c r="E27" s="57"/>
+      <x:c r="F27" s="57"/>
+      <x:c r="G27" s="57"/>
+      <x:c r="H27" s="57"/>
+      <x:c r="I27" s="57"/>
+      <x:c r="J27" s="58" t="str">
+        <x:v>Outcome lock</x:v>
+      </x:c>
+      <x:c r="K27" s="58" t="str">
+        <x:f>IF(AND(K24=0,K25=2,K26=1),"CASCADE DIRECT PASS","REVIEW")</x:f>
+        <x:v>CASCADE DIRECT PASS</x:v>
+      </x:c>
+      <x:c r="L27" s="58" t="str">
+        <x:f>IF(K27="CASCADE DIRECT PASS","PASS","HOLD")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="M27" s="57"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:M2"/>
+    <x:mergeCell ref="A21:H23"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="2">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rebf6d880b3174b0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d3711a7d9ae4c67"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -11359,10 +12169,10 @@
       <x:c r="D5" s="13" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E5" s="61" t="n">
+      <x:c r="E5" s="62" t="n">
         <x:v>0.105</x:v>
       </x:c>
-      <x:c r="F5" s="61" t="n">
+      <x:c r="F5" s="62" t="n">
         <x:v>0.4212</x:v>
       </x:c>
       <x:c r="G5" s="13" t="n">
@@ -11391,10 +12201,10 @@
       <x:c r="D6" s="13" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E6" s="61" t="n">
+      <x:c r="E6" s="62" t="n">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="F6" s="61" t="n">
+      <x:c r="F6" s="62" t="n">
         <x:v>0.263</x:v>
       </x:c>
       <x:c r="G6" s="13" t="n">
@@ -11490,8 +12300,8 @@
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="64" t="str">
-        <x:v>FINAL BLOCKER: Spurs baseline role is closed. Execute Atlanta player-game impacts and review any Spellman competitive stints before standings/lottery.</x:v>
+      <x:c r="A14" s="65" t="str">
+        <x:v>FINAL BLOCKER: Spurs, Dallas, and Denver contract layers are closed. Execute Atlanta player-game impacts and review only minutes beyond each displaced-player base before standings/lottery.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11505,7 +12315,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -11547,10 +12357,10 @@
         <x:v>G0</x:v>
       </x:c>
       <x:c r="B5" s="51" t="str">
-        <x:v>Spellman destination + second-team baseline</x:v>
+        <x:v>Changed-pick contract and direct-game baselines</x:v>
       </x:c>
       <x:c r="C5" s="51" t="str">
-        <x:v>Spurs #49; base 29 G/145.4 min; ATL series 0 min</x:v>
+        <x:v>Spurs 145.4 min; Dallas 1 min; Denver 36 min; ATL series all 0</x:v>
       </x:c>
       <x:c r="D5" s="53" t="str">
         <x:v>PASS</x:v>
@@ -11559,7 +12369,7 @@
         <x:v>None</x:v>
       </x:c>
       <x:c r="F5" s="51" t="str">
-        <x:v>Preserve role cap and donor trigger</x:v>
+        <x:v>Preserve team-specific caps and triggers</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -11743,25 +12553,25 @@
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="66"/>
-      <x:c r="B15" s="66"/>
-      <x:c r="C15" s="66"/>
-      <x:c r="D15" s="66"/>
-      <x:c r="E15" s="66"/>
-      <x:c r="F15" s="66"/>
+      <x:c r="A15" s="67"/>
+      <x:c r="B15" s="67"/>
+      <x:c r="C15" s="67"/>
+      <x:c r="D15" s="67"/>
+      <x:c r="E15" s="67"/>
+      <x:c r="F15" s="67"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="50" t="str">
         <x:v>OVERALL</x:v>
       </x:c>
       <x:c r="B16" s="50" t="str">
-        <x:v>SECOND_TEAM_BASELINE_PASS / OUTCOME_HOLD</x:v>
+        <x:v>CASCADE_CONTRACT_PASS / OUTCOME_HOLD</x:v>
       </x:c>
       <x:c r="C16" s="50"/>
       <x:c r="D16" s="50"/>
       <x:c r="E16" s="50"/>
       <x:c r="F16" s="50" t="str">
-        <x:v>Atlanta player-game and competitive-stint outcomes remain</x:v>
+        <x:v>Atlanta player-game and above-baseline competitive stints remain</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11772,7 +12582,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -12061,7 +12871,7 @@
         <x:v>Nuggets — Thomas Welsh two-way</x:v>
       </x:c>
       <x:c r="C23" s="51" t="str">
-        <x:v>Actual Welsh two-way destination used as role-preservation baseline</x:v>
+        <x:v>Actual Welsh occupied one Denver two-way slot</x:v>
       </x:c>
       <x:c r="D23" s="51" t="str">
         <x:v>https://www.nba.com/nuggets/news/thomas-welsh-signs-two-way-contract-071918</x:v>
@@ -12177,6 +12987,174 @@
       </x:c>
       <x:c r="D31" s="51" t="str">
         <x:v>https://www.nba.com/spurs/news/san-antonio-assigns-chimezie-metu-austin-spurs-8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="51" t="str">
+        <x:v>S28</x:v>
+      </x:c>
+      <x:c r="B32" s="51" t="str">
+        <x:v>Mavericks — Spalding signing</x:v>
+      </x:c>
+      <x:c r="C32" s="51" t="str">
+        <x:v>Dallas signed the actual #56 pick to a standard NBA contract</x:v>
+      </x:c>
+      <x:c r="D32" s="51" t="str">
+        <x:v>https://www.nba.com/mavs/mavericks-sign-forward-ray-spalding</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="51" t="str">
+        <x:v>S29</x:v>
+      </x:c>
+      <x:c r="B33" s="51" t="str">
+        <x:v>Mavericks — Porzingis trade and Spalding waiver</x:v>
+      </x:c>
+      <x:c r="C33" s="51" t="str">
+        <x:v>Spalding appeared in one Dallas game and was waived in the Jan. 31 roster move</x:v>
+      </x:c>
+      <x:c r="D33" s="51" t="str">
+        <x:v>https://www.nba.com/mavs/mavericks-acquire-all-star-kristaps-porzingis-tim-hardaway-jr-courtney-lee-and-trey-burke-in-trade-with-knicks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="51" t="str">
+        <x:v>S30</x:v>
+      </x:c>
+      <x:c r="B34" s="51" t="str">
+        <x:v>NBA G League — Ray Spalding</x:v>
+      </x:c>
+      <x:c r="C34" s="51" t="str">
+        <x:v>2018-19 Texas: 29 games, 26 starts, 30.1 MPG</x:v>
+      </x:c>
+      <x:c r="D34" s="51" t="str">
+        <x:v>https://gleague.nba.com/player/1629034/ray-spalding</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="51" t="str">
+        <x:v>S31</x:v>
+      </x:c>
+      <x:c r="B35" s="51" t="str">
+        <x:v>Nuggets — Thomas Welsh two-way</x:v>
+      </x:c>
+      <x:c r="C35" s="51" t="str">
+        <x:v>Denver signed the actual #58 pick to a two-way contract</x:v>
+      </x:c>
+      <x:c r="D35" s="51" t="str">
+        <x:v>https://www.nba.com/nuggets/news/thomas-welsh-signs-two-way-contract-071918</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="51" t="str">
+        <x:v>S32</x:v>
+      </x:c>
+      <x:c r="B36" s="51" t="str">
+        <x:v>Nuggets — 2018-19 two-way preview</x:v>
+      </x:c>
+      <x:c r="C36" s="51" t="str">
+        <x:v>Welsh and Akoon-Purcell occupied Denver's two two-way positions</x:v>
+      </x:c>
+      <x:c r="D36" s="51" t="str">
+        <x:v>https://www.nba.com/nuggets/news/1819-player-previews-akoon-purcell-welsh-091918</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="51" t="str">
+        <x:v>S33</x:v>
+      </x:c>
+      <x:c r="B37" s="51" t="str">
+        <x:v>NBA G League — 2018 two-way rule</x:v>
+      </x:c>
+      <x:c r="C37" s="51" t="str">
+        <x:v>2018-19 teams could carry two two-way players beyond the 15-man roster</x:v>
+      </x:c>
+      <x:c r="D37" s="51" t="str">
+        <x:v>https://windycity.gleague.nba.com/news/bulls-sign-brandon-sampson-to-two-way-contract</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="51" t="str">
+        <x:v>S34</x:v>
+      </x:c>
+      <x:c r="B38" s="51" t="str">
+        <x:v>Nuggets — Welsh 2018-19 recap</x:v>
+      </x:c>
+      <x:c r="C38" s="51" t="str">
+        <x:v>Welsh played 11 NBA games and 36 minutes; G League was his primary venue</x:v>
+      </x:c>
+      <x:c r="D38" s="51" t="str">
+        <x:v>https://www.nba.com/nuggets/news/denver-nuggets-thomas-welsh-excited-for-nba-summer-league-070219c</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="51" t="str">
+        <x:v>S35</x:v>
+      </x:c>
+      <x:c r="B39" s="51" t="str">
+        <x:v>RealGM — Thomas Welsh profile</x:v>
+      </x:c>
+      <x:c r="C39" s="51" t="str">
+        <x:v>Two-way transaction and 20-game G League allocation baseline</x:v>
+      </x:c>
+      <x:c r="D39" s="51" t="str">
+        <x:v>https://basketball.realgm.com/player/Thomas-Welsh/Summary/64323</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="51" t="str">
+        <x:v>S36</x:v>
+      </x:c>
+      <x:c r="B40" s="51" t="str">
+        <x:v>NBA — 2018-11-15 Atlanta at Denver</x:v>
+      </x:c>
+      <x:c r="C40" s="51" t="str">
+        <x:v>Denver 138-93 official game baseline</x:v>
+      </x:c>
+      <x:c r="D40" s="51" t="str">
+        <x:v>https://www.nba.com/game/atl-vs-den-0021800214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="51" t="str">
+        <x:v>S37</x:v>
+      </x:c>
+      <x:c r="B41" s="51" t="str">
+        <x:v>Basketball-Reference — 2018-11-15 box score</x:v>
+      </x:c>
+      <x:c r="C41" s="51" t="str">
+        <x:v>Welsh did not play against Atlanta</x:v>
+      </x:c>
+      <x:c r="D41" s="51" t="str">
+        <x:v>https://www.basketball-reference.com/boxscores/201811150DEN.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="51" t="str">
+        <x:v>S38</x:v>
+      </x:c>
+      <x:c r="B42" s="51" t="str">
+        <x:v>NBA Hawks — 2018-12-08 Denver at Atlanta</x:v>
+      </x:c>
+      <x:c r="C42" s="51" t="str">
+        <x:v>Atlanta 106-98 official game baseline</x:v>
+      </x:c>
+      <x:c r="D42" s="51" t="str">
+        <x:v>https://www.nba.com/hawks/game/0021800380</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="51" t="str">
+        <x:v>S39</x:v>
+      </x:c>
+      <x:c r="B43" s="51" t="str">
+        <x:v>Basketball-Reference — 2018-12-08 box score</x:v>
+      </x:c>
+      <x:c r="C43" s="51" t="str">
+        <x:v>Welsh did not play against Atlanta</x:v>
+      </x:c>
+      <x:c r="D43" s="51" t="str">
+        <x:v>https://www.basketball-reference.com/boxscores/201812080ATL.html</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12185,7 +13163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31c25f5cf78044f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52b7422b3c84448d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/simulation/ATLANTA_2018_19_CAUSALITY_LEDGER.xlsx
+++ b/simulation/ATLANTA_2018_19_CAUSALITY_LEDGER.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R857e0e900e5f48b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Ledger" sheetId="2" r:id="R421ea17d058944b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATL Assignment" sheetId="3" r:id="Recb3f187aaf34a7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season Minutes" sheetId="4" r:id="R0dee289dd5fc4935"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2018 Draft Board" sheetId="5" r:id="R76b2143f7df54d37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spurs Impact" sheetId="6" r:id="R6da4065cfaf44ba4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cascade Impact" sheetId="7" r:id="Rf4c6210d74524e73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft Bridge" sheetId="8" r:id="R9fe329ea575e411e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gate Audit" sheetId="9" r:id="Rb29fd86664374fb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" r:id="Rd2b857ef2cec4f04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc997d6f89aab4847"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Game Ledger" sheetId="2" r:id="R0d4cb4fc8a8f4de9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATL Assignment" sheetId="3" r:id="R65ca169544144882"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATL Receivers" sheetId="4" r:id="R0aebcfec6d2648d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season Minutes" sheetId="5" r:id="Rfc6e6e93bf1940f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2018 Draft Board" sheetId="6" r:id="R4808eeb5bda648c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spurs Impact" sheetId="7" r:id="R090ac7c97812452b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cascade Impact" sheetId="8" r:id="Ra54f70017df842d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Draft Bridge" sheetId="9" r:id="R8d32aabdeac84653"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gate Audit" sheetId="10" r:id="R5e26db9aea6b42ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="11" r:id="R679f9980e00943ad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -185,7 +186,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="90">
+  <x:cellXfs count="108">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -335,19 +336,78 @@
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -361,21 +421,12 @@
     <x:xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="204" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -424,7 +475,7 @@
     <x:tableColumn id="17" name="Protagonist status"/>
     <x:tableColumn id="18" name="Protagonist min"/>
     <x:tableColumn id="19" name="Spellman donor"/>
-    <x:tableColumn id="20" name="Reserve receiver"/>
+    <x:tableColumn id="20" name="Named receiver pool"/>
     <x:tableColumn id="21" name="Minute check"/>
     <x:tableColumn id="22" name="Outcome status"/>
     <x:tableColumn id="23" name="CF result"/>
@@ -436,7 +487,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SeasonMinutesTable" displayName="SeasonMinutesTable" ref="A5:L29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AtlReceiverAllocationTable" displayName="AtlReceiverAllocationTable" ref="A6:R37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="18">
+    <x:tableColumn id="1" name="Alloc"/>
+    <x:tableColumn id="2" name="Game"/>
+    <x:tableColumn id="3" name="Date"/>
+    <x:tableColumn id="4" name="Opponent"/>
+    <x:tableColumn id="5" name="Event ID"/>
+    <x:tableColumn id="6" name="Phase"/>
+    <x:tableColumn id="7" name="Receiver"/>
+    <x:tableColumn id="8" name="Box status"/>
+    <x:tableColumn id="9" name="Actual MIN"/>
+    <x:tableColumn id="10" name="Observed max"/>
+    <x:tableColumn id="11" name="Capacity"/>
+    <x:tableColumn id="12" name="Allocated"/>
+    <x:tableColumn id="13" name="Adjusted MIN"/>
+    <x:tableColumn id="14" name="Date allocated"/>
+    <x:tableColumn id="15" name="Game pool"/>
+    <x:tableColumn id="16" name="Date balance"/>
+    <x:tableColumn id="17" name="Source ID"/>
+    <x:tableColumn id="18" name="Evidence URL"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="AtlReceiverSummaryTable" displayName="AtlReceiverSummaryTable" ref="A42:J47" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="Receiver"/>
+    <x:tableColumn id="2" name="Pos"/>
+    <x:tableColumn id="3" name="Actual GP"/>
+    <x:tableColumn id="4" name="Actual MIN"/>
+    <x:tableColumn id="5" name="Observed max"/>
+    <x:tableColumn id="6" name="Allocated"/>
+    <x:tableColumn id="7" name="Added GP"/>
+    <x:tableColumn id="8" name="CF GP"/>
+    <x:tableColumn id="9" name="CF MIN"/>
+    <x:tableColumn id="10" name="Source ID"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SeasonMinutesTable" displayName="SeasonMinutesTable" ref="A5:L29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Player / bridge"/>
     <x:tableColumn id="2" name="Pos"/>
@@ -455,8 +550,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DraftBoardTable" displayName="DraftBoardTable" ref="A6:K37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DraftBoardTable" displayName="DraftBoardTable" ref="A6:K37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="Pick"/>
     <x:tableColumn id="2" name="Actual destination"/>
@@ -474,8 +569,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SpursAssignmentTable" displayName="SpursAssignmentTable" ref="A15:H34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="SpursAssignmentTable" displayName="SpursAssignmentTable" ref="A15:H34" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Window"/>
     <x:tableColumn id="2" name="Assign date"/>
@@ -490,8 +585,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="CascadeContractTable" displayName="CascadeContractTable" ref="A6:M12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="CascadeContractTable" displayName="CascadeContractTable" ref="A6:M12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="Team"/>
     <x:tableColumn id="2" name="World"/>
@@ -511,8 +606,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CascadeDirectGameTable" displayName="CascadeDirectGameTable" ref="A15:L19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="CascadeDirectGameTable" displayName="CascadeDirectGameTable" ref="A15:L19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Team"/>
     <x:tableColumn id="2" name="Date"/>
@@ -531,8 +626,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="SourceTable" displayName="SourceTable" ref="A4:D47" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="SourceTable" displayName="SourceTable" ref="A4:D50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Source"/>
@@ -750,7 +845,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="24" t="str">
-        <x:v>ATLANTA 2018-19 — CAUSALITY LEDGER / DRAFT BOARD v0.5</x:v>
+        <x:v>ATLANTA 2018-19 — CAUSALITY LEDGER / DRAFT BOARD v0.6</x:v>
       </x:c>
       <x:c r="B1" s="25"/>
       <x:c r="C1" s="25"/>
@@ -785,13 +880,13 @@
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B4" s="26" t="str">
-        <x:v>ATL_DONOR_VECTOR_PASS / OUTCOME_HOLD</x:v>
+        <x:v>ATL_RECEIVER_PASS / OUTCOME_HOLD</x:v>
       </x:c>
       <x:c r="C4" s="26" t="str">
         <x:v>Canon</x:v>
       </x:c>
       <x:c r="D4" s="26" t="str">
-        <x:v>v0.23 PARTIAL</x:v>
+        <x:v>v0.24 PARTIAL</x:v>
       </x:c>
       <x:c r="E4" s="26" t="str">
         <x:v>Manuscript</x:v>
@@ -1008,18 +1103,18 @@
         <x:v>PASS (rounding)</x:v>
       </x:c>
       <x:c r="E12" s="28" t="str">
-        <x:v>Protected core</x:v>
-      </x:c>
-      <x:c r="F12" s="28" t="str">
-        <x:f>"Young/Huerter/Collins"</x:f>
-        <x:v>Young/Huerter/Collins</x:v>
-      </x:c>
-      <x:c r="G12" s="28" t="str">
-        <x:v>Same</x:v>
+        <x:v>Named receiver balance</x:v>
+      </x:c>
+      <x:c r="F12" s="28" t="n">
+        <x:f>'ATL Receivers'!F4</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="28" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="29" t="str">
-        <x:f>IF(G12="Same","LOCK","FAIL")</x:f>
-        <x:v>LOCK</x:v>
+        <x:f>IF(ABS(F12-G12)&lt;0.01,"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1105,7 +1200,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B19" s="28" t="str">
-        <x:v>The 183.1-minute ATL remainder pool is an accounting bridge, not a fictional player. Named recipients and all counterfactual scores/results remain HOLD.</x:v>
+        <x:v>The 183.1-minute bridge is fully assigned by same-date evidence: Anderson 105.6, Poythress 48.6, Plumlee 17.5, Hamilton 11.4. Production and outcomes remain HOLD.</x:v>
       </x:c>
       <x:c r="C19" s="28"/>
       <x:c r="D19" s="28"/>
@@ -1126,7 +1221,7 @@
     </x:row>
     <x:row r="21" ht="34" customHeight="1">
       <x:c r="A21" s="32" t="str">
-        <x:v>NEXT: name the 183.1-minute reserve receivers → preregister pB/impact → fixed-hash outcome → opponent W/L → standings → lottery</x:v>
+        <x:v>NEXT: preregister player production / pB / impact priors → fixed-hash outcome → opponent W/L → standings → lottery</x:v>
       </x:c>
       <x:c r="B21" s="25"/>
       <x:c r="C21" s="25"/>
@@ -1155,6 +1250,273 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>R09 AUDIT GATES</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="11" t="str">
+        <x:v>Gate</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>Requirement</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>Current evidence</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>Blocks</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>Next action</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="82" t="str">
+        <x:v>G0</x:v>
+      </x:c>
+      <x:c r="B5" s="82" t="str">
+        <x:v>Changed-pick contract and direct-game baselines</x:v>
+      </x:c>
+      <x:c r="C5" s="82" t="str">
+        <x:v>Spurs 145.4 min; Dallas 1 min; Denver 36 min; ATL series all 0</x:v>
+      </x:c>
+      <x:c r="D5" s="84" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="E5" s="82" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="F5" s="82" t="str">
+        <x:v>Preserve team-specific caps and triggers</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="82" t="str">
+        <x:v>G1</x:v>
+      </x:c>
+      <x:c r="B6" s="82" t="str">
+        <x:v>82 unique + 29-53 + score/OT checksum</x:v>
+      </x:c>
+      <x:c r="C6" s="82" t="str">
+        <x:v>82 rows; 29-53; 9,294 pts; 19,855 game-min</x:v>
+      </x:c>
+      <x:c r="D6" s="84" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="E6" s="82" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="F6" s="82" t="str">
+        <x:v>Preserve immutable baseline</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="82" t="str">
+        <x:v>G2</x:v>
+      </x:c>
+      <x:c r="B7" s="82" t="str">
+        <x:v>Rotation/assignment/impact priors before results</x:v>
+      </x:c>
+      <x:c r="C7" s="82" t="str">
+        <x:v>≥7 donor gate; 16 cap; Nov. 19 cost; Dec. 7-22 Erie</x:v>
+      </x:c>
+      <x:c r="D7" s="84" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="E7" s="82" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="F7" s="82" t="str">
+        <x:v>Preserve before outcome model</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="82" t="str">
+        <x:v>G3</x:v>
+      </x:c>
+      <x:c r="B8" s="82" t="str">
+        <x:v>Every game minute-conserved; no NBA/Erie collision</x:v>
+      </x:c>
+      <x:c r="C8" s="82" t="str">
+        <x:v>621.9 protagonist + 183.1 named receivers = 805.0; 29 dates; zero balance</x:v>
+      </x:c>
+      <x:c r="D8" s="84" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="E8" s="82" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="F8" s="82" t="str">
+        <x:v>Preserve named receiver vector</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="82" t="str">
+        <x:v>G4</x:v>
+      </x:c>
+      <x:c r="B9" s="82" t="str">
+        <x:v>All 82 games contact classified</x:v>
+      </x:c>
+      <x:c r="C9" s="82" t="str">
+        <x:v>43 DIRECT / 39 ROSTER</x:v>
+      </x:c>
+      <x:c r="D9" s="84" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="E9" s="82" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="F9" s="82" t="str">
+        <x:v>Upgrade CASCADE only with evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="82" t="str">
+        <x:v>G5</x:v>
+      </x:c>
+      <x:c r="B10" s="82" t="str">
+        <x:v>Pregame-only pB; fixed latent u; no manual flip</x:v>
+      </x:c>
+      <x:c r="C10" s="82" t="str">
+        <x:v>Method selected; inputs absent</x:v>
+      </x:c>
+      <x:c r="D10" s="84" t="str">
+        <x:v>HOLD</x:v>
+      </x:c>
+      <x:c r="E10" s="82" t="str">
+        <x:v>CF result</x:v>
+      </x:c>
+      <x:c r="F10" s="82" t="str">
+        <x:v>Calibrate and preregister</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="82" t="str">
+        <x:v>G6</x:v>
+      </x:c>
+      <x:c r="B11" s="82" t="str">
+        <x:v>Chronological injury/fatigue/trade updates</x:v>
+      </x:c>
+      <x:c r="C11" s="82" t="str">
+        <x:v>Not executed</x:v>
+      </x:c>
+      <x:c r="D11" s="84" t="str">
+        <x:v>HOLD</x:v>
+      </x:c>
+      <x:c r="E11" s="82" t="str">
+        <x:v>CF result</x:v>
+      </x:c>
+      <x:c r="F11" s="82" t="str">
+        <x:v>Process in date order</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="82" t="str">
+        <x:v>G7</x:v>
+      </x:c>
+      <x:c r="B12" s="82" t="str">
+        <x:v>No exact score invention; sensitivity isolated</x:v>
+      </x:c>
+      <x:c r="C12" s="82" t="str">
+        <x:v>No CF scores/results created</x:v>
+      </x:c>
+      <x:c r="D12" s="84" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="E12" s="82" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="F12" s="82" t="str">
+        <x:v>Keep results HOLD until model</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="82" t="str">
+        <x:v>G8</x:v>
+      </x:c>
+      <x:c r="B13" s="82" t="str">
+        <x:v>Opponent W/L + league standings/tiebreaker</x:v>
+      </x:c>
+      <x:c r="C13" s="82" t="str">
+        <x:v>Not executed</x:v>
+      </x:c>
+      <x:c r="D13" s="84" t="str">
+        <x:v>HOLD</x:v>
+      </x:c>
+      <x:c r="E13" s="82" t="str">
+        <x:v>2019 lottery</x:v>
+      </x:c>
+      <x:c r="F13" s="82" t="str">
+        <x:v>Build league bridge</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="82" t="str">
+        <x:v>G9</x:v>
+      </x:c>
+      <x:c r="B14" s="82" t="str">
+        <x:v>Raw baseline immutable; run/model/seed logged</x:v>
+      </x:c>
+      <x:c r="C14" s="82" t="str">
+        <x:v>Baseline + protagonist + named receiver date vectors recorded</x:v>
+      </x:c>
+      <x:c r="D14" s="84" t="str">
+        <x:v>PARTIAL</x:v>
+      </x:c>
+      <x:c r="E14" s="82" t="str">
+        <x:v>Reproduction</x:v>
+      </x:c>
+      <x:c r="F14" s="82" t="str">
+        <x:v>Add production/outcome run manifest</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="81"/>
+      <x:c r="B15" s="81"/>
+      <x:c r="C15" s="81"/>
+      <x:c r="D15" s="81"/>
+      <x:c r="E15" s="81"/>
+      <x:c r="F15" s="81"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="77" t="str">
+        <x:v>OVERALL</x:v>
+      </x:c>
+      <x:c r="B16" s="77" t="str">
+        <x:v>ATL_RECEIVER_ALLOCATION_PASS / OUTCOME_HOLD</x:v>
+      </x:c>
+      <x:c r="C16" s="77"/>
+      <x:c r="D16" s="77"/>
+      <x:c r="E16" s="77"/>
+      <x:c r="F16" s="77" t="str">
+        <x:v>Preregister player production and game-impact priors before outcome execution</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="35" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
@@ -1181,605 +1543,647 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="75" t="str">
+      <x:c r="A5" s="82" t="str">
         <x:v>S01</x:v>
       </x:c>
-      <x:c r="B5" s="75" t="str">
+      <x:c r="B5" s="82" t="str">
         <x:v>NBA Stats — Atlanta schedule</x:v>
       </x:c>
-      <x:c r="C5" s="75" t="str">
+      <x:c r="C5" s="82" t="str">
         <x:v>82-game official schedule baseline</x:v>
       </x:c>
-      <x:c r="D5" s="75" t="str">
+      <x:c r="D5" s="82" t="str">
         <x:v>https://www.nba.com/stats/team/1610612737/schedule?Season=2018-19</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="75" t="str">
+      <x:c r="A6" s="82" t="str">
         <x:v>S02</x:v>
       </x:c>
-      <x:c r="B6" s="75" t="str">
+      <x:c r="B6" s="82" t="str">
         <x:v>ESPN — Atlanta schedule</x:v>
       </x:c>
-      <x:c r="C6" s="75" t="str">
+      <x:c r="C6" s="82" t="str">
         <x:v>Scores/order cross-check; timezone dates not authoritative</x:v>
       </x:c>
-      <x:c r="D6" s="75" t="str">
+      <x:c r="D6" s="82" t="str">
         <x:v>https://www.espn.com/nba/team/schedule?name=ATL&amp;season=2019&amp;seasontype=2</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="75" t="str">
+      <x:c r="A7" s="82" t="str">
         <x:v>S03</x:v>
       </x:c>
-      <x:c r="B7" s="75" t="str">
+      <x:c r="B7" s="82" t="str">
         <x:v>Basketball-Reference — Atlanta schedule</x:v>
       </x:c>
-      <x:c r="C7" s="75" t="str">
+      <x:c r="C7" s="82" t="str">
         <x:v>29-53 and game-log cross-check</x:v>
       </x:c>
-      <x:c r="D7" s="75" t="str">
+      <x:c r="D7" s="82" t="str">
         <x:v>https://www.basketball-reference.com/teams/ATL/2019_games.html</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="75" t="str">
+      <x:c r="A8" s="82" t="str">
         <x:v>S04</x:v>
       </x:c>
-      <x:c r="B8" s="75" t="str">
+      <x:c r="B8" s="82" t="str">
         <x:v>NBA Stats — Atlanta player totals</x:v>
       </x:c>
-      <x:c r="C8" s="75" t="str">
+      <x:c r="C8" s="82" t="str">
         <x:v>Roster GP/GS/minutes baseline</x:v>
       </x:c>
-      <x:c r="D8" s="75" t="str">
+      <x:c r="D8" s="82" t="str">
         <x:v>https://www.nba.com/stats/players/traditional?Season=2018-19&amp;SeasonType=Regular%20Season&amp;TeamID=1610612737&amp;PerMode=Totals</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="75" t="str">
+      <x:c r="A9" s="82" t="str">
         <x:v>S05</x:v>
       </x:c>
-      <x:c r="B9" s="75" t="str">
+      <x:c r="B9" s="82" t="str">
         <x:v>Hawks — Spellman injury update</x:v>
       </x:c>
-      <x:c r="C9" s="75" t="str">
+      <x:c r="C9" s="82" t="str">
         <x:v>March 1 high ankle sprain; not copied to protagonist</x:v>
       </x:c>
-      <x:c r="D9" s="75" t="str">
+      <x:c r="D9" s="82" t="str">
         <x:v>https://www.nba.com/hawks/news/omari-spellman-injury-update</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="75" t="str">
+      <x:c r="A10" s="82" t="str">
         <x:v>S06</x:v>
       </x:c>
-      <x:c r="B10" s="75" t="str">
+      <x:c r="B10" s="82" t="str">
         <x:v>NBA G League — Spellman</x:v>
       </x:c>
-      <x:c r="C10" s="75" t="str">
+      <x:c r="C10" s="82" t="str">
         <x:v>2018-19: 3 starts, 32.7 MPG</x:v>
       </x:c>
-      <x:c r="D10" s="75" t="str">
+      <x:c r="D10" s="82" t="str">
         <x:v>https://gleague.nba.com/player/1629016</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="75" t="str">
+      <x:c r="A11" s="82" t="str">
         <x:v>S07</x:v>
       </x:c>
-      <x:c r="B11" s="75" t="str">
+      <x:c r="B11" s="82" t="str">
         <x:v>Hawks — 2019 lottery odds explained</x:v>
       </x:c>
-      <x:c r="C11" s="75" t="str">
+      <x:c r="C11" s="82" t="str">
         <x:v>Atlanta/Dallas pick protection and odds baseline</x:v>
       </x:c>
-      <x:c r="D11" s="75" t="str">
+      <x:c r="D11" s="82" t="str">
         <x:v>https://www.nba.com/hawks/features/hawks-lottery-odds-explained</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="75" t="str">
+      <x:c r="A12" s="82" t="str">
         <x:v>S08</x:v>
       </x:c>
-      <x:c r="B12" s="75" t="str">
+      <x:c r="B12" s="82" t="str">
         <x:v>NBA Communications — 2019 tiebreakers</x:v>
       </x:c>
-      <x:c r="C12" s="75" t="str">
+      <x:c r="C12" s="82" t="str">
         <x:v>Lottery teams, inverse order, tied combinations</x:v>
       </x:c>
-      <x:c r="D12" s="75" t="str">
+      <x:c r="D12" s="82" t="str">
         <x:v>https://pr.nba.com/2019-nba-draft-tiebreakers/</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="75" t="str">
+      <x:c r="A13" s="82" t="str">
         <x:v>S09</x:v>
       </x:c>
-      <x:c r="B13" s="75" t="str">
+      <x:c r="B13" s="82" t="str">
         <x:v>NBA — 2019 lottery result</x:v>
       </x:c>
-      <x:c r="C13" s="75" t="str">
+      <x:c r="C13" s="82" t="str">
         <x:v>Actual draw baseline only</x:v>
       </x:c>
-      <x:c r="D13" s="75" t="str">
+      <x:c r="D13" s="82" t="str">
         <x:v>https://www.nba.com/news/pelicans-win-nba-draft-lottery</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="75" t="str">
+      <x:c r="A14" s="82" t="str">
         <x:v>S10</x:v>
       </x:c>
-      <x:c r="B14" s="75" t="str">
+      <x:c r="B14" s="82" t="str">
         <x:v>Hawks — Oct. 24 Dallas game</x:v>
       </x:c>
-      <x:c r="C14" s="75" t="str">
+      <x:c r="C14" s="82" t="str">
         <x:v>Atlanta 111-104 Dallas official game page</x:v>
       </x:c>
-      <x:c r="D14" s="75" t="str">
+      <x:c r="D14" s="82" t="str">
         <x:v>https://www.nba.com/hawks/game/0021800052-mavericks-vs-hawks-atlanta-ga-10-24-2018</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="75" t="str">
+      <x:c r="A15" s="82" t="str">
         <x:v>S11</x:v>
       </x:c>
-      <x:c r="B15" s="75" t="str">
+      <x:c r="B15" s="82" t="str">
         <x:v>Mavericks — Dec. 12 Atlanta game</x:v>
       </x:c>
-      <x:c r="C15" s="75" t="str">
+      <x:c r="C15" s="82" t="str">
         <x:v>Dallas 114-107 Atlanta official recap</x:v>
       </x:c>
-      <x:c r="D15" s="75" t="str">
+      <x:c r="D15" s="82" t="str">
         <x:v>https://www.nba.com/mavs/mavs-get-a-spark-from-carlisle-and-rallied-for-a-114-107-victory-over-the-hawks</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="75" t="str">
+      <x:c r="A16" s="82" t="str">
         <x:v>S12</x:v>
       </x:c>
-      <x:c r="B16" s="75" t="str">
+      <x:c r="B16" s="82" t="str">
         <x:v>NBA — 2018 Atlanta draft</x:v>
       </x:c>
-      <x:c r="C16" s="75" t="str">
+      <x:c r="C16" s="82" t="str">
         <x:v>Actual 30th pick was Spellman</x:v>
       </x:c>
-      <x:c r="D16" s="75" t="str">
+      <x:c r="D16" s="82" t="str">
         <x:v>https://www.nba.com/hawks/news/hawks-acquire-trae-young-select-kevin-huerter-omari-spellman-2018-nba-draft</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="75" t="str">
+      <x:c r="A17" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
-      <x:c r="B17" s="75" t="str">
+      <x:c r="B17" s="82" t="str">
         <x:v>NBA — 2018 Draft Trade Tracker</x:v>
       </x:c>
-      <x:c r="C17" s="75" t="str">
+      <x:c r="C17" s="82" t="str">
         <x:v>Actual picks, rights trades, and destination teams</x:v>
       </x:c>
-      <x:c r="D17" s="75" t="str">
+      <x:c r="D17" s="82" t="str">
         <x:v>https://www.nba.com/2018-draft-trade-tracker</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="75" t="str">
+      <x:c r="A18" s="82" t="str">
         <x:v>S14</x:v>
       </x:c>
-      <x:c r="B18" s="75" t="str">
+      <x:c r="B18" s="82" t="str">
         <x:v>San Antonio Express-News — Spurs workout target</x:v>
       </x:c>
-      <x:c r="C18" s="75" t="str">
+      <x:c r="C18" s="82" t="str">
         <x:v>Spellman worked out for Spurs; second workout interest</x:v>
       </x:c>
-      <x:c r="D18" s="75" t="str">
+      <x:c r="D18" s="82" t="str">
         <x:v>https://www.expressnews.com/spurs-nation/article/Spurs-target-Villanova-s-Spellman-others-for-12994749.php</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="75" t="str">
+      <x:c r="A19" s="82" t="str">
         <x:v>S15</x:v>
       </x:c>
-      <x:c r="B19" s="75" t="str">
+      <x:c r="B19" s="82" t="str">
         <x:v>Sports Illustrated — final 2018 mock</x:v>
       </x:c>
-      <x:c r="C19" s="75" t="str">
+      <x:c r="C19" s="82" t="str">
         <x:v>Spellman #44 range; Spurs fit; Metu second-round range</x:v>
       </x:c>
-      <x:c r="D19" s="75" t="str">
+      <x:c r="D19" s="82" t="str">
         <x:v>https://www.si.com/nba/2018/06/21/nba-mock-draft-2018-trade-rumors-final-picks-deandre-ayton-trae-young</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="75" t="str">
+      <x:c r="A20" s="82" t="str">
         <x:v>S16</x:v>
       </x:c>
-      <x:c r="B20" s="75" t="str">
+      <x:c r="B20" s="82" t="str">
         <x:v>Wizards — Issuf Sanon plan</x:v>
       </x:c>
-      <x:c r="C20" s="75" t="str">
+      <x:c r="C20" s="82" t="str">
         <x:v>Washington explicitly preferred an overseas stash</x:v>
       </x:c>
-      <x:c r="D20" s="75" t="str">
+      <x:c r="D20" s="82" t="str">
         <x:v>https://www.nba.com/wizards/wizards-plan-second-round-pick-issuf-sanon</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="75" t="str">
+      <x:c r="A21" s="82" t="str">
         <x:v>S17</x:v>
       </x:c>
-      <x:c r="B21" s="75" t="str">
+      <x:c r="B21" s="82" t="str">
         <x:v>Nets — Rodions Kurucs scouting history</x:v>
       </x:c>
-      <x:c r="C21" s="75" t="str">
+      <x:c r="C21" s="82" t="str">
         <x:v>Brooklyn's long-running Kurucs evaluation</x:v>
       </x:c>
-      <x:c r="D21" s="75" t="str">
+      <x:c r="D21" s="82" t="str">
         <x:v>https://www.nba.com/nets/news/feature/2018/12/28/brooklyn-nets-rookie-rodions-kurucs-had-a-breakout-month-in-december</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="75" t="str">
+      <x:c r="A22" s="82" t="str">
         <x:v>S18</x:v>
       </x:c>
-      <x:c r="B22" s="75" t="str">
+      <x:c r="B22" s="82" t="str">
         <x:v>NBA — 2018 big-board tiers</x:v>
       </x:c>
-      <x:c r="C22" s="75" t="str">
+      <x:c r="C22" s="82" t="str">
         <x:v>Spalding in drafted second-round tier; Welsh in the mix</x:v>
       </x:c>
-      <x:c r="D22" s="75" t="str">
+      <x:c r="D22" s="82" t="str">
         <x:v>https://www.nba.com/da-big-board-bigs-2018-draft</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="75" t="str">
+      <x:c r="A23" s="82" t="str">
         <x:v>S19</x:v>
       </x:c>
-      <x:c r="B23" s="75" t="str">
+      <x:c r="B23" s="82" t="str">
         <x:v>Nuggets — Thomas Welsh two-way</x:v>
       </x:c>
-      <x:c r="C23" s="75" t="str">
+      <x:c r="C23" s="82" t="str">
         <x:v>Actual Welsh occupied one Denver two-way slot</x:v>
       </x:c>
-      <x:c r="D23" s="75" t="str">
+      <x:c r="D23" s="82" t="str">
         <x:v>https://www.nba.com/nuggets/news/thomas-welsh-signs-two-way-contract-071918</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="75" t="str">
+      <x:c r="A24" s="82" t="str">
         <x:v>S20</x:v>
       </x:c>
-      <x:c r="B24" s="75" t="str">
+      <x:c r="B24" s="82" t="str">
         <x:v>Basketball-Reference — Chimezie Metu</x:v>
       </x:c>
-      <x:c r="C24" s="75" t="str">
+      <x:c r="C24" s="82" t="str">
         <x:v>2018-19 San Antonio: 29 games, 5.0 MPG (145 minutes)</x:v>
       </x:c>
-      <x:c r="D24" s="75" t="str">
+      <x:c r="D24" s="82" t="str">
         <x:v>https://www.basketball-reference.com/players/m/metuch01.html</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="75" t="str">
+      <x:c r="A25" s="82" t="str">
         <x:v>S21</x:v>
       </x:c>
-      <x:c r="B25" s="75" t="str">
+      <x:c r="B25" s="82" t="str">
         <x:v>Pounding the Rock — Metu season review</x:v>
       </x:c>
-      <x:c r="C25" s="75" t="str">
+      <x:c r="C25" s="82" t="str">
         <x:v>Most rookie NBA minutes came in garbage time; Austin was primary development venue</x:v>
       </x:c>
-      <x:c r="D25" s="75" t="str">
+      <x:c r="D25" s="82" t="str">
         <x:v>https://www.poundingtherock.com/2019/5/4/18523491/2018-2019-spurs-player-reviews-chimezie-metu</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="75" t="str">
+      <x:c r="A26" s="82" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="B26" s="75" t="str">
+      <x:c r="B26" s="82" t="str">
         <x:v>RealGM — Chimezie Metu profile</x:v>
       </x:c>
-      <x:c r="C26" s="75" t="str">
+      <x:c r="C26" s="82" t="str">
         <x:v>2018-19 NBA totals, Austin totals, and assignment/recall transaction log</x:v>
       </x:c>
-      <x:c r="D26" s="75" t="str">
+      <x:c r="D26" s="82" t="str">
         <x:v>https://basketball.realgm.com/player/Chimezie-Metu/Summary/76976</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="75" t="str">
+      <x:c r="A27" s="82" t="str">
         <x:v>S23</x:v>
       </x:c>
-      <x:c r="B27" s="75" t="str">
+      <x:c r="B27" s="82" t="str">
         <x:v>Spurs — Metu signing</x:v>
       </x:c>
-      <x:c r="C27" s="75" t="str">
+      <x:c r="C27" s="82" t="str">
         <x:v>Second-round pick signed to an NBA multi-year contract, not a two-way</x:v>
       </x:c>
-      <x:c r="D27" s="75" t="str">
+      <x:c r="D27" s="82" t="str">
         <x:v>https://www.nba.com/spurs/news/spurs-sign-2018-second-round-pick-chimezie-metu</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="75" t="str">
+      <x:c r="A28" s="82" t="str">
         <x:v>S24</x:v>
       </x:c>
-      <x:c r="B28" s="75" t="str">
+      <x:c r="B28" s="82" t="str">
         <x:v>Fox San Antonio — Nov. 20 assignment</x:v>
       </x:c>
-      <x:c r="C28" s="75" t="str">
+      <x:c r="C28" s="82" t="str">
         <x:v>Contemporary report identifies Metu's second Austin assignment and NBA baseline</x:v>
       </x:c>
-      <x:c r="D28" s="75" t="str">
+      <x:c r="D28" s="82" t="str">
         <x:v>https://foxsanantonio.com/sports/max-sports/spurs-assign-rookie-metu-to-g-league</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="75" t="str">
+      <x:c r="A29" s="82" t="str">
         <x:v>S25</x:v>
       </x:c>
-      <x:c r="B29" s="75" t="str">
+      <x:c r="B29" s="82" t="str">
         <x:v>ESPN — 2019-03-06 Spurs at Atlanta</x:v>
       </x:c>
-      <x:c r="C29" s="75" t="str">
+      <x:c r="C29" s="82" t="str">
         <x:v>Spurs 111-104; Metu DNP-Coach's Decision</x:v>
       </x:c>
-      <x:c r="D29" s="75" t="str">
+      <x:c r="D29" s="82" t="str">
         <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071641</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="75" t="str">
+      <x:c r="A30" s="82" t="str">
         <x:v>S26</x:v>
       </x:c>
-      <x:c r="B30" s="75" t="str">
+      <x:c r="B30" s="82" t="str">
         <x:v>NBA Hawks — 2019-04-02 Atlanta at Spurs</x:v>
       </x:c>
-      <x:c r="C30" s="75" t="str">
+      <x:c r="C30" s="82" t="str">
         <x:v>Spurs 117-111; Metu recorded no minutes</x:v>
       </x:c>
-      <x:c r="D30" s="75" t="str">
+      <x:c r="D30" s="82" t="str">
         <x:v>https://www.nba.com/hawks/game/0021801162-hawks-vs-spurs-san-antonio-tx-04-02-2019</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="75" t="str">
+      <x:c r="A31" s="82" t="str">
         <x:v>S27</x:v>
       </x:c>
-      <x:c r="B31" s="75" t="str">
+      <x:c r="B31" s="82" t="str">
         <x:v>Spurs — 2019 Metu Austin recap</x:v>
       </x:c>
-      <x:c r="C31" s="75" t="str">
+      <x:c r="C31" s="82" t="str">
         <x:v>2018-19 Austin: 26 games, 14.0/7.4/2.3 in 27.3 MPG</x:v>
       </x:c>
-      <x:c r="D31" s="75" t="str">
+      <x:c r="D31" s="82" t="str">
         <x:v>https://www.nba.com/spurs/news/san-antonio-assigns-chimezie-metu-austin-spurs-8</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="75" t="str">
+      <x:c r="A32" s="82" t="str">
         <x:v>S28</x:v>
       </x:c>
-      <x:c r="B32" s="75" t="str">
+      <x:c r="B32" s="82" t="str">
         <x:v>Mavericks — Spalding signing</x:v>
       </x:c>
-      <x:c r="C32" s="75" t="str">
+      <x:c r="C32" s="82" t="str">
         <x:v>Dallas signed the actual #56 pick to a standard NBA contract</x:v>
       </x:c>
-      <x:c r="D32" s="75" t="str">
+      <x:c r="D32" s="82" t="str">
         <x:v>https://www.nba.com/mavs/mavericks-sign-forward-ray-spalding</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="75" t="str">
+      <x:c r="A33" s="82" t="str">
         <x:v>S29</x:v>
       </x:c>
-      <x:c r="B33" s="75" t="str">
+      <x:c r="B33" s="82" t="str">
         <x:v>Mavericks — Porzingis trade and Spalding waiver</x:v>
       </x:c>
-      <x:c r="C33" s="75" t="str">
+      <x:c r="C33" s="82" t="str">
         <x:v>Spalding appeared in one Dallas game and was waived in the Jan. 31 roster move</x:v>
       </x:c>
-      <x:c r="D33" s="75" t="str">
+      <x:c r="D33" s="82" t="str">
         <x:v>https://www.nba.com/mavs/mavericks-acquire-all-star-kristaps-porzingis-tim-hardaway-jr-courtney-lee-and-trey-burke-in-trade-with-knicks</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="75" t="str">
+      <x:c r="A34" s="82" t="str">
         <x:v>S30</x:v>
       </x:c>
-      <x:c r="B34" s="75" t="str">
+      <x:c r="B34" s="82" t="str">
         <x:v>NBA G League — Ray Spalding</x:v>
       </x:c>
-      <x:c r="C34" s="75" t="str">
+      <x:c r="C34" s="82" t="str">
         <x:v>2018-19 Texas: 29 games, 26 starts, 30.1 MPG</x:v>
       </x:c>
-      <x:c r="D34" s="75" t="str">
+      <x:c r="D34" s="82" t="str">
         <x:v>https://gleague.nba.com/player/1629034/ray-spalding</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="75" t="str">
+      <x:c r="A35" s="82" t="str">
         <x:v>S31</x:v>
       </x:c>
-      <x:c r="B35" s="75" t="str">
+      <x:c r="B35" s="82" t="str">
         <x:v>Nuggets — Thomas Welsh two-way</x:v>
       </x:c>
-      <x:c r="C35" s="75" t="str">
+      <x:c r="C35" s="82" t="str">
         <x:v>Denver signed the actual #58 pick to a two-way contract</x:v>
       </x:c>
-      <x:c r="D35" s="75" t="str">
+      <x:c r="D35" s="82" t="str">
         <x:v>https://www.nba.com/nuggets/news/thomas-welsh-signs-two-way-contract-071918</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="75" t="str">
+      <x:c r="A36" s="82" t="str">
         <x:v>S32</x:v>
       </x:c>
-      <x:c r="B36" s="75" t="str">
+      <x:c r="B36" s="82" t="str">
         <x:v>Nuggets — 2018-19 two-way preview</x:v>
       </x:c>
-      <x:c r="C36" s="75" t="str">
+      <x:c r="C36" s="82" t="str">
         <x:v>Welsh and Akoon-Purcell occupied Denver's two two-way positions</x:v>
       </x:c>
-      <x:c r="D36" s="75" t="str">
+      <x:c r="D36" s="82" t="str">
         <x:v>https://www.nba.com/nuggets/news/1819-player-previews-akoon-purcell-welsh-091918</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="75" t="str">
+      <x:c r="A37" s="82" t="str">
         <x:v>S33</x:v>
       </x:c>
-      <x:c r="B37" s="75" t="str">
+      <x:c r="B37" s="82" t="str">
         <x:v>NBA G League — 2018 two-way rule</x:v>
       </x:c>
-      <x:c r="C37" s="75" t="str">
+      <x:c r="C37" s="82" t="str">
         <x:v>2018-19 teams could carry two two-way players beyond the 15-man roster</x:v>
       </x:c>
-      <x:c r="D37" s="75" t="str">
+      <x:c r="D37" s="82" t="str">
         <x:v>https://windycity.gleague.nba.com/news/bulls-sign-brandon-sampson-to-two-way-contract</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="75" t="str">
+      <x:c r="A38" s="82" t="str">
         <x:v>S34</x:v>
       </x:c>
-      <x:c r="B38" s="75" t="str">
+      <x:c r="B38" s="82" t="str">
         <x:v>Nuggets — Welsh 2018-19 recap</x:v>
       </x:c>
-      <x:c r="C38" s="75" t="str">
+      <x:c r="C38" s="82" t="str">
         <x:v>Welsh played 11 NBA games and 36 minutes; G League was his primary venue</x:v>
       </x:c>
-      <x:c r="D38" s="75" t="str">
+      <x:c r="D38" s="82" t="str">
         <x:v>https://www.nba.com/nuggets/news/denver-nuggets-thomas-welsh-excited-for-nba-summer-league-070219c</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="75" t="str">
+      <x:c r="A39" s="82" t="str">
         <x:v>S35</x:v>
       </x:c>
-      <x:c r="B39" s="75" t="str">
+      <x:c r="B39" s="82" t="str">
         <x:v>RealGM — Thomas Welsh profile</x:v>
       </x:c>
-      <x:c r="C39" s="75" t="str">
+      <x:c r="C39" s="82" t="str">
         <x:v>Two-way transaction and 20-game G League allocation baseline</x:v>
       </x:c>
-      <x:c r="D39" s="75" t="str">
+      <x:c r="D39" s="82" t="str">
         <x:v>https://basketball.realgm.com/player/Thomas-Welsh/Summary/64323</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="75" t="str">
+      <x:c r="A40" s="82" t="str">
         <x:v>S36</x:v>
       </x:c>
-      <x:c r="B40" s="75" t="str">
+      <x:c r="B40" s="82" t="str">
         <x:v>NBA — 2018-11-15 Atlanta at Denver</x:v>
       </x:c>
-      <x:c r="C40" s="75" t="str">
+      <x:c r="C40" s="82" t="str">
         <x:v>Denver 138-93 official game baseline</x:v>
       </x:c>
-      <x:c r="D40" s="75" t="str">
+      <x:c r="D40" s="82" t="str">
         <x:v>https://www.nba.com/game/atl-vs-den-0021800214</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="75" t="str">
+      <x:c r="A41" s="82" t="str">
         <x:v>S37</x:v>
       </x:c>
-      <x:c r="B41" s="75" t="str">
+      <x:c r="B41" s="82" t="str">
         <x:v>Basketball-Reference — 2018-11-15 box score</x:v>
       </x:c>
-      <x:c r="C41" s="75" t="str">
+      <x:c r="C41" s="82" t="str">
         <x:v>Welsh did not play against Atlanta</x:v>
       </x:c>
-      <x:c r="D41" s="75" t="str">
+      <x:c r="D41" s="82" t="str">
         <x:v>https://www.basketball-reference.com/boxscores/201811150DEN.html</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="75" t="str">
+      <x:c r="A42" s="82" t="str">
         <x:v>S38</x:v>
       </x:c>
-      <x:c r="B42" s="75" t="str">
+      <x:c r="B42" s="82" t="str">
         <x:v>NBA Hawks — 2018-12-08 Denver at Atlanta</x:v>
       </x:c>
-      <x:c r="C42" s="75" t="str">
+      <x:c r="C42" s="82" t="str">
         <x:v>Atlanta 106-98 official game baseline</x:v>
       </x:c>
-      <x:c r="D42" s="75" t="str">
+      <x:c r="D42" s="82" t="str">
         <x:v>https://www.nba.com/hawks/game/0021800380</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="75" t="str">
+      <x:c r="A43" s="82" t="str">
         <x:v>S39</x:v>
       </x:c>
-      <x:c r="B43" s="75" t="str">
+      <x:c r="B43" s="82" t="str">
         <x:v>Basketball-Reference — 2018-12-08 box score</x:v>
       </x:c>
-      <x:c r="C43" s="75" t="str">
+      <x:c r="C43" s="82" t="str">
         <x:v>Welsh did not play against Atlanta</x:v>
       </x:c>
-      <x:c r="D43" s="75" t="str">
+      <x:c r="D43" s="82" t="str">
         <x:v>https://www.basketball-reference.com/boxscores/201812080ATL.html</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="75" t="str">
+      <x:c r="A44" s="82" t="str">
         <x:v>S40</x:v>
       </x:c>
-      <x:c r="B44" s="75" t="str">
+      <x:c r="B44" s="82" t="str">
         <x:v>HoopsStats — Omari Spellman 2018-19 game log</x:v>
       </x:c>
-      <x:c r="C44" s="75" t="str">
+      <x:c r="C44" s="82" t="str">
         <x:v>Exact 46 appearance dates and published tenths-of-a-minute donor vector; sums to 805.0</x:v>
       </x:c>
-      <x:c r="D44" s="75" t="str">
+      <x:c r="D44" s="82" t="str">
         <x:v>https://www.hoopsstats.com/basketball/fantasy/nba/atlanta-hawks/players/omari-spellman/gamelog/19/1/16</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="75" t="str">
+      <x:c r="A45" s="82" t="str">
         <x:v>S41</x:v>
       </x:c>
-      <x:c r="B45" s="75" t="str">
+      <x:c r="B45" s="82" t="str">
         <x:v>RealGM — Omari Spellman profile</x:v>
       </x:c>
-      <x:c r="C45" s="75" t="str">
+      <x:c r="C45" s="82" t="str">
         <x:v>46 games, 11 starts, 804.6 exact season minutes cross-check</x:v>
       </x:c>
-      <x:c r="D45" s="75" t="str">
+      <x:c r="D45" s="82" t="str">
         <x:v>https://basketball.realgm.com/player/Omari-Spellman/Summary/74078</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="75" t="str">
+      <x:c r="A46" s="82" t="str">
         <x:v>S42</x:v>
       </x:c>
-      <x:c r="B46" s="75" t="str">
+      <x:c r="B46" s="82" t="str">
         <x:v>Peachtree Hoops — Spellman assigned to Erie</x:v>
       </x:c>
-      <x:c r="C46" s="75" t="str">
+      <x:c r="C46" s="82" t="str">
         <x:v>Actual Dec. 30 assignment followed hip-injury absence and conditioning need; context only, not copied</x:v>
       </x:c>
-      <x:c r="D46" s="75" t="str">
+      <x:c r="D46" s="82" t="str">
         <x:v>https://www.peachtreehoops.com/2018/12/30/18161520/omari-spellman-alex-poythress-atlanta-hawks-g-league-erie-bayhawks-assignment-transfer-roster</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="75" t="str">
+      <x:c r="A47" s="82" t="str">
         <x:v>S43</x:v>
       </x:c>
-      <x:c r="B47" s="75" t="str">
+      <x:c r="B47" s="82" t="str">
         <x:v>Basketball-Reference — Erie 2018-19 schedule</x:v>
       </x:c>
-      <x:c r="C47" s="75" t="str">
+      <x:c r="C47" s="82" t="str">
         <x:v>Six real Erie games in the Dec. 7-22 development window</x:v>
       </x:c>
-      <x:c r="D47" s="75" t="str">
+      <x:c r="D47" s="82" t="str">
         <x:v>https://www.basketball-reference.com/gleague/schedules/HAW/2019.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="82" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="B48" s="82" t="str">
+        <x:v>ESPN — Atlanta 2018-19 schedule and box scores</x:v>
+      </x:c>
+      <x:c r="C48" s="82" t="str">
+        <x:v>Same-date box-score listing, DNP-CD status, actual minutes, event IDs, and observed single-game maxima</x:v>
+      </x:c>
+      <x:c r="D48" s="82" t="str">
+        <x:v>https://www.espn.com/nba/team/schedule/_/name/atl/season/2019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="82" t="str">
+        <x:v>S45</x:v>
+      </x:c>
+      <x:c r="B49" s="82" t="str">
+        <x:v>Atlanta Hawks — Justin Anderson 2018-19 review</x:v>
+      </x:c>
+      <x:c r="C49" s="82" t="str">
+        <x:v>Anderson missed the first 16 games while rehabbing and returned for the Nov. 19 game</x:v>
+      </x:c>
+      <x:c r="D49" s="82" t="str">
+        <x:v>https://www.nba.com/hawks/features/five-things-know-about-justin-andersons-2018-19-season</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="82" t="str">
+        <x:v>S46</x:v>
+      </x:c>
+      <x:c r="B50" s="82" t="str">
+        <x:v>Atlanta Hawks — Alex Poythress 2018-19 review</x:v>
+      </x:c>
+      <x:c r="C50" s="82" t="str">
+        <x:v>Poythress held a two-way development role with Atlanta and Erie</x:v>
+      </x:c>
+      <x:c r="D50" s="82" t="str">
+        <x:v>https://www.nba.com/hawks/five-things-know-about-alex-poythress-2018-19-season</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1788,7 +2192,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7a5298ee7294a92"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bf0622d0ab84251"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1803,8 +2207,8 @@
     <x:col min="17" max="17" width="13" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="16" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="16" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="16" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="16" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="27" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="24" hidden="0" customWidth="1"/>
     <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="7" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
@@ -1893,7 +2297,7 @@
         <x:v>Spellman donor</x:v>
       </x:c>
       <x:c r="T5" s="51" t="str">
-        <x:v>Reserve receiver</x:v>
+        <x:v>Named receiver pool</x:v>
       </x:c>
       <x:c r="U5" s="51" t="str">
         <x:v>Minute check</x:v>
@@ -1988,10 +2392,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X6" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y6" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2072,10 +2476,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X7" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y7" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2156,10 +2560,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X8" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y8" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2240,10 +2644,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X9" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y9" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2324,10 +2728,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X10" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y10" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2408,10 +2812,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X11" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y11" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2492,10 +2896,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X12" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y12" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2576,10 +2980,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X13" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y13" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2660,10 +3064,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X14" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y14" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2744,10 +3148,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X15" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y15" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2828,10 +3232,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X16" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y16" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2912,10 +3316,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X17" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y17" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2996,10 +3400,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X18" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y18" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -3080,10 +3484,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X19" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y19" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -3164,10 +3568,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X20" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y20" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -3248,10 +3652,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X21" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y21" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -3332,10 +3736,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X22" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y22" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -3416,10 +3820,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X23" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y23" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3500,10 +3904,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X24" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y24" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -3584,10 +3988,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X25" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y25" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -3668,10 +4072,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X26" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y26" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3752,10 +4156,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X27" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y27" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -3836,10 +4240,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X28" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y28" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -3920,10 +4324,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X29" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y29" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -4004,10 +4408,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X30" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y30" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -4088,10 +4492,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X31" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y31" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -4172,10 +4576,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X32" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y32" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -4256,10 +4660,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X33" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y33" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4340,10 +4744,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X34" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y34" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -4424,10 +4828,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X35" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y35" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -4508,10 +4912,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X36" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y36" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4592,10 +4996,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X37" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y37" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -4676,10 +5080,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X38" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y38" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4760,10 +5164,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X39" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y39" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4844,10 +5248,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X40" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y40" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4928,10 +5332,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X41" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y41" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -5012,10 +5416,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X42" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y42" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -5096,10 +5500,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X43" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y43" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -5180,10 +5584,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X44" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y44" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -5264,10 +5668,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X45" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y45" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -5348,10 +5752,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X46" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y46" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -5432,10 +5836,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X47" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y47" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -5516,10 +5920,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X48" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y48" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -5600,10 +6004,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X49" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y49" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -5684,10 +6088,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X50" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y50" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -5768,10 +6172,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X51" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y51" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -5852,10 +6256,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X52" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y52" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -5936,10 +6340,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X53" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y53" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -6020,10 +6424,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X54" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y54" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -6104,10 +6508,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X55" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y55" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -6188,10 +6592,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X56" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y56" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -6272,10 +6676,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X57" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y57" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -6356,10 +6760,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X58" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y58" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -6440,10 +6844,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X59" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y59" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -6524,10 +6928,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X60" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y60" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -6608,10 +7012,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X61" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y61" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -6692,10 +7096,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X62" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y62" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -6776,10 +7180,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X63" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y63" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -6860,10 +7264,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X64" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y64" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -6944,10 +7348,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X65" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y65" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -7028,10 +7432,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X66" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y66" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -7112,10 +7516,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X67" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y67" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -7196,10 +7600,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X68" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y68" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -7280,10 +7684,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X69" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y69" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -7364,10 +7768,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X70" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y70" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -7448,10 +7852,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X71" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y71" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -7532,10 +7936,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X72" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y72" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -7616,10 +8020,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X73" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y73" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -7700,10 +8104,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X74" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y74" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -7784,10 +8188,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X75" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y75" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -7868,10 +8272,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X76" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y76" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -7952,10 +8356,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X77" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y77" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -8036,10 +8440,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X78" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y78" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -8120,10 +8524,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X79" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y79" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -8204,10 +8608,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X80" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y80" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -8288,10 +8692,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X81" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y81" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -8372,10 +8776,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X82" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y82" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -8456,10 +8860,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X83" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y83" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -8540,10 +8944,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X84" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y84" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -8624,10 +9028,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X85" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y85" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -8708,10 +9112,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X86" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y86" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -8792,10 +9196,10 @@
         <x:v>HOLD</x:v>
       </x:c>
       <x:c r="X87" s="59" t="str">
-        <x:v>PENDING</x:v>
+        <x:v>PRODUCTION_PRIOR_PENDING</x:v>
       </x:c>
       <x:c r="Y87" s="59" t="str">
-        <x:v>S01/S02/S03/S40</x:v>
+        <x:v>S01/S02/S03/S40/S44</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8805,7 +9209,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cb31e5e23254da4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d8b85fd19944e52"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9338,13 +9742,2474 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="21" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="21" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="13" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="48" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>ATLANTA 2018-19 — NAMED RESERVE RECEIVER ALLOCATION</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="87" t="str">
+        <x:v>Pool</x:v>
+      </x:c>
+      <x:c r="B4" s="88" t="n">
+        <x:f>SUM('Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>183.10000000000002</x:v>
+      </x:c>
+      <x:c r="C4" s="88" t="str">
+        <x:v>Allocated</x:v>
+      </x:c>
+      <x:c r="D4" s="88" t="n">
+        <x:f>SUM(L7:L37)</x:f>
+        <x:v>183.10000000000002</x:v>
+      </x:c>
+      <x:c r="E4" s="88" t="str">
+        <x:v>Balance</x:v>
+      </x:c>
+      <x:c r="F4" s="88" t="n">
+        <x:f>B4-D4</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="87" t="str">
+        <x:v>Dates</x:v>
+      </x:c>
+      <x:c r="H4" s="87" t="n">
+        <x:f>COUNTIF('Game Ledger'!$T$6:$T$87,"&gt;0")</x:f>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I4" s="87" t="str">
+        <x:v>Rows</x:v>
+      </x:c>
+      <x:c r="J4" s="87" t="n">
+        <x:f>COUNTA(A7:A37)</x:f>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K4" s="87" t="str">
+        <x:v>Receivers</x:v>
+      </x:c>
+      <x:c r="L4" s="87" t="n">
+        <x:f>COUNTIF(F43:F47,"&gt;0")</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M4" s="87" t="str">
+        <x:v>Uncovered</x:v>
+      </x:c>
+      <x:c r="N4" s="87" t="n">
+        <x:f>COUNTIF(P7:P37,"&gt;0.001")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O4" s="87" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="P4" s="89" t="str">
+        <x:f>IF(AND(ABS(F4)&lt;0.01,H4=29,J4=31,L4=4,N4=0),"PASS","FAIL")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="Q4" s="87" t="str">
+        <x:v>Next</x:v>
+      </x:c>
+      <x:c r="R4" s="87" t="str">
+        <x:v>Production prior</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="90"/>
+      <x:c r="B5" s="90"/>
+      <x:c r="C5" s="90"/>
+      <x:c r="D5" s="90"/>
+      <x:c r="E5" s="90"/>
+      <x:c r="F5" s="90"/>
+      <x:c r="G5" s="90"/>
+      <x:c r="H5" s="90"/>
+      <x:c r="I5" s="90"/>
+      <x:c r="J5" s="90"/>
+      <x:c r="K5" s="90"/>
+      <x:c r="L5" s="90"/>
+      <x:c r="M5" s="90"/>
+      <x:c r="N5" s="90"/>
+      <x:c r="O5" s="90"/>
+      <x:c r="P5" s="90"/>
+      <x:c r="Q5" s="90"/>
+      <x:c r="R5" s="90"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="51" t="str">
+        <x:v>Alloc</x:v>
+      </x:c>
+      <x:c r="B6" s="51" t="str">
+        <x:v>Game</x:v>
+      </x:c>
+      <x:c r="C6" s="51" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="D6" s="51" t="str">
+        <x:v>Opponent</x:v>
+      </x:c>
+      <x:c r="E6" s="51" t="str">
+        <x:v>Event ID</x:v>
+      </x:c>
+      <x:c r="F6" s="51" t="str">
+        <x:v>Phase</x:v>
+      </x:c>
+      <x:c r="G6" s="51" t="str">
+        <x:v>Receiver</x:v>
+      </x:c>
+      <x:c r="H6" s="51" t="str">
+        <x:v>Box status</x:v>
+      </x:c>
+      <x:c r="I6" s="51" t="str">
+        <x:v>Actual MIN</x:v>
+      </x:c>
+      <x:c r="J6" s="51" t="str">
+        <x:v>Observed max</x:v>
+      </x:c>
+      <x:c r="K6" s="51" t="str">
+        <x:v>Capacity</x:v>
+      </x:c>
+      <x:c r="L6" s="51" t="str">
+        <x:v>Allocated</x:v>
+      </x:c>
+      <x:c r="M6" s="51" t="str">
+        <x:v>Adjusted MIN</x:v>
+      </x:c>
+      <x:c r="N6" s="51" t="str">
+        <x:v>Date allocated</x:v>
+      </x:c>
+      <x:c r="O6" s="51" t="str">
+        <x:v>Game pool</x:v>
+      </x:c>
+      <x:c r="P6" s="51" t="str">
+        <x:v>Date balance</x:v>
+      </x:c>
+      <x:c r="Q6" s="51" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="R6" s="51" t="str">
+        <x:v>Evidence URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="91" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B7" s="91" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="92" t="n">
+        <x:v>43394.5</x:v>
+      </x:c>
+      <x:c r="D7" s="91" t="str">
+        <x:v>Cleveland Cavaliers</x:v>
+      </x:c>
+      <x:c r="E7" s="91" t="str">
+        <x:v>401070718</x:v>
+      </x:c>
+      <x:c r="F7" s="93" t="str">
+        <x:v>PRE_ANDERSON</x:v>
+      </x:c>
+      <x:c r="G7" s="93" t="str">
+        <x:v>Alex Poythress</x:v>
+      </x:c>
+      <x:c r="H7" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I7" s="94" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J7" s="94" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K7" s="95" t="n">
+        <x:f>J7-I7</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L7" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M7" s="95" t="n">
+        <x:f>I7+L7</x:f>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="N7" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C7,$L$7:$L$37)</x:f>
+        <x:v>7.8</x:v>
+      </x:c>
+      <x:c r="O7" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C7,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>7.8</x:v>
+      </x:c>
+      <x:c r="P7" s="95" t="n">
+        <x:f>O7-N7</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R7" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070718</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="91" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="91" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="92" t="n">
+        <x:v>43394.5</x:v>
+      </x:c>
+      <x:c r="D8" s="91" t="str">
+        <x:v>Cleveland Cavaliers</x:v>
+      </x:c>
+      <x:c r="E8" s="91" t="str">
+        <x:v>401070718</x:v>
+      </x:c>
+      <x:c r="F8" s="93" t="str">
+        <x:v>PRE_ANDERSON</x:v>
+      </x:c>
+      <x:c r="G8" s="93" t="str">
+        <x:v>Miles Plumlee</x:v>
+      </x:c>
+      <x:c r="H8" s="93" t="str">
+        <x:v>DNP-CD</x:v>
+      </x:c>
+      <x:c r="I8" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="94" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K8" s="95" t="n">
+        <x:f>J8-I8</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L8" s="95" t="n">
+        <x:v>5.8</x:v>
+      </x:c>
+      <x:c r="M8" s="95" t="n">
+        <x:f>I8+L8</x:f>
+        <x:v>5.8</x:v>
+      </x:c>
+      <x:c r="N8" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C8,$L$7:$L$37)</x:f>
+        <x:v>7.8</x:v>
+      </x:c>
+      <x:c r="O8" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C8,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>7.8</x:v>
+      </x:c>
+      <x:c r="P8" s="95" t="n">
+        <x:f>O8-N8</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R8" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070718</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="91" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="91" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C9" s="92" t="n">
+        <x:v>43402.5</x:v>
+      </x:c>
+      <x:c r="D9" s="91" t="str">
+        <x:v>Philadelphia 76ers</x:v>
+      </x:c>
+      <x:c r="E9" s="91" t="str">
+        <x:v>401070769</x:v>
+      </x:c>
+      <x:c r="F9" s="93" t="str">
+        <x:v>PRE_ANDERSON</x:v>
+      </x:c>
+      <x:c r="G9" s="93" t="str">
+        <x:v>Miles Plumlee</x:v>
+      </x:c>
+      <x:c r="H9" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I9" s="94" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J9" s="94" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K9" s="95" t="n">
+        <x:f>J9-I9</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L9" s="95" t="n">
+        <x:v>7.3</x:v>
+      </x:c>
+      <x:c r="M9" s="95" t="n">
+        <x:f>I9+L9</x:f>
+        <x:v>17.3</x:v>
+      </x:c>
+      <x:c r="N9" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C9,$L$7:$L$37)</x:f>
+        <x:v>7.3</x:v>
+      </x:c>
+      <x:c r="O9" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C9,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>7.3</x:v>
+      </x:c>
+      <x:c r="P9" s="95" t="n">
+        <x:f>O9-N9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q9" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R9" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070769</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="91" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B10" s="91" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C10" s="92" t="n">
+        <x:v>43403.5</x:v>
+      </x:c>
+      <x:c r="D10" s="91" t="str">
+        <x:v>Cleveland Cavaliers</x:v>
+      </x:c>
+      <x:c r="E10" s="91" t="str">
+        <x:v>401070778</x:v>
+      </x:c>
+      <x:c r="F10" s="93" t="str">
+        <x:v>PRE_ANDERSON</x:v>
+      </x:c>
+      <x:c r="G10" s="93" t="str">
+        <x:v>Miles Plumlee</x:v>
+      </x:c>
+      <x:c r="H10" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I10" s="94" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J10" s="94" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K10" s="95" t="n">
+        <x:f>J10-I10</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L10" s="95" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="M10" s="95" t="n">
+        <x:f>I10+L10</x:f>
+        <x:v>5.4</x:v>
+      </x:c>
+      <x:c r="N10" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C10,$L$7:$L$37)</x:f>
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="O10" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C10,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="P10" s="95" t="n">
+        <x:f>O10-N10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q10" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R10" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="91" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B11" s="91" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C11" s="92" t="n">
+        <x:v>43405.5</x:v>
+      </x:c>
+      <x:c r="D11" s="91" t="str">
+        <x:v>Sacramento Kings</x:v>
+      </x:c>
+      <x:c r="E11" s="91" t="str">
+        <x:v>401070795</x:v>
+      </x:c>
+      <x:c r="F11" s="93" t="str">
+        <x:v>PRE_ANDERSON</x:v>
+      </x:c>
+      <x:c r="G11" s="93" t="str">
+        <x:v>Alex Poythress</x:v>
+      </x:c>
+      <x:c r="H11" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I11" s="94" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="94" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K11" s="95" t="n">
+        <x:f>J11-I11</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L11" s="95" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="M11" s="95" t="n">
+        <x:f>I11+L11</x:f>
+        <x:v>21.5</x:v>
+      </x:c>
+      <x:c r="N11" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C11,$L$7:$L$37)</x:f>
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="O11" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C11,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="P11" s="95" t="n">
+        <x:f>O11-N11</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q11" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R11" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070795</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="91" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B12" s="91" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C12" s="92" t="n">
+        <x:v>43407.5</x:v>
+      </x:c>
+      <x:c r="D12" s="91" t="str">
+        <x:v>Miami Heat</x:v>
+      </x:c>
+      <x:c r="E12" s="91" t="str">
+        <x:v>401070809</x:v>
+      </x:c>
+      <x:c r="F12" s="93" t="str">
+        <x:v>PRE_ANDERSON</x:v>
+      </x:c>
+      <x:c r="G12" s="93" t="str">
+        <x:v>Alex Poythress</x:v>
+      </x:c>
+      <x:c r="H12" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I12" s="94" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J12" s="94" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K12" s="95" t="n">
+        <x:f>J12-I12</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L12" s="95" t="n">
+        <x:v>4.2</x:v>
+      </x:c>
+      <x:c r="M12" s="95" t="n">
+        <x:f>I12+L12</x:f>
+        <x:v>14.2</x:v>
+      </x:c>
+      <x:c r="N12" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C12,$L$7:$L$37)</x:f>
+        <x:v>4.2</x:v>
+      </x:c>
+      <x:c r="O12" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C12,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>4.2</x:v>
+      </x:c>
+      <x:c r="P12" s="95" t="n">
+        <x:f>O12-N12</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R12" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070809</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="91" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B13" s="91" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C13" s="92" t="n">
+        <x:v>43410.5</x:v>
+      </x:c>
+      <x:c r="D13" s="91" t="str">
+        <x:v>Charlotte Hornets</x:v>
+      </x:c>
+      <x:c r="E13" s="91" t="str">
+        <x:v>401070830</x:v>
+      </x:c>
+      <x:c r="F13" s="93" t="str">
+        <x:v>PRE_ANDERSON</x:v>
+      </x:c>
+      <x:c r="G13" s="93" t="str">
+        <x:v>Alex Poythress</x:v>
+      </x:c>
+      <x:c r="H13" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I13" s="94" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="94" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K13" s="95" t="n">
+        <x:f>J13-I13</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L13" s="95" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="M13" s="95" t="n">
+        <x:f>I13+L13</x:f>
+        <x:v>17.8</x:v>
+      </x:c>
+      <x:c r="N13" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C13,$L$7:$L$37)</x:f>
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="O13" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C13,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="P13" s="95" t="n">
+        <x:f>O13-N13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R13" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070830</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="91" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B14" s="91" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C14" s="92" t="n">
+        <x:v>43411.5</x:v>
+      </x:c>
+      <x:c r="D14" s="91" t="str">
+        <x:v>New York Knicks</x:v>
+      </x:c>
+      <x:c r="E14" s="91" t="str">
+        <x:v>401070836</x:v>
+      </x:c>
+      <x:c r="F14" s="93" t="str">
+        <x:v>PRE_ANDERSON</x:v>
+      </x:c>
+      <x:c r="G14" s="93" t="str">
+        <x:v>Alex Poythress</x:v>
+      </x:c>
+      <x:c r="H14" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I14" s="94" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J14" s="94" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K14" s="95" t="n">
+        <x:f>J14-I14</x:f>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="L14" s="95" t="n">
+        <x:v>12.5</x:v>
+      </x:c>
+      <x:c r="M14" s="95" t="n">
+        <x:f>I14+L14</x:f>
+        <x:v>21.5</x:v>
+      </x:c>
+      <x:c r="N14" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C14,$L$7:$L$37)</x:f>
+        <x:v>12.5</x:v>
+      </x:c>
+      <x:c r="O14" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C14,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>12.5</x:v>
+      </x:c>
+      <x:c r="P14" s="95" t="n">
+        <x:f>O14-N14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q14" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R14" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070836</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="91" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B15" s="91" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C15" s="92" t="n">
+        <x:v>43413.5</x:v>
+      </x:c>
+      <x:c r="D15" s="91" t="str">
+        <x:v>Detroit Pistons</x:v>
+      </x:c>
+      <x:c r="E15" s="91" t="str">
+        <x:v>401070850</x:v>
+      </x:c>
+      <x:c r="F15" s="93" t="str">
+        <x:v>PRE_ANDERSON</x:v>
+      </x:c>
+      <x:c r="G15" s="93" t="str">
+        <x:v>Alex Poythress</x:v>
+      </x:c>
+      <x:c r="H15" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I15" s="94" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J15" s="94" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K15" s="95" t="n">
+        <x:f>J15-I15</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L15" s="95" t="n">
+        <x:v>10.7</x:v>
+      </x:c>
+      <x:c r="M15" s="95" t="n">
+        <x:f>I15+L15</x:f>
+        <x:v>21.7</x:v>
+      </x:c>
+      <x:c r="N15" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C15,$L$7:$L$37)</x:f>
+        <x:v>10.7</x:v>
+      </x:c>
+      <x:c r="O15" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C15,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>10.7</x:v>
+      </x:c>
+      <x:c r="P15" s="95" t="n">
+        <x:f>O15-N15</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q15" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R15" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070850</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="91" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B16" s="91" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" s="92" t="n">
+        <x:v>43415.5</x:v>
+      </x:c>
+      <x:c r="D16" s="91" t="str">
+        <x:v>Los Angeles Lakers</x:v>
+      </x:c>
+      <x:c r="E16" s="91" t="str">
+        <x:v>401070870</x:v>
+      </x:c>
+      <x:c r="F16" s="93" t="str">
+        <x:v>PRE_ANDERSON</x:v>
+      </x:c>
+      <x:c r="G16" s="93" t="str">
+        <x:v>Alex Poythress</x:v>
+      </x:c>
+      <x:c r="H16" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I16" s="94" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J16" s="94" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K16" s="95" t="n">
+        <x:f>J16-I16</x:f>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L16" s="95" t="n">
+        <x:v>11.9</x:v>
+      </x:c>
+      <x:c r="M16" s="95" t="n">
+        <x:f>I16+L16</x:f>
+        <x:v>14.9</x:v>
+      </x:c>
+      <x:c r="N16" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C16,$L$7:$L$37)</x:f>
+        <x:v>11.9</x:v>
+      </x:c>
+      <x:c r="O16" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C16,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>11.9</x:v>
+      </x:c>
+      <x:c r="P16" s="95" t="n">
+        <x:f>O16-N16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q16" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R16" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070870</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="91" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B17" s="91" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C17" s="92" t="n">
+        <x:v>43419.5</x:v>
+      </x:c>
+      <x:c r="D17" s="91" t="str">
+        <x:v>Denver Nuggets</x:v>
+      </x:c>
+      <x:c r="E17" s="91" t="str">
+        <x:v>401070895</x:v>
+      </x:c>
+      <x:c r="F17" s="93" t="str">
+        <x:v>PRE_ANDERSON</x:v>
+      </x:c>
+      <x:c r="G17" s="93" t="str">
+        <x:v>Alex Poythress</x:v>
+      </x:c>
+      <x:c r="H17" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I17" s="94" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J17" s="94" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K17" s="95" t="n">
+        <x:f>J17-I17</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L17" s="95" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M17" s="95" t="n">
+        <x:f>I17+L17</x:f>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="N17" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C17,$L$7:$L$37)</x:f>
+        <x:v>10.7</x:v>
+      </x:c>
+      <x:c r="O17" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C17,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>10.7</x:v>
+      </x:c>
+      <x:c r="P17" s="95" t="n">
+        <x:f>O17-N17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q17" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R17" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070895</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="91" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B18" s="91" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="92" t="n">
+        <x:v>43419.5</x:v>
+      </x:c>
+      <x:c r="D18" s="91" t="str">
+        <x:v>Denver Nuggets</x:v>
+      </x:c>
+      <x:c r="E18" s="91" t="str">
+        <x:v>401070895</x:v>
+      </x:c>
+      <x:c r="F18" s="93" t="str">
+        <x:v>PRE_ANDERSON</x:v>
+      </x:c>
+      <x:c r="G18" s="93" t="str">
+        <x:v>Daniel Hamilton</x:v>
+      </x:c>
+      <x:c r="H18" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I18" s="94" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J18" s="94" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K18" s="95" t="n">
+        <x:f>J18-I18</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L18" s="95" t="n">
+        <x:v>8.7</x:v>
+      </x:c>
+      <x:c r="M18" s="95" t="n">
+        <x:f>I18+L18</x:f>
+        <x:v>16.7</x:v>
+      </x:c>
+      <x:c r="N18" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C18,$L$7:$L$37)</x:f>
+        <x:v>10.7</x:v>
+      </x:c>
+      <x:c r="O18" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C18,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>10.7</x:v>
+      </x:c>
+      <x:c r="P18" s="95" t="n">
+        <x:f>O18-N18</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q18" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R18" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070895</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="91" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B19" s="91" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C19" s="92" t="n">
+        <x:v>43423.5</x:v>
+      </x:c>
+      <x:c r="D19" s="91" t="str">
+        <x:v>Los Angeles Clippers</x:v>
+      </x:c>
+      <x:c r="E19" s="91" t="str">
+        <x:v>401070924</x:v>
+      </x:c>
+      <x:c r="F19" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G19" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H19" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I19" s="94" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J19" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K19" s="95" t="n">
+        <x:f>J19-I19</x:f>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L19" s="95" t="n">
+        <x:v>14.1</x:v>
+      </x:c>
+      <x:c r="M19" s="95" t="n">
+        <x:f>I19+L19</x:f>
+        <x:v>17.1</x:v>
+      </x:c>
+      <x:c r="N19" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C19,$L$7:$L$37)</x:f>
+        <x:v>14.1</x:v>
+      </x:c>
+      <x:c r="O19" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C19,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>14.1</x:v>
+      </x:c>
+      <x:c r="P19" s="95" t="n">
+        <x:f>O19-N19</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q19" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R19" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070924</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="91" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B20" s="91" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C20" s="92" t="n">
+        <x:v>43431.5</x:v>
+      </x:c>
+      <x:c r="D20" s="91" t="str">
+        <x:v>Miami Heat</x:v>
+      </x:c>
+      <x:c r="E20" s="91" t="str">
+        <x:v>401070983</x:v>
+      </x:c>
+      <x:c r="F20" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G20" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H20" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I20" s="94" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J20" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K20" s="95" t="n">
+        <x:f>J20-I20</x:f>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L20" s="95" t="n">
+        <x:v>4.3</x:v>
+      </x:c>
+      <x:c r="M20" s="95" t="n">
+        <x:f>I20+L20</x:f>
+        <x:v>6.3</x:v>
+      </x:c>
+      <x:c r="N20" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C20,$L$7:$L$37)</x:f>
+        <x:v>4.3</x:v>
+      </x:c>
+      <x:c r="O20" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C20,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>4.3</x:v>
+      </x:c>
+      <x:c r="P20" s="95" t="n">
+        <x:f>O20-N20</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q20" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R20" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070983</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="91" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B21" s="91" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C21" s="92" t="n">
+        <x:v>43432.5</x:v>
+      </x:c>
+      <x:c r="D21" s="91" t="str">
+        <x:v>Charlotte Hornets</x:v>
+      </x:c>
+      <x:c r="E21" s="91" t="str">
+        <x:v>401070987</x:v>
+      </x:c>
+      <x:c r="F21" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G21" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H21" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I21" s="94" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J21" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K21" s="95" t="n">
+        <x:f>J21-I21</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="L21" s="95" t="n">
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="M21" s="95" t="n">
+        <x:f>I21+L21</x:f>
+        <x:v>22.6</x:v>
+      </x:c>
+      <x:c r="N21" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C21,$L$7:$L$37)</x:f>
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="O21" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C21,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>5.6</x:v>
+      </x:c>
+      <x:c r="P21" s="95" t="n">
+        <x:f>O21-N21</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q21" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R21" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401070987</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="91" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B22" s="91" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C22" s="92" t="n">
+        <x:v>43471.5</x:v>
+      </x:c>
+      <x:c r="D22" s="91" t="str">
+        <x:v>Miami Heat</x:v>
+      </x:c>
+      <x:c r="E22" s="91" t="str">
+        <x:v>401071263</x:v>
+      </x:c>
+      <x:c r="F22" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G22" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H22" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I22" s="94" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J22" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K22" s="95" t="n">
+        <x:f>J22-I22</x:f>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L22" s="95" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="M22" s="95" t="n">
+        <x:f>I22+L22</x:f>
+        <x:v>5.7</x:v>
+      </x:c>
+      <x:c r="N22" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C22,$L$7:$L$37)</x:f>
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="O22" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C22,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="P22" s="95" t="n">
+        <x:f>O22-N22</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q22" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R22" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="91" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B23" s="91" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C23" s="92" t="n">
+        <x:v>43476.5</x:v>
+      </x:c>
+      <x:c r="D23" s="91" t="str">
+        <x:v>Philadelphia 76ers</x:v>
+      </x:c>
+      <x:c r="E23" s="91" t="str">
+        <x:v>401071297</x:v>
+      </x:c>
+      <x:c r="F23" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G23" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H23" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I23" s="94" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J23" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K23" s="95" t="n">
+        <x:f>J23-I23</x:f>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L23" s="95" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="M23" s="95" t="n">
+        <x:f>I23+L23</x:f>
+        <x:v>13.9</x:v>
+      </x:c>
+      <x:c r="N23" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C23,$L$7:$L$37)</x:f>
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="O23" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C23,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="P23" s="95" t="n">
+        <x:f>O23-N23</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q23" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R23" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="91" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B24" s="91" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C24" s="92" t="n">
+        <x:v>43478.5</x:v>
+      </x:c>
+      <x:c r="D24" s="91" t="str">
+        <x:v>Milwaukee Bucks</x:v>
+      </x:c>
+      <x:c r="E24" s="91" t="str">
+        <x:v>401071316</x:v>
+      </x:c>
+      <x:c r="F24" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G24" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H24" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I24" s="94" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J24" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K24" s="95" t="n">
+        <x:f>J24-I24</x:f>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L24" s="95" t="n">
+        <x:v>13.9</x:v>
+      </x:c>
+      <x:c r="M24" s="95" t="n">
+        <x:f>I24+L24</x:f>
+        <x:v>16.9</x:v>
+      </x:c>
+      <x:c r="N24" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C24,$L$7:$L$37)</x:f>
+        <x:v>13.9</x:v>
+      </x:c>
+      <x:c r="O24" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C24,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>13.9</x:v>
+      </x:c>
+      <x:c r="P24" s="95" t="n">
+        <x:f>O24-N24</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q24" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R24" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071316</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="91" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B25" s="91" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C25" s="92" t="n">
+        <x:v>43480.5</x:v>
+      </x:c>
+      <x:c r="D25" s="91" t="str">
+        <x:v>Oklahoma City Thunder</x:v>
+      </x:c>
+      <x:c r="E25" s="91" t="str">
+        <x:v>401071329</x:v>
+      </x:c>
+      <x:c r="F25" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G25" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H25" s="93" t="str">
+        <x:v>DNP-CD</x:v>
+      </x:c>
+      <x:c r="I25" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J25" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K25" s="95" t="n">
+        <x:f>J25-I25</x:f>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L25" s="95" t="n">
+        <x:v>5.9</x:v>
+      </x:c>
+      <x:c r="M25" s="95" t="n">
+        <x:f>I25+L25</x:f>
+        <x:v>5.9</x:v>
+      </x:c>
+      <x:c r="N25" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C25,$L$7:$L$37)</x:f>
+        <x:v>5.9</x:v>
+      </x:c>
+      <x:c r="O25" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C25,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>5.9</x:v>
+      </x:c>
+      <x:c r="P25" s="95" t="n">
+        <x:f>O25-N25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q25" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R25" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="91" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B26" s="91" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C26" s="92" t="n">
+        <x:v>43486.5</x:v>
+      </x:c>
+      <x:c r="D26" s="91" t="str">
+        <x:v>Orlando Magic</x:v>
+      </x:c>
+      <x:c r="E26" s="91" t="str">
+        <x:v>401071371</x:v>
+      </x:c>
+      <x:c r="F26" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G26" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H26" s="93" t="str">
+        <x:v>DNP-CD</x:v>
+      </x:c>
+      <x:c r="I26" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K26" s="95" t="n">
+        <x:f>J26-I26</x:f>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L26" s="95" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="M26" s="95" t="n">
+        <x:f>I26+L26</x:f>
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="N26" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C26,$L$7:$L$37)</x:f>
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="O26" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C26,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="P26" s="95" t="n">
+        <x:f>O26-N26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q26" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R26" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071371</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="91" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B27" s="91" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C27" s="92" t="n">
+        <x:v>43488.5</x:v>
+      </x:c>
+      <x:c r="D27" s="91" t="str">
+        <x:v>Chicago Bulls</x:v>
+      </x:c>
+      <x:c r="E27" s="91" t="str">
+        <x:v>401071385</x:v>
+      </x:c>
+      <x:c r="F27" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G27" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H27" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I27" s="94" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J27" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K27" s="95" t="n">
+        <x:f>J27-I27</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L27" s="95" t="n">
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="M27" s="95" t="n">
+        <x:f>I27+L27</x:f>
+        <x:v>21.6</x:v>
+      </x:c>
+      <x:c r="N27" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C27,$L$7:$L$37)</x:f>
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="O27" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C27,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="P27" s="95" t="n">
+        <x:f>O27-N27</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q27" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R27" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="91" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B28" s="91" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C28" s="92" t="n">
+        <x:v>43495.5</x:v>
+      </x:c>
+      <x:c r="D28" s="91" t="str">
+        <x:v>Sacramento Kings</x:v>
+      </x:c>
+      <x:c r="E28" s="91" t="str">
+        <x:v>401071435</x:v>
+      </x:c>
+      <x:c r="F28" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G28" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H28" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I28" s="94" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J28" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K28" s="95" t="n">
+        <x:f>J28-I28</x:f>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L28" s="95" t="n">
+        <x:v>8.1</x:v>
+      </x:c>
+      <x:c r="M28" s="95" t="n">
+        <x:f>I28+L28</x:f>
+        <x:v>11.1</x:v>
+      </x:c>
+      <x:c r="N28" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C28,$L$7:$L$37)</x:f>
+        <x:v>8.1</x:v>
+      </x:c>
+      <x:c r="O28" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C28,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>8.1</x:v>
+      </x:c>
+      <x:c r="P28" s="95" t="n">
+        <x:f>O28-N28</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q28" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R28" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="91" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B29" s="91" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C29" s="92" t="n">
+        <x:v>43497.5</x:v>
+      </x:c>
+      <x:c r="D29" s="91" t="str">
+        <x:v>Utah Jazz</x:v>
+      </x:c>
+      <x:c r="E29" s="91" t="str">
+        <x:v>401071446</x:v>
+      </x:c>
+      <x:c r="F29" s="93" t="str">
+        <x:v>ANDERSON_NOT_LISTED</x:v>
+      </x:c>
+      <x:c r="G29" s="93" t="str">
+        <x:v>Daniel Hamilton</x:v>
+      </x:c>
+      <x:c r="H29" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I29" s="94" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J29" s="94" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K29" s="95" t="n">
+        <x:f>J29-I29</x:f>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L29" s="95" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="M29" s="95" t="n">
+        <x:f>I29+L29</x:f>
+        <x:v>4.7</x:v>
+      </x:c>
+      <x:c r="N29" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C29,$L$7:$L$37)</x:f>
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="O29" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C29,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="P29" s="95" t="n">
+        <x:f>O29-N29</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q29" s="91" t="str">
+        <x:v>S44</x:v>
+      </x:c>
+      <x:c r="R29" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071446</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="91" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B30" s="91" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C30" s="92" t="n">
+        <x:v>43500.5</x:v>
+      </x:c>
+      <x:c r="D30" s="91" t="str">
+        <x:v>Washington Wizards</x:v>
+      </x:c>
+      <x:c r="E30" s="91" t="str">
+        <x:v>401071464</x:v>
+      </x:c>
+      <x:c r="F30" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G30" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H30" s="93" t="str">
+        <x:v>DNP-CD</x:v>
+      </x:c>
+      <x:c r="I30" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J30" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K30" s="95" t="n">
+        <x:f>J30-I30</x:f>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L30" s="95" t="n">
+        <x:v>13.9</x:v>
+      </x:c>
+      <x:c r="M30" s="95" t="n">
+        <x:f>I30+L30</x:f>
+        <x:v>13.9</x:v>
+      </x:c>
+      <x:c r="N30" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C30,$L$7:$L$37)</x:f>
+        <x:v>13.9</x:v>
+      </x:c>
+      <x:c r="O30" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C30,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>13.9</x:v>
+      </x:c>
+      <x:c r="P30" s="95" t="n">
+        <x:f>O30-N30</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q30" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R30" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071464</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="91" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B31" s="91" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C31" s="92" t="n">
+        <x:v>43506.5</x:v>
+      </x:c>
+      <x:c r="D31" s="91" t="str">
+        <x:v>Orlando Magic</x:v>
+      </x:c>
+      <x:c r="E31" s="91" t="str">
+        <x:v>401071510</x:v>
+      </x:c>
+      <x:c r="F31" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G31" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H31" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I31" s="94" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J31" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K31" s="95" t="n">
+        <x:f>J31-I31</x:f>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="L31" s="95" t="n">
+        <x:v>10.3</x:v>
+      </x:c>
+      <x:c r="M31" s="95" t="n">
+        <x:f>I31+L31</x:f>
+        <x:v>19.3</x:v>
+      </x:c>
+      <x:c r="N31" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C31,$L$7:$L$37)</x:f>
+        <x:v>10.3</x:v>
+      </x:c>
+      <x:c r="O31" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C31,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>10.3</x:v>
+      </x:c>
+      <x:c r="P31" s="95" t="n">
+        <x:f>O31-N31</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q31" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R31" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071510</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="91" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B32" s="91" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C32" s="92" t="n">
+        <x:v>43510.5</x:v>
+      </x:c>
+      <x:c r="D32" s="91" t="str">
+        <x:v>New York Knicks</x:v>
+      </x:c>
+      <x:c r="E32" s="91" t="str">
+        <x:v>401071538</x:v>
+      </x:c>
+      <x:c r="F32" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G32" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H32" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I32" s="94" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J32" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K32" s="95" t="n">
+        <x:f>J32-I32</x:f>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L32" s="95" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="M32" s="95" t="n">
+        <x:f>I32+L32</x:f>
+        <x:v>6.1</x:v>
+      </x:c>
+      <x:c r="N32" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C32,$L$7:$L$37)</x:f>
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="O32" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C32,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="P32" s="95" t="n">
+        <x:f>O32-N32</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q32" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R32" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071538</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="91" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B33" s="91" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C33" s="92" t="n">
+        <x:v>43518.5</x:v>
+      </x:c>
+      <x:c r="D33" s="91" t="str">
+        <x:v>Detroit Pistons</x:v>
+      </x:c>
+      <x:c r="E33" s="91" t="str">
+        <x:v>401071550</x:v>
+      </x:c>
+      <x:c r="F33" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G33" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H33" s="93" t="str">
+        <x:v>DNP-CD</x:v>
+      </x:c>
+      <x:c r="I33" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J33" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K33" s="95" t="n">
+        <x:f>J33-I33</x:f>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L33" s="95" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="M33" s="95" t="n">
+        <x:f>I33+L33</x:f>
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="N33" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C33,$L$7:$L$37)</x:f>
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="O33" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C33,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="P33" s="95" t="n">
+        <x:f>O33-N33</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q33" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R33" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="91" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B34" s="91" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C34" s="92" t="n">
+        <x:v>43519.5</x:v>
+      </x:c>
+      <x:c r="D34" s="91" t="str">
+        <x:v>Phoenix Suns</x:v>
+      </x:c>
+      <x:c r="E34" s="91" t="str">
+        <x:v>401071556</x:v>
+      </x:c>
+      <x:c r="F34" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G34" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H34" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I34" s="94" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J34" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K34" s="95" t="n">
+        <x:f>J34-I34</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L34" s="95" t="n">
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="M34" s="95" t="n">
+        <x:f>I34+L34</x:f>
+        <x:v>11.5</x:v>
+      </x:c>
+      <x:c r="N34" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C34,$L$7:$L$37)</x:f>
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="O34" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C34,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>5.5</x:v>
+      </x:c>
+      <x:c r="P34" s="95" t="n">
+        <x:f>O34-N34</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q34" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R34" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="91" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B35" s="91" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C35" s="92" t="n">
+        <x:v>43521.5</x:v>
+      </x:c>
+      <x:c r="D35" s="91" t="str">
+        <x:v>Houston Rockets</x:v>
+      </x:c>
+      <x:c r="E35" s="91" t="str">
+        <x:v>401071576</x:v>
+      </x:c>
+      <x:c r="F35" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G35" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H35" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I35" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J35" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K35" s="95" t="n">
+        <x:f>J35-I35</x:f>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L35" s="95" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M35" s="95" t="n">
+        <x:f>I35+L35</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N35" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C35,$L$7:$L$37)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O35" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C35,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="P35" s="95" t="n">
+        <x:f>O35-N35</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q35" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R35" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071576</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="91" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B36" s="91" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C36" s="92" t="n">
+        <x:v>43523.5</x:v>
+      </x:c>
+      <x:c r="D36" s="91" t="str">
+        <x:v>Minnesota Timberwolves</x:v>
+      </x:c>
+      <x:c r="E36" s="91" t="str">
+        <x:v>401071585</x:v>
+      </x:c>
+      <x:c r="F36" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G36" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H36" s="93" t="str">
+        <x:v>DNP-CD</x:v>
+      </x:c>
+      <x:c r="I36" s="94" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K36" s="95" t="n">
+        <x:f>J36-I36</x:f>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L36" s="95" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="M36" s="95" t="n">
+        <x:f>I36+L36</x:f>
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="N36" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C36,$L$7:$L$37)</x:f>
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="O36" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C36,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="P36" s="95" t="n">
+        <x:f>O36-N36</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q36" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R36" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071585</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="91" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B37" s="91" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C37" s="92" t="n">
+        <x:v>43525.5</x:v>
+      </x:c>
+      <x:c r="D37" s="91" t="str">
+        <x:v>Chicago Bulls</x:v>
+      </x:c>
+      <x:c r="E37" s="91" t="str">
+        <x:v>401071601</x:v>
+      </x:c>
+      <x:c r="F37" s="93" t="str">
+        <x:v>ANDERSON_AVAILABLE</x:v>
+      </x:c>
+      <x:c r="G37" s="93" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="H37" s="93" t="str">
+        <x:v>PLAY</x:v>
+      </x:c>
+      <x:c r="I37" s="94" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J37" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K37" s="95" t="n">
+        <x:f>J37-I37</x:f>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="L37" s="95" t="n">
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="M37" s="95" t="n">
+        <x:f>I37+L37</x:f>
+        <x:v>7.9</x:v>
+      </x:c>
+      <x:c r="N37" s="95" t="n">
+        <x:f>SUMIF($C$7:$C$37,C37,$L$7:$L$37)</x:f>
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="O37" s="95" t="n">
+        <x:f>SUMIF('Game Ledger'!$B$6:$B$87,C37,'Game Ledger'!$T$6:$T$87)</x:f>
+        <x:v>2.9</x:v>
+      </x:c>
+      <x:c r="P37" s="95" t="n">
+        <x:f>O37-N37</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q37" s="91" t="str">
+        <x:v>S44/S45</x:v>
+      </x:c>
+      <x:c r="R37" s="91" t="str">
+        <x:v>https://www.espn.com/nba/boxscore/_/gameId/401071601</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="90"/>
+      <x:c r="B38" s="90"/>
+      <x:c r="C38" s="90"/>
+      <x:c r="D38" s="90"/>
+      <x:c r="E38" s="90"/>
+      <x:c r="F38" s="90"/>
+      <x:c r="G38" s="90"/>
+      <x:c r="H38" s="90"/>
+      <x:c r="I38" s="90"/>
+      <x:c r="J38" s="90"/>
+      <x:c r="K38" s="90"/>
+      <x:c r="L38" s="90"/>
+      <x:c r="M38" s="90"/>
+      <x:c r="N38" s="90"/>
+      <x:c r="O38" s="90"/>
+      <x:c r="P38" s="90"/>
+      <x:c r="Q38" s="90"/>
+      <x:c r="R38" s="90"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="90"/>
+      <x:c r="B39" s="90"/>
+      <x:c r="C39" s="90"/>
+      <x:c r="D39" s="90"/>
+      <x:c r="E39" s="90"/>
+      <x:c r="F39" s="90"/>
+      <x:c r="G39" s="90"/>
+      <x:c r="H39" s="90"/>
+      <x:c r="I39" s="90"/>
+      <x:c r="J39" s="90"/>
+      <x:c r="K39" s="90"/>
+      <x:c r="L39" s="90"/>
+      <x:c r="M39" s="90"/>
+      <x:c r="N39" s="90"/>
+      <x:c r="O39" s="90"/>
+      <x:c r="P39" s="90"/>
+      <x:c r="Q39" s="90"/>
+      <x:c r="R39" s="90"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="87" t="str">
+        <x:v>SEASON RECEIVER SUMMARY — cap = actual 2018-19 observed single-game high; added GP counts DNP-CD dates converted to appearances</x:v>
+      </x:c>
+      <x:c r="B40" s="87"/>
+      <x:c r="C40" s="87"/>
+      <x:c r="D40" s="87"/>
+      <x:c r="E40" s="87"/>
+      <x:c r="F40" s="87"/>
+      <x:c r="G40" s="87"/>
+      <x:c r="H40" s="87"/>
+      <x:c r="I40" s="87"/>
+      <x:c r="J40" s="87"/>
+      <x:c r="K40" s="90"/>
+      <x:c r="L40" s="90"/>
+      <x:c r="M40" s="90"/>
+      <x:c r="N40" s="90"/>
+      <x:c r="O40" s="90"/>
+      <x:c r="P40" s="90"/>
+      <x:c r="Q40" s="90"/>
+      <x:c r="R40" s="90"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="90"/>
+      <x:c r="B41" s="90"/>
+      <x:c r="C41" s="90"/>
+      <x:c r="D41" s="90"/>
+      <x:c r="E41" s="90"/>
+      <x:c r="F41" s="90"/>
+      <x:c r="G41" s="90"/>
+      <x:c r="H41" s="90"/>
+      <x:c r="I41" s="90"/>
+      <x:c r="J41" s="90"/>
+      <x:c r="K41" s="90"/>
+      <x:c r="L41" s="90"/>
+      <x:c r="M41" s="90"/>
+      <x:c r="N41" s="90"/>
+      <x:c r="O41" s="90"/>
+      <x:c r="P41" s="90"/>
+      <x:c r="Q41" s="90"/>
+      <x:c r="R41" s="90"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="51" t="str">
+        <x:v>Receiver</x:v>
+      </x:c>
+      <x:c r="B42" s="51" t="str">
+        <x:v>Pos</x:v>
+      </x:c>
+      <x:c r="C42" s="51" t="str">
+        <x:v>Actual GP</x:v>
+      </x:c>
+      <x:c r="D42" s="51" t="str">
+        <x:v>Actual MIN</x:v>
+      </x:c>
+      <x:c r="E42" s="51" t="str">
+        <x:v>Observed max</x:v>
+      </x:c>
+      <x:c r="F42" s="51" t="str">
+        <x:v>Allocated</x:v>
+      </x:c>
+      <x:c r="G42" s="51" t="str">
+        <x:v>Added GP</x:v>
+      </x:c>
+      <x:c r="H42" s="51" t="str">
+        <x:v>CF GP</x:v>
+      </x:c>
+      <x:c r="I42" s="51" t="str">
+        <x:v>CF MIN</x:v>
+      </x:c>
+      <x:c r="J42" s="51" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="K42" s="90"/>
+      <x:c r="L42" s="90"/>
+      <x:c r="M42" s="90"/>
+      <x:c r="N42" s="90"/>
+      <x:c r="O42" s="90"/>
+      <x:c r="P42" s="90"/>
+      <x:c r="Q42" s="90"/>
+      <x:c r="R42" s="90"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="91" t="str">
+        <x:v>Justin Anderson</x:v>
+      </x:c>
+      <x:c r="B43" s="91" t="str">
+        <x:v>SF</x:v>
+      </x:c>
+      <x:c r="C43" s="91" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D43" s="94" t="n">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="E43" s="94" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F43" s="95" t="n">
+        <x:f>SUMIF($G$7:$G$37,A43,$L$7:$L$37)</x:f>
+        <x:v>105.60000000000001</x:v>
+      </x:c>
+      <x:c r="G43" s="95" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H43" s="95" t="n">
+        <x:f>C43+G43</x:f>
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I43" s="95" t="n">
+        <x:f>D43+F43</x:f>
+        <x:v>568.6</x:v>
+      </x:c>
+      <x:c r="J43" s="91" t="str">
+        <x:v>S04/S44/S45</x:v>
+      </x:c>
+      <x:c r="K43" s="90"/>
+      <x:c r="L43" s="90"/>
+      <x:c r="M43" s="90"/>
+      <x:c r="N43" s="90"/>
+      <x:c r="O43" s="90"/>
+      <x:c r="P43" s="90"/>
+      <x:c r="Q43" s="90"/>
+      <x:c r="R43" s="90"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="91" t="str">
+        <x:v>Alex Poythress</x:v>
+      </x:c>
+      <x:c r="B44" s="91" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="C44" s="91" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D44" s="94" t="n">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="E44" s="94" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F44" s="95" t="n">
+        <x:f>SUMIF($G$7:$G$37,A44,$L$7:$L$37)</x:f>
+        <x:v>48.6</x:v>
+      </x:c>
+      <x:c r="G44" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H44" s="95" t="n">
+        <x:f>C44+G44</x:f>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I44" s="95" t="n">
+        <x:f>D44+F44</x:f>
+        <x:v>353.6</x:v>
+      </x:c>
+      <x:c r="J44" s="91" t="str">
+        <x:v>S04/S44/S46</x:v>
+      </x:c>
+      <x:c r="K44" s="90"/>
+      <x:c r="L44" s="90"/>
+      <x:c r="M44" s="90"/>
+      <x:c r="N44" s="90"/>
+      <x:c r="O44" s="90"/>
+      <x:c r="P44" s="90"/>
+      <x:c r="Q44" s="90"/>
+      <x:c r="R44" s="90"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="91" t="str">
+        <x:v>Daniel Hamilton</x:v>
+      </x:c>
+      <x:c r="B45" s="91" t="str">
+        <x:v>G-F</x:v>
+      </x:c>
+      <x:c r="C45" s="91" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D45" s="94" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="E45" s="94" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F45" s="95" t="n">
+        <x:f>SUMIF($G$7:$G$37,A45,$L$7:$L$37)</x:f>
+        <x:v>11.399999999999999</x:v>
+      </x:c>
+      <x:c r="G45" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H45" s="95" t="n">
+        <x:f>C45+G45</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I45" s="95" t="n">
+        <x:f>D45+F45</x:f>
+        <x:v>215.4</x:v>
+      </x:c>
+      <x:c r="J45" s="91" t="str">
+        <x:v>S04/S44</x:v>
+      </x:c>
+      <x:c r="K45" s="90"/>
+      <x:c r="L45" s="90"/>
+      <x:c r="M45" s="90"/>
+      <x:c r="N45" s="90"/>
+      <x:c r="O45" s="90"/>
+      <x:c r="P45" s="90"/>
+      <x:c r="Q45" s="90"/>
+      <x:c r="R45" s="90"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="91" t="str">
+        <x:v>Miles Plumlee</x:v>
+      </x:c>
+      <x:c r="B46" s="91" t="str">
+        <x:v>F-C</x:v>
+      </x:c>
+      <x:c r="C46" s="91" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D46" s="94" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="E46" s="94" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F46" s="95" t="n">
+        <x:f>SUMIF($G$7:$G$37,A46,$L$7:$L$37)</x:f>
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="G46" s="95" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H46" s="95" t="n">
+        <x:f>C46+G46</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I46" s="95" t="n">
+        <x:f>D46+F46</x:f>
+        <x:v>190.5</x:v>
+      </x:c>
+      <x:c r="J46" s="91" t="str">
+        <x:v>S04/S44</x:v>
+      </x:c>
+      <x:c r="K46" s="90"/>
+      <x:c r="L46" s="90"/>
+      <x:c r="M46" s="90"/>
+      <x:c r="N46" s="90"/>
+      <x:c r="O46" s="90"/>
+      <x:c r="P46" s="90"/>
+      <x:c r="Q46" s="90"/>
+      <x:c r="R46" s="90"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="91" t="str">
+        <x:v>B.J. Johnson</x:v>
+      </x:c>
+      <x:c r="B47" s="91" t="str">
+        <x:v>SF</x:v>
+      </x:c>
+      <x:c r="C47" s="91" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D47" s="94" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E47" s="94" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F47" s="95" t="n">
+        <x:f>SUMIF($G$7:$G$37,A47,$L$7:$L$37)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G47" s="95" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H47" s="95" t="n">
+        <x:f>C47+G47</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I47" s="95" t="n">
+        <x:f>D47+F47</x:f>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J47" s="91" t="str">
+        <x:v>S04/S44</x:v>
+      </x:c>
+      <x:c r="K47" s="90"/>
+      <x:c r="L47" s="90"/>
+      <x:c r="M47" s="90"/>
+      <x:c r="N47" s="90"/>
+      <x:c r="O47" s="90"/>
+      <x:c r="P47" s="90"/>
+      <x:c r="Q47" s="90"/>
+      <x:c r="R47" s="90"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="90"/>
+      <x:c r="B48" s="90"/>
+      <x:c r="C48" s="90"/>
+      <x:c r="D48" s="90"/>
+      <x:c r="E48" s="90"/>
+      <x:c r="F48" s="90"/>
+      <x:c r="G48" s="90"/>
+      <x:c r="H48" s="90"/>
+      <x:c r="I48" s="90"/>
+      <x:c r="J48" s="90"/>
+      <x:c r="K48" s="90"/>
+      <x:c r="L48" s="90"/>
+      <x:c r="M48" s="90"/>
+      <x:c r="N48" s="90"/>
+      <x:c r="O48" s="90"/>
+      <x:c r="P48" s="90"/>
+      <x:c r="Q48" s="90"/>
+      <x:c r="R48" s="90"/>
+    </x:row>
+    <x:row r="49" ht="32" customHeight="1">
+      <x:c r="A49" s="87" t="str">
+        <x:v>TOTAL</x:v>
+      </x:c>
+      <x:c r="B49" s="87"/>
+      <x:c r="C49" s="87"/>
+      <x:c r="D49" s="87"/>
+      <x:c r="E49" s="87"/>
+      <x:c r="F49" s="88" t="n">
+        <x:f>SUM(F43:F47)</x:f>
+        <x:v>183.10000000000002</x:v>
+      </x:c>
+      <x:c r="G49" s="88"/>
+      <x:c r="H49" s="88"/>
+      <x:c r="I49" s="88" t="n">
+        <x:f>SUM(I43:I47)</x:f>
+        <x:v>1371.1000000000001</x:v>
+      </x:c>
+      <x:c r="J49" s="87" t="str">
+        <x:v>B.J. Johnson audited at zero: his only overlapping residual date (Mar. 1) already has Anderson available.</x:v>
+      </x:c>
+      <x:c r="K49" s="96"/>
+      <x:c r="L49" s="96"/>
+      <x:c r="M49" s="96"/>
+      <x:c r="N49" s="96"/>
+      <x:c r="O49" s="96"/>
+      <x:c r="P49" s="96"/>
+      <x:c r="Q49" s="96"/>
+      <x:c r="R49" s="96"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:R2"/>
+    <x:mergeCell ref="A40:J40"/>
+    <x:mergeCell ref="J49:R49"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="2">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bc187f26d61418c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1657639e7f5d4742"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="31" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
@@ -9358,7 +12223,7 @@
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="73" t="str">
+      <x:c r="A3" s="97" t="str">
         <x:v>Published integer player minutes sum two minutes below game capacity because of source rounding. Allow the two-minute audit delta; never spend it as new minutes.</x:v>
       </x:c>
     </x:row>
@@ -9878,18 +12743,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I17" s="48" t="n">
-        <x:v>0</x:v>
+        <x:f>SUMIF('ATL Receivers'!$G$7:$G$37,A17,'ATL Receivers'!$L$7:$L$37)</x:f>
+        <x:v>105.60000000000001</x:v>
       </x:c>
       <x:c r="J17" s="49" t="n">
         <x:f>E17-H17+I17</x:f>
-        <x:v>463</x:v>
+        <x:v>568.6</x:v>
       </x:c>
       <x:c r="K17" s="49" t="n">
         <x:f>J17-(E17-H17+I17)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L17" s="38" t="str">
-        <x:v>S04</x:v>
+        <x:v>S04/S44/S45</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -9960,18 +12826,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I19" s="48" t="n">
-        <x:v>0</x:v>
+        <x:f>SUMIF('ATL Receivers'!$G$7:$G$37,A19,'ATL Receivers'!$L$7:$L$37)</x:f>
+        <x:v>48.6</x:v>
       </x:c>
       <x:c r="J19" s="49" t="n">
         <x:f>E19-H19+I19</x:f>
-        <x:v>305</x:v>
+        <x:v>353.6</x:v>
       </x:c>
       <x:c r="K19" s="49" t="n">
         <x:f>J19-(E19-H19+I19)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L19" s="38" t="str">
-        <x:v>S04</x:v>
+        <x:v>S04/S44/S46</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -10042,18 +12909,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I21" s="48" t="n">
-        <x:v>0</x:v>
+        <x:f>SUMIF('ATL Receivers'!$G$7:$G$37,A21,'ATL Receivers'!$L$7:$L$37)</x:f>
+        <x:v>11.399999999999999</x:v>
       </x:c>
       <x:c r="J21" s="49" t="n">
         <x:f>E21-H21+I21</x:f>
-        <x:v>204</x:v>
+        <x:v>215.4</x:v>
       </x:c>
       <x:c r="K21" s="49" t="n">
         <x:f>J21-(E21-H21+I21)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L21" s="38" t="str">
-        <x:v>S04</x:v>
+        <x:v>S04/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -10083,18 +12951,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I22" s="48" t="n">
-        <x:v>0</x:v>
+        <x:f>SUMIF('ATL Receivers'!$G$7:$G$37,A22,'ATL Receivers'!$L$7:$L$37)</x:f>
+        <x:v>17.5</x:v>
       </x:c>
       <x:c r="J22" s="49" t="n">
         <x:f>E22-H22+I22</x:f>
-        <x:v>173</x:v>
+        <x:v>190.5</x:v>
       </x:c>
       <x:c r="K22" s="49" t="n">
         <x:f>J22-(E22-H22+I22)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L22" s="38" t="str">
-        <x:v>S04</x:v>
+        <x:v>S04/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -10206,6 +13075,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I25" s="48" t="n">
+        <x:f>SUMIF('ATL Receivers'!$G$7:$G$37,A25,'ATL Receivers'!$L$7:$L$37)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J25" s="49" t="n">
@@ -10217,7 +13087,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L25" s="38" t="str">
-        <x:v>S04</x:v>
+        <x:v>S04/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -10365,25 +13235,25 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G29" s="38" t="str">
-        <x:v>ACCOUNTING_BRIDGE</x:v>
+        <x:v>RESOLVED_ACCOUNTING_BRIDGE</x:v>
       </x:c>
       <x:c r="H29" s="48" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I29" s="48" t="n">
-        <x:f>SUM('Game Ledger'!$T$6:$T$87)</x:f>
-        <x:v>183.10000000000002</x:v>
+        <x:f>SUM('Game Ledger'!$T$6:$T$87)-SUM('ATL Receivers'!$L$7:$L$37)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J29" s="49" t="n">
         <x:f>E29-H29+I29</x:f>
-        <x:v>183.10000000000002</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K29" s="49" t="n">
         <x:f>J29-(E29-H29+I29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L29" s="38" t="str">
-        <x:v>S40</x:v>
+        <x:v>S40/S44</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -10418,30 +13288,30 @@
       <x:c r="L31" s="6"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="74" t="str">
+      <x:c r="A33" s="77" t="str">
         <x:v>Primary rule</x:v>
       </x:c>
-      <x:c r="B33" s="74" t="str">
+      <x:c r="B33" s="77" t="str">
         <x:v>Donor ≥7.0; cap 16.0</x:v>
       </x:c>
-      <x:c r="C33" s="74"/>
-      <x:c r="D33" s="74" t="str">
+      <x:c r="C33" s="77"/>
+      <x:c r="D33" s="77" t="str">
         <x:v>Exact NBA line</x:v>
       </x:c>
-      <x:c r="E33" s="74" t="str">
+      <x:c r="E33" s="77" t="str">
         <x:v>43 GP / 621.9 MIN / 14.46 MPG</x:v>
       </x:c>
-      <x:c r="F33" s="74"/>
-      <x:c r="G33" s="74"/>
-      <x:c r="H33" s="74" t="str">
-        <x:v>Bridge</x:v>
-      </x:c>
-      <x:c r="I33" s="74" t="str">
-        <x:v>183.1 min ATL remainder pool</x:v>
-      </x:c>
-      <x:c r="J33" s="74"/>
-      <x:c r="K33" s="74"/>
-      <x:c r="L33" s="74"/>
+      <x:c r="F33" s="77"/>
+      <x:c r="G33" s="77"/>
+      <x:c r="H33" s="77" t="str">
+        <x:v>Named receivers</x:v>
+      </x:c>
+      <x:c r="I33" s="77" t="str">
+        <x:v>183.1 min / 4 players / 0 unresolved</x:v>
+      </x:c>
+      <x:c r="J33" s="77"/>
+      <x:c r="K33" s="77"/>
+      <x:c r="L33" s="77"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -10453,12 +13323,12 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfad03ea34c6a4b0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redd6eb4b56ec4def"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -10506,7 +13376,7 @@
         <x:v>Next blocker</x:v>
       </x:c>
       <x:c r="H4" s="6" t="str">
-        <x:v>ATL remainder recipients</x:v>
+        <x:v>ATL production / outcome prior</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -10545,1087 +13415,1087 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="77" t="n">
+      <x:c r="A7" s="84" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B7" s="77" t="str">
+      <x:c r="B7" s="84" t="str">
         <x:v>Atlanta Hawks</x:v>
       </x:c>
-      <x:c r="C7" s="77" t="str">
+      <x:c r="C7" s="84" t="str">
         <x:v>Omari Spellman</x:v>
       </x:c>
-      <x:c r="D7" s="77" t="str">
+      <x:c r="D7" s="84" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E7" s="77" t="str">
+      <x:c r="E7" s="84" t="str">
         <x:v>Atlanta Hawks</x:v>
       </x:c>
-      <x:c r="F7" s="77" t="str">
+      <x:c r="F7" s="84" t="str">
         <x:v>Fictional protagonist</x:v>
       </x:c>
-      <x:c r="G7" s="77" t="str">
+      <x:c r="G7" s="84" t="str">
         <x:v>CHANGED</x:v>
       </x:c>
-      <x:c r="H7" s="77" t="str">
+      <x:c r="H7" s="84" t="str">
         <x:v>Protagonist</x:v>
       </x:c>
-      <x:c r="I7" s="77" t="str">
+      <x:c r="I7" s="84" t="str">
         <x:v>The new player occupies Atlanta's actual #30 slot.</x:v>
       </x:c>
-      <x:c r="J7" s="77" t="str">
+      <x:c r="J7" s="84" t="str">
         <x:v>Atlanta roster/minutes rerun</x:v>
       </x:c>
-      <x:c r="K7" s="77" t="str">
+      <x:c r="K7" s="84" t="str">
         <x:v>S12/S13</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="75" t="n">
+      <x:c r="A8" s="82" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B8" s="75" t="str">
+      <x:c r="B8" s="82" t="str">
         <x:v>Phoenix Suns</x:v>
       </x:c>
-      <x:c r="C8" s="75" t="str">
+      <x:c r="C8" s="82" t="str">
         <x:v>Elie Okobo</x:v>
       </x:c>
-      <x:c r="D8" s="75" t="str">
+      <x:c r="D8" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E8" s="75" t="str">
+      <x:c r="E8" s="82" t="str">
         <x:v>Phoenix Suns</x:v>
       </x:c>
-      <x:c r="F8" s="75" t="str">
+      <x:c r="F8" s="82" t="str">
         <x:v>Elie Okobo</x:v>
       </x:c>
-      <x:c r="G8" s="76" t="str">
+      <x:c r="G8" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H8" s="75" t="str">
+      <x:c r="H8" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I8" s="75" t="str">
+      <x:c r="I8" s="82" t="str">
         <x:v>Guard-development choice remains rational.</x:v>
       </x:c>
-      <x:c r="J8" s="75" t="str">
+      <x:c r="J8" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K8" s="75" t="str">
+      <x:c r="K8" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="75" t="n">
+      <x:c r="A9" s="82" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B9" s="75" t="str">
+      <x:c r="B9" s="82" t="str">
         <x:v>Memphis Grizzlies</x:v>
       </x:c>
-      <x:c r="C9" s="75" t="str">
+      <x:c r="C9" s="82" t="str">
         <x:v>Jevon Carter</x:v>
       </x:c>
-      <x:c r="D9" s="75" t="str">
+      <x:c r="D9" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E9" s="75" t="str">
+      <x:c r="E9" s="82" t="str">
         <x:v>Memphis Grizzlies</x:v>
       </x:c>
-      <x:c r="F9" s="75" t="str">
+      <x:c r="F9" s="82" t="str">
         <x:v>Jevon Carter</x:v>
       </x:c>
-      <x:c r="G9" s="76" t="str">
+      <x:c r="G9" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H9" s="75" t="str">
+      <x:c r="H9" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I9" s="75" t="str">
+      <x:c r="I9" s="82" t="str">
         <x:v>Point-of-attack guard need remains distinct.</x:v>
       </x:c>
-      <x:c r="J9" s="75" t="str">
+      <x:c r="J9" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K9" s="75" t="str">
+      <x:c r="K9" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="75" t="n">
+      <x:c r="A10" s="82" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B10" s="75" t="str">
+      <x:c r="B10" s="82" t="str">
         <x:v>Dallas Mavericks</x:v>
       </x:c>
-      <x:c r="C10" s="75" t="str">
+      <x:c r="C10" s="82" t="str">
         <x:v>Jalen Brunson</x:v>
       </x:c>
-      <x:c r="D10" s="75" t="str">
+      <x:c r="D10" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E10" s="75" t="str">
+      <x:c r="E10" s="82" t="str">
         <x:v>Dallas Mavericks</x:v>
       </x:c>
-      <x:c r="F10" s="75" t="str">
+      <x:c r="F10" s="82" t="str">
         <x:v>Jalen Brunson</x:v>
       </x:c>
-      <x:c r="G10" s="76" t="str">
+      <x:c r="G10" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H10" s="75" t="str">
+      <x:c r="H10" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I10" s="75" t="str">
+      <x:c r="I10" s="82" t="str">
         <x:v>Lead-guard depth remains the stronger fit.</x:v>
       </x:c>
-      <x:c r="J10" s="75" t="str">
+      <x:c r="J10" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K10" s="75" t="str">
+      <x:c r="K10" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="75" t="n">
+      <x:c r="A11" s="82" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B11" s="75" t="str">
+      <x:c r="B11" s="82" t="str">
         <x:v>Charlotte Hornets</x:v>
       </x:c>
-      <x:c r="C11" s="75" t="str">
+      <x:c r="C11" s="82" t="str">
         <x:v>Devonte' Graham</x:v>
       </x:c>
-      <x:c r="D11" s="75" t="str">
+      <x:c r="D11" s="82" t="str">
         <x:v>Rights from ATL for 2019 + 2023 seconds</x:v>
       </x:c>
-      <x:c r="E11" s="75" t="str">
+      <x:c r="E11" s="82" t="str">
         <x:v>Charlotte Hornets</x:v>
       </x:c>
-      <x:c r="F11" s="75" t="str">
+      <x:c r="F11" s="82" t="str">
         <x:v>Devonte' Graham</x:v>
       </x:c>
-      <x:c r="G11" s="76" t="str">
+      <x:c r="G11" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H11" s="75" t="str">
+      <x:c r="H11" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I11" s="75" t="str">
+      <x:c r="I11" s="82" t="str">
         <x:v>Charlotte paid two future seconds for a directed guard choice.</x:v>
       </x:c>
-      <x:c r="J11" s="75" t="str">
+      <x:c r="J11" s="82" t="str">
         <x:v>ATL asset trade preserved</x:v>
       </x:c>
-      <x:c r="K11" s="75" t="str">
+      <x:c r="K11" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="75" t="n">
+      <x:c r="A12" s="82" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="B12" s="75" t="str">
+      <x:c r="B12" s="82" t="str">
         <x:v>Orlando Magic</x:v>
       </x:c>
-      <x:c r="C12" s="75" t="str">
+      <x:c r="C12" s="82" t="str">
         <x:v>Melvin Frazier</x:v>
       </x:c>
-      <x:c r="D12" s="75" t="str">
+      <x:c r="D12" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E12" s="75" t="str">
+      <x:c r="E12" s="82" t="str">
         <x:v>Orlando Magic</x:v>
       </x:c>
-      <x:c r="F12" s="75" t="str">
+      <x:c r="F12" s="82" t="str">
         <x:v>Melvin Frazier</x:v>
       </x:c>
-      <x:c r="G12" s="76" t="str">
+      <x:c r="G12" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H12" s="75" t="str">
+      <x:c r="H12" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I12" s="75" t="str">
+      <x:c r="I12" s="82" t="str">
         <x:v>Wing-development lane remains distinct.</x:v>
       </x:c>
-      <x:c r="J12" s="75" t="str">
+      <x:c r="J12" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K12" s="75" t="str">
+      <x:c r="K12" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="75" t="n">
+      <x:c r="A13" s="82" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="B13" s="75" t="str">
+      <x:c r="B13" s="82" t="str">
         <x:v>New York Knicks</x:v>
       </x:c>
-      <x:c r="C13" s="75" t="str">
+      <x:c r="C13" s="82" t="str">
         <x:v>Mitchell Robinson</x:v>
       </x:c>
-      <x:c r="D13" s="75" t="str">
+      <x:c r="D13" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E13" s="75" t="str">
+      <x:c r="E13" s="82" t="str">
         <x:v>New York Knicks</x:v>
       </x:c>
-      <x:c r="F13" s="75" t="str">
+      <x:c r="F13" s="82" t="str">
         <x:v>Mitchell Robinson</x:v>
       </x:c>
-      <x:c r="G13" s="76" t="str">
+      <x:c r="G13" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H13" s="75" t="str">
+      <x:c r="H13" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I13" s="75" t="str">
+      <x:c r="I13" s="82" t="str">
         <x:v>Robinson's upside remains the board priority.</x:v>
       </x:c>
-      <x:c r="J13" s="75" t="str">
+      <x:c r="J13" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K13" s="75" t="str">
+      <x:c r="K13" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="75" t="n">
+      <x:c r="A14" s="82" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B14" s="75" t="str">
+      <x:c r="B14" s="82" t="str">
         <x:v>Portland Trail Blazers</x:v>
       </x:c>
-      <x:c r="C14" s="75" t="str">
+      <x:c r="C14" s="82" t="str">
         <x:v>Gary Trent Jr.</x:v>
       </x:c>
-      <x:c r="D14" s="75" t="str">
+      <x:c r="D14" s="82" t="str">
         <x:v>Rights from SAC</x:v>
       </x:c>
-      <x:c r="E14" s="75" t="str">
+      <x:c r="E14" s="82" t="str">
         <x:v>Portland Trail Blazers</x:v>
       </x:c>
-      <x:c r="F14" s="75" t="str">
+      <x:c r="F14" s="82" t="str">
         <x:v>Gary Trent Jr.</x:v>
       </x:c>
-      <x:c r="G14" s="76" t="str">
+      <x:c r="G14" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H14" s="75" t="str">
+      <x:c r="H14" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I14" s="75" t="str">
+      <x:c r="I14" s="82" t="str">
         <x:v>Perimeter shooting/development need remains.</x:v>
       </x:c>
-      <x:c r="J14" s="75" t="str">
+      <x:c r="J14" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K14" s="75" t="str">
+      <x:c r="K14" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="75" t="n">
+      <x:c r="A15" s="82" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B15" s="75" t="str">
+      <x:c r="B15" s="82" t="str">
         <x:v>Detroit Pistons</x:v>
       </x:c>
-      <x:c r="C15" s="75" t="str">
+      <x:c r="C15" s="82" t="str">
         <x:v>Khyri Thomas</x:v>
       </x:c>
-      <x:c r="D15" s="75" t="str">
+      <x:c r="D15" s="82" t="str">
         <x:v>Rights from PHI</x:v>
       </x:c>
-      <x:c r="E15" s="75" t="str">
+      <x:c r="E15" s="82" t="str">
         <x:v>Detroit Pistons</x:v>
       </x:c>
-      <x:c r="F15" s="75" t="str">
+      <x:c r="F15" s="82" t="str">
         <x:v>Khyri Thomas</x:v>
       </x:c>
-      <x:c r="G15" s="76" t="str">
+      <x:c r="G15" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H15" s="75" t="str">
+      <x:c r="H15" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I15" s="75" t="str">
+      <x:c r="I15" s="82" t="str">
         <x:v>Perimeter defense need remains distinct.</x:v>
       </x:c>
-      <x:c r="J15" s="75" t="str">
+      <x:c r="J15" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K15" s="75" t="str">
+      <x:c r="K15" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="75" t="n">
+      <x:c r="A16" s="82" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B16" s="75" t="str">
+      <x:c r="B16" s="82" t="str">
         <x:v>Los Angeles Lakers</x:v>
       </x:c>
-      <x:c r="C16" s="75" t="str">
+      <x:c r="C16" s="82" t="str">
         <x:v>Isaac Bonga</x:v>
       </x:c>
-      <x:c r="D16" s="75" t="str">
+      <x:c r="D16" s="82" t="str">
         <x:v>Rights from PHI</x:v>
       </x:c>
-      <x:c r="E16" s="75" t="str">
+      <x:c r="E16" s="82" t="str">
         <x:v>Los Angeles Lakers</x:v>
       </x:c>
-      <x:c r="F16" s="75" t="str">
+      <x:c r="F16" s="82" t="str">
         <x:v>Isaac Bonga</x:v>
       </x:c>
-      <x:c r="G16" s="76" t="str">
+      <x:c r="G16" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H16" s="75" t="str">
+      <x:c r="H16" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I16" s="75" t="str">
+      <x:c r="I16" s="82" t="str">
         <x:v>Lakers already used #25 on stretch big Moritz Wagner.</x:v>
       </x:c>
-      <x:c r="J16" s="75" t="str">
+      <x:c r="J16" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K16" s="75" t="str">
+      <x:c r="K16" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="75" t="n">
+      <x:c r="A17" s="82" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B17" s="75" t="str">
+      <x:c r="B17" s="82" t="str">
         <x:v>Brooklyn Nets</x:v>
       </x:c>
-      <x:c r="C17" s="75" t="str">
+      <x:c r="C17" s="82" t="str">
         <x:v>Rodions Kurucs</x:v>
       </x:c>
-      <x:c r="D17" s="75" t="str">
+      <x:c r="D17" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E17" s="75" t="str">
+      <x:c r="E17" s="82" t="str">
         <x:v>Brooklyn Nets</x:v>
       </x:c>
-      <x:c r="F17" s="75" t="str">
+      <x:c r="F17" s="82" t="str">
         <x:v>Rodions Kurucs</x:v>
       </x:c>
-      <x:c r="G17" s="76" t="str">
+      <x:c r="G17" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H17" s="75" t="str">
+      <x:c r="H17" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I17" s="75" t="str">
+      <x:c r="I17" s="82" t="str">
         <x:v>Long-running Kurucs scouting interest remains decisive.</x:v>
       </x:c>
-      <x:c r="J17" s="75" t="str">
+      <x:c r="J17" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K17" s="75" t="str">
+      <x:c r="K17" s="82" t="str">
         <x:v>S17</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="75" t="n">
+      <x:c r="A18" s="82" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B18" s="75" t="str">
+      <x:c r="B18" s="82" t="str">
         <x:v>Denver Nuggets</x:v>
       </x:c>
-      <x:c r="C18" s="75" t="str">
+      <x:c r="C18" s="82" t="str">
         <x:v>Jarred Vanderbilt</x:v>
       </x:c>
-      <x:c r="D18" s="75" t="str">
+      <x:c r="D18" s="82" t="str">
         <x:v>Rights from ORL</x:v>
       </x:c>
-      <x:c r="E18" s="75" t="str">
+      <x:c r="E18" s="82" t="str">
         <x:v>Denver Nuggets</x:v>
       </x:c>
-      <x:c r="F18" s="75" t="str">
+      <x:c r="F18" s="82" t="str">
         <x:v>Jarred Vanderbilt</x:v>
       </x:c>
-      <x:c r="G18" s="76" t="str">
+      <x:c r="G18" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H18" s="75" t="str">
+      <x:c r="H18" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I18" s="75" t="str">
+      <x:c r="I18" s="82" t="str">
         <x:v>Vanderbilt upside remains the preferred development bet.</x:v>
       </x:c>
-      <x:c r="J18" s="75" t="str">
+      <x:c r="J18" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K18" s="75" t="str">
+      <x:c r="K18" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="75" t="n">
+      <x:c r="A19" s="82" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="B19" s="75" t="str">
+      <x:c r="B19" s="82" t="str">
         <x:v>Detroit Pistons</x:v>
       </x:c>
-      <x:c r="C19" s="75" t="str">
+      <x:c r="C19" s="82" t="str">
         <x:v>Bruce Brown</x:v>
       </x:c>
-      <x:c r="D19" s="75" t="str">
+      <x:c r="D19" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E19" s="75" t="str">
+      <x:c r="E19" s="82" t="str">
         <x:v>Detroit Pistons</x:v>
       </x:c>
-      <x:c r="F19" s="75" t="str">
+      <x:c r="F19" s="82" t="str">
         <x:v>Bruce Brown</x:v>
       </x:c>
-      <x:c r="G19" s="76" t="str">
+      <x:c r="G19" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H19" s="75" t="str">
+      <x:c r="H19" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I19" s="75" t="str">
+      <x:c r="I19" s="82" t="str">
         <x:v>Guard/wing role remains distinct.</x:v>
       </x:c>
-      <x:c r="J19" s="75" t="str">
+      <x:c r="J19" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K19" s="75" t="str">
+      <x:c r="K19" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="75" t="n">
+      <x:c r="A20" s="82" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B20" s="75" t="str">
+      <x:c r="B20" s="82" t="str">
         <x:v>Orlando Magic</x:v>
       </x:c>
-      <x:c r="C20" s="75" t="str">
+      <x:c r="C20" s="82" t="str">
         <x:v>Justin Jackson</x:v>
       </x:c>
-      <x:c r="D20" s="75" t="str">
+      <x:c r="D20" s="82" t="str">
         <x:v>Rights from DEN</x:v>
       </x:c>
-      <x:c r="E20" s="75" t="str">
+      <x:c r="E20" s="82" t="str">
         <x:v>Orlando Magic</x:v>
       </x:c>
-      <x:c r="F20" s="75" t="str">
+      <x:c r="F20" s="82" t="str">
         <x:v>Justin Jackson</x:v>
       </x:c>
-      <x:c r="G20" s="76" t="str">
+      <x:c r="G20" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H20" s="75" t="str">
+      <x:c r="H20" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I20" s="75" t="str">
+      <x:c r="I20" s="82" t="str">
         <x:v>Wing-development lane remains distinct.</x:v>
       </x:c>
-      <x:c r="J20" s="75" t="str">
+      <x:c r="J20" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K20" s="75" t="str">
+      <x:c r="K20" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="75" t="n">
+      <x:c r="A21" s="82" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B21" s="75" t="str">
+      <x:c r="B21" s="82" t="str">
         <x:v>Washington Wizards</x:v>
       </x:c>
-      <x:c r="C21" s="75" t="str">
+      <x:c r="C21" s="82" t="str">
         <x:v>Issuf Sanon</x:v>
       </x:c>
-      <x:c r="D21" s="75" t="str">
+      <x:c r="D21" s="82" t="str">
         <x:v>Own pick; overseas stash</x:v>
       </x:c>
-      <x:c r="E21" s="75" t="str">
+      <x:c r="E21" s="82" t="str">
         <x:v>Washington Wizards</x:v>
       </x:c>
-      <x:c r="F21" s="75" t="str">
+      <x:c r="F21" s="82" t="str">
         <x:v>Issuf Sanon</x:v>
       </x:c>
-      <x:c r="G21" s="76" t="str">
+      <x:c r="G21" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H21" s="75" t="str">
+      <x:c r="H21" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I21" s="75" t="str">
+      <x:c r="I21" s="82" t="str">
         <x:v>Roster/cap plan explicitly favored an overseas stash.</x:v>
       </x:c>
-      <x:c r="J21" s="75" t="str">
+      <x:c r="J21" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K21" s="75" t="str">
+      <x:c r="K21" s="82" t="str">
         <x:v>S16</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="75" t="n">
+      <x:c r="A22" s="82" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B22" s="75" t="str">
+      <x:c r="B22" s="82" t="str">
         <x:v>Oklahoma City Thunder</x:v>
       </x:c>
-      <x:c r="C22" s="75" t="str">
+      <x:c r="C22" s="82" t="str">
         <x:v>Hamidou Diallo</x:v>
       </x:c>
-      <x:c r="D22" s="75" t="str">
+      <x:c r="D22" s="82" t="str">
         <x:v>Rights via BKN/CHA</x:v>
       </x:c>
-      <x:c r="E22" s="75" t="str">
+      <x:c r="E22" s="82" t="str">
         <x:v>Oklahoma City Thunder</x:v>
       </x:c>
-      <x:c r="F22" s="75" t="str">
+      <x:c r="F22" s="82" t="str">
         <x:v>Hamidou Diallo</x:v>
       </x:c>
-      <x:c r="G22" s="76" t="str">
+      <x:c r="G22" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H22" s="75" t="str">
+      <x:c r="H22" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I22" s="75" t="str">
+      <x:c r="I22" s="82" t="str">
         <x:v>Athletic guard target remains distinct.</x:v>
       </x:c>
-      <x:c r="J22" s="75" t="str">
+      <x:c r="J22" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K22" s="75" t="str">
+      <x:c r="K22" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="75" t="n">
+      <x:c r="A23" s="82" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B23" s="75" t="str">
+      <x:c r="B23" s="82" t="str">
         <x:v>Houston Rockets</x:v>
       </x:c>
-      <x:c r="C23" s="75" t="str">
+      <x:c r="C23" s="82" t="str">
         <x:v>De'Anthony Melton</x:v>
       </x:c>
-      <x:c r="D23" s="75" t="str">
+      <x:c r="D23" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E23" s="75" t="str">
+      <x:c r="E23" s="82" t="str">
         <x:v>Houston Rockets</x:v>
       </x:c>
-      <x:c r="F23" s="75" t="str">
+      <x:c r="F23" s="82" t="str">
         <x:v>De'Anthony Melton</x:v>
       </x:c>
-      <x:c r="G23" s="76" t="str">
+      <x:c r="G23" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H23" s="75" t="str">
+      <x:c r="H23" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I23" s="75" t="str">
+      <x:c r="I23" s="82" t="str">
         <x:v>Guard asset profile remains distinct.</x:v>
       </x:c>
-      <x:c r="J23" s="75" t="str">
+      <x:c r="J23" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K23" s="75" t="str">
+      <x:c r="K23" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="75" t="n">
+      <x:c r="A24" s="82" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B24" s="75" t="str">
+      <x:c r="B24" s="82" t="str">
         <x:v>Los Angeles Lakers</x:v>
       </x:c>
-      <x:c r="C24" s="75" t="str">
+      <x:c r="C24" s="82" t="str">
         <x:v>Svi Mykhailiuk</x:v>
       </x:c>
-      <x:c r="D24" s="75" t="str">
+      <x:c r="D24" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E24" s="75" t="str">
+      <x:c r="E24" s="82" t="str">
         <x:v>Los Angeles Lakers</x:v>
       </x:c>
-      <x:c r="F24" s="75" t="str">
+      <x:c r="F24" s="82" t="str">
         <x:v>Svi Mykhailiuk</x:v>
       </x:c>
-      <x:c r="G24" s="76" t="str">
+      <x:c r="G24" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H24" s="75" t="str">
+      <x:c r="H24" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I24" s="75" t="str">
+      <x:c r="I24" s="82" t="str">
         <x:v>Shooting role remains distinct.</x:v>
       </x:c>
-      <x:c r="J24" s="75" t="str">
+      <x:c r="J24" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K24" s="75" t="str">
+      <x:c r="K24" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="75" t="n">
+      <x:c r="A25" s="82" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B25" s="75" t="str">
+      <x:c r="B25" s="82" t="str">
         <x:v>Minnesota Timberwolves</x:v>
       </x:c>
-      <x:c r="C25" s="75" t="str">
+      <x:c r="C25" s="82" t="str">
         <x:v>Keita Bates-Diop</x:v>
       </x:c>
-      <x:c r="D25" s="75" t="str">
+      <x:c r="D25" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E25" s="75" t="str">
+      <x:c r="E25" s="82" t="str">
         <x:v>Minnesota Timberwolves</x:v>
       </x:c>
-      <x:c r="F25" s="75" t="str">
+      <x:c r="F25" s="82" t="str">
         <x:v>Keita Bates-Diop</x:v>
       </x:c>
-      <x:c r="G25" s="76" t="str">
+      <x:c r="G25" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H25" s="75" t="str">
+      <x:c r="H25" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I25" s="75" t="str">
+      <x:c r="I25" s="82" t="str">
         <x:v>Wing-forward choice does not require a cascade.</x:v>
       </x:c>
-      <x:c r="J25" s="75" t="str">
+      <x:c r="J25" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K25" s="75" t="str">
+      <x:c r="K25" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="77" t="n">
+      <x:c r="A26" s="84" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B26" s="77" t="str">
+      <x:c r="B26" s="84" t="str">
         <x:v>San Antonio Spurs</x:v>
       </x:c>
-      <x:c r="C26" s="77" t="str">
+      <x:c r="C26" s="84" t="str">
         <x:v>Chimezie Metu</x:v>
       </x:c>
-      <x:c r="D26" s="77" t="str">
+      <x:c r="D26" s="84" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E26" s="77" t="str">
+      <x:c r="E26" s="84" t="str">
         <x:v>San Antonio Spurs</x:v>
       </x:c>
-      <x:c r="F26" s="77" t="str">
+      <x:c r="F26" s="84" t="str">
         <x:v>Omari Spellman</x:v>
       </x:c>
-      <x:c r="G26" s="77" t="str">
+      <x:c r="G26" s="84" t="str">
         <x:v>CHANGED</x:v>
       </x:c>
-      <x:c r="H26" s="77" t="str">
+      <x:c r="H26" s="84" t="str">
         <x:v>Spellman</x:v>
       </x:c>
-      <x:c r="I26" s="77" t="str">
+      <x:c r="I26" s="84" t="str">
         <x:v>Spellman worked out for San Antonio and fit its spacing/IQ profile.</x:v>
       </x:c>
-      <x:c r="J26" s="77" t="str">
+      <x:c r="J26" s="84" t="str">
         <x:v>Spurs baseline role PASS; outcomes HOLD</x:v>
       </x:c>
-      <x:c r="K26" s="77" t="str">
+      <x:c r="K26" s="84" t="str">
         <x:v>S14/S15/S22</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="75" t="n">
+      <x:c r="A27" s="82" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B27" s="75" t="str">
+      <x:c r="B27" s="82" t="str">
         <x:v>Indiana Pacers</x:v>
       </x:c>
-      <x:c r="C27" s="75" t="str">
+      <x:c r="C27" s="82" t="str">
         <x:v>Alize Johnson</x:v>
       </x:c>
-      <x:c r="D27" s="75" t="str">
+      <x:c r="D27" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E27" s="75" t="str">
+      <x:c r="E27" s="82" t="str">
         <x:v>Indiana Pacers</x:v>
       </x:c>
-      <x:c r="F27" s="75" t="str">
+      <x:c r="F27" s="82" t="str">
         <x:v>Alize Johnson</x:v>
       </x:c>
-      <x:c r="G27" s="76" t="str">
+      <x:c r="G27" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H27" s="75" t="str">
+      <x:c r="H27" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I27" s="75" t="str">
+      <x:c r="I27" s="82" t="str">
         <x:v>Actual forward choice remains available.</x:v>
       </x:c>
-      <x:c r="J27" s="75" t="str">
+      <x:c r="J27" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K27" s="75" t="str">
+      <x:c r="K27" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="75" t="n">
+      <x:c r="A28" s="82" t="n">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B28" s="75" t="str">
+      <x:c r="B28" s="82" t="str">
         <x:v>New Orleans Pelicans</x:v>
       </x:c>
-      <x:c r="C28" s="75" t="str">
+      <x:c r="C28" s="82" t="str">
         <x:v>Tony Carr</x:v>
       </x:c>
-      <x:c r="D28" s="75" t="str">
+      <x:c r="D28" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E28" s="75" t="str">
+      <x:c r="E28" s="82" t="str">
         <x:v>New Orleans Pelicans</x:v>
       </x:c>
-      <x:c r="F28" s="75" t="str">
+      <x:c r="F28" s="82" t="str">
         <x:v>Tony Carr</x:v>
       </x:c>
-      <x:c r="G28" s="76" t="str">
+      <x:c r="G28" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H28" s="75" t="str">
+      <x:c r="H28" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I28" s="75" t="str">
+      <x:c r="I28" s="82" t="str">
         <x:v>Guard-development choice remains distinct.</x:v>
       </x:c>
-      <x:c r="J28" s="75" t="str">
+      <x:c r="J28" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K28" s="75" t="str">
+      <x:c r="K28" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="75" t="n">
+      <x:c r="A29" s="82" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B29" s="75" t="str">
+      <x:c r="B29" s="82" t="str">
         <x:v>Houston Rockets</x:v>
       </x:c>
-      <x:c r="C29" s="75" t="str">
+      <x:c r="C29" s="82" t="str">
         <x:v>Vincent Edwards</x:v>
       </x:c>
-      <x:c r="D29" s="75" t="str">
+      <x:c r="D29" s="82" t="str">
         <x:v>Rights from UTA</x:v>
       </x:c>
-      <x:c r="E29" s="75" t="str">
+      <x:c r="E29" s="82" t="str">
         <x:v>Houston Rockets</x:v>
       </x:c>
-      <x:c r="F29" s="75" t="str">
+      <x:c r="F29" s="82" t="str">
         <x:v>Vincent Edwards</x:v>
       </x:c>
-      <x:c r="G29" s="76" t="str">
+      <x:c r="G29" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H29" s="75" t="str">
+      <x:c r="H29" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I29" s="75" t="str">
+      <x:c r="I29" s="82" t="str">
         <x:v>Wing-development choice remains distinct.</x:v>
       </x:c>
-      <x:c r="J29" s="75" t="str">
+      <x:c r="J29" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K29" s="75" t="str">
+      <x:c r="K29" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="75" t="n">
+      <x:c r="A30" s="82" t="n">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B30" s="75" t="str">
+      <x:c r="B30" s="82" t="str">
         <x:v>Oklahoma City Thunder</x:v>
       </x:c>
-      <x:c r="C30" s="75" t="str">
+      <x:c r="C30" s="82" t="str">
         <x:v>Devon Hall</x:v>
       </x:c>
-      <x:c r="D30" s="75" t="str">
+      <x:c r="D30" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E30" s="75" t="str">
+      <x:c r="E30" s="82" t="str">
         <x:v>Oklahoma City Thunder</x:v>
       </x:c>
-      <x:c r="F30" s="75" t="str">
+      <x:c r="F30" s="82" t="str">
         <x:v>Devon Hall</x:v>
       </x:c>
-      <x:c r="G30" s="76" t="str">
+      <x:c r="G30" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H30" s="75" t="str">
+      <x:c r="H30" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I30" s="75" t="str">
+      <x:c r="I30" s="82" t="str">
         <x:v>Perimeter/stash route remains distinct.</x:v>
       </x:c>
-      <x:c r="J30" s="75" t="str">
+      <x:c r="J30" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K30" s="75" t="str">
+      <x:c r="K30" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="75" t="n">
+      <x:c r="A31" s="82" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B31" s="75" t="str">
+      <x:c r="B31" s="82" t="str">
         <x:v>Philadelphia 76ers</x:v>
       </x:c>
-      <x:c r="C31" s="75" t="str">
+      <x:c r="C31" s="82" t="str">
         <x:v>Shake Milton</x:v>
       </x:c>
-      <x:c r="D31" s="75" t="str">
+      <x:c r="D31" s="82" t="str">
         <x:v>Rights from DAL</x:v>
       </x:c>
-      <x:c r="E31" s="75" t="str">
+      <x:c r="E31" s="82" t="str">
         <x:v>Philadelphia 76ers</x:v>
       </x:c>
-      <x:c r="F31" s="75" t="str">
+      <x:c r="F31" s="82" t="str">
         <x:v>Shake Milton</x:v>
       </x:c>
-      <x:c r="G31" s="76" t="str">
+      <x:c r="G31" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H31" s="75" t="str">
+      <x:c r="H31" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I31" s="75" t="str">
+      <x:c r="I31" s="82" t="str">
         <x:v>Guard target and trade structure remain intact.</x:v>
       </x:c>
-      <x:c r="J31" s="75" t="str">
+      <x:c r="J31" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K31" s="75" t="str">
+      <x:c r="K31" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="75" t="n">
+      <x:c r="A32" s="82" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B32" s="75" t="str">
+      <x:c r="B32" s="82" t="str">
         <x:v>Charlotte Hornets</x:v>
       </x:c>
-      <x:c r="C32" s="75" t="str">
+      <x:c r="C32" s="82" t="str">
         <x:v>Arnoldas Kulboka</x:v>
       </x:c>
-      <x:c r="D32" s="75" t="str">
+      <x:c r="D32" s="82" t="str">
         <x:v>Own pick; overseas stash</x:v>
       </x:c>
-      <x:c r="E32" s="75" t="str">
+      <x:c r="E32" s="82" t="str">
         <x:v>Charlotte Hornets</x:v>
       </x:c>
-      <x:c r="F32" s="75" t="str">
+      <x:c r="F32" s="82" t="str">
         <x:v>Arnoldas Kulboka</x:v>
       </x:c>
-      <x:c r="G32" s="76" t="str">
+      <x:c r="G32" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H32" s="75" t="str">
+      <x:c r="H32" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I32" s="75" t="str">
+      <x:c r="I32" s="82" t="str">
         <x:v>Overseas-stash route remains distinct.</x:v>
       </x:c>
-      <x:c r="J32" s="75" t="str">
+      <x:c r="J32" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K32" s="75" t="str">
+      <x:c r="K32" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="77" t="n">
+      <x:c r="A33" s="84" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B33" s="77" t="str">
+      <x:c r="B33" s="84" t="str">
         <x:v>Dallas Mavericks</x:v>
       </x:c>
-      <x:c r="C33" s="77" t="str">
+      <x:c r="C33" s="84" t="str">
         <x:v>Ray Spalding</x:v>
       </x:c>
-      <x:c r="D33" s="77" t="str">
+      <x:c r="D33" s="84" t="str">
         <x:v>Rights from PHI</x:v>
       </x:c>
-      <x:c r="E33" s="77" t="str">
+      <x:c r="E33" s="84" t="str">
         <x:v>Dallas Mavericks</x:v>
       </x:c>
-      <x:c r="F33" s="77" t="str">
+      <x:c r="F33" s="84" t="str">
         <x:v>Chimezie Metu</x:v>
       </x:c>
-      <x:c r="G33" s="77" t="str">
+      <x:c r="G33" s="84" t="str">
         <x:v>CASCADE</x:v>
       </x:c>
-      <x:c r="H33" s="77" t="str">
+      <x:c r="H33" s="84" t="str">
         <x:v>Metu</x:v>
       </x:c>
-      <x:c r="I33" s="77" t="str">
+      <x:c r="I33" s="84" t="str">
         <x:v>Metu is the displaced #49 athletic big and remains above this slot.</x:v>
       </x:c>
-      <x:c r="J33" s="77" t="str">
+      <x:c r="J33" s="84" t="str">
         <x:v>Dallas contract layer PASS; outcomes HOLD</x:v>
       </x:c>
-      <x:c r="K33" s="77" t="str">
+      <x:c r="K33" s="84" t="str">
         <x:v>S13/S15/S28/S29/S30</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="75" t="n">
+      <x:c r="A34" s="82" t="n">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B34" s="75" t="str">
+      <x:c r="B34" s="82" t="str">
         <x:v>Oklahoma City Thunder</x:v>
       </x:c>
-      <x:c r="C34" s="75" t="str">
+      <x:c r="C34" s="82" t="str">
         <x:v>Kevin Hervey</x:v>
       </x:c>
-      <x:c r="D34" s="75" t="str">
+      <x:c r="D34" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E34" s="75" t="str">
+      <x:c r="E34" s="82" t="str">
         <x:v>Oklahoma City Thunder</x:v>
       </x:c>
-      <x:c r="F34" s="75" t="str">
+      <x:c r="F34" s="82" t="str">
         <x:v>Kevin Hervey</x:v>
       </x:c>
-      <x:c r="G34" s="76" t="str">
+      <x:c r="G34" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H34" s="75" t="str">
+      <x:c r="H34" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I34" s="75" t="str">
+      <x:c r="I34" s="82" t="str">
         <x:v>Actual forward choice remains available.</x:v>
       </x:c>
-      <x:c r="J34" s="75" t="str">
+      <x:c r="J34" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K34" s="75" t="str">
+      <x:c r="K34" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="77" t="n">
+      <x:c r="A35" s="84" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B35" s="77" t="str">
+      <x:c r="B35" s="84" t="str">
         <x:v>Denver Nuggets</x:v>
       </x:c>
-      <x:c r="C35" s="77" t="str">
+      <x:c r="C35" s="84" t="str">
         <x:v>Thomas Welsh</x:v>
       </x:c>
-      <x:c r="D35" s="77" t="str">
+      <x:c r="D35" s="84" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E35" s="77" t="str">
+      <x:c r="E35" s="84" t="str">
         <x:v>Denver Nuggets</x:v>
       </x:c>
-      <x:c r="F35" s="77" t="str">
+      <x:c r="F35" s="84" t="str">
         <x:v>Ray Spalding</x:v>
       </x:c>
-      <x:c r="G35" s="77" t="str">
+      <x:c r="G35" s="84" t="str">
         <x:v>CASCADE</x:v>
       </x:c>
-      <x:c r="H35" s="77" t="str">
+      <x:c r="H35" s="84" t="str">
         <x:v>Spalding</x:v>
       </x:c>
-      <x:c r="I35" s="77" t="str">
+      <x:c r="I35" s="84" t="str">
         <x:v>Spalding was graded in the drafted second-round big tier.</x:v>
       </x:c>
-      <x:c r="J35" s="77" t="str">
+      <x:c r="J35" s="84" t="str">
         <x:v>Denver contract layer PASS; Welsh market HOLD</x:v>
       </x:c>
-      <x:c r="K35" s="77" t="str">
+      <x:c r="K35" s="84" t="str">
         <x:v>S18/S31/S32/S33/S34</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="75" t="n">
+      <x:c r="A36" s="82" t="n">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B36" s="75" t="str">
+      <x:c r="B36" s="82" t="str">
         <x:v>Phoenix Suns</x:v>
       </x:c>
-      <x:c r="C36" s="75" t="str">
+      <x:c r="C36" s="82" t="str">
         <x:v>George King</x:v>
       </x:c>
-      <x:c r="D36" s="75" t="str">
+      <x:c r="D36" s="82" t="str">
         <x:v>Own pick</x:v>
       </x:c>
-      <x:c r="E36" s="75" t="str">
+      <x:c r="E36" s="82" t="str">
         <x:v>Phoenix Suns</x:v>
       </x:c>
-      <x:c r="F36" s="75" t="str">
+      <x:c r="F36" s="82" t="str">
         <x:v>George King</x:v>
       </x:c>
-      <x:c r="G36" s="76" t="str">
+      <x:c r="G36" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H36" s="75" t="str">
+      <x:c r="H36" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I36" s="75" t="str">
+      <x:c r="I36" s="82" t="str">
         <x:v>Actual wing choice remains available.</x:v>
       </x:c>
-      <x:c r="J36" s="75" t="str">
+      <x:c r="J36" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K36" s="75" t="str">
+      <x:c r="K36" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="75" t="n">
+      <x:c r="A37" s="82" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B37" s="75" t="str">
+      <x:c r="B37" s="82" t="str">
         <x:v>Dallas Mavericks</x:v>
       </x:c>
-      <x:c r="C37" s="75" t="str">
+      <x:c r="C37" s="82" t="str">
         <x:v>Kostas Antetokounmpo</x:v>
       </x:c>
-      <x:c r="D37" s="75" t="str">
+      <x:c r="D37" s="82" t="str">
         <x:v>Rights from PHI</x:v>
       </x:c>
-      <x:c r="E37" s="75" t="str">
+      <x:c r="E37" s="82" t="str">
         <x:v>Dallas Mavericks</x:v>
       </x:c>
-      <x:c r="F37" s="75" t="str">
+      <x:c r="F37" s="82" t="str">
         <x:v>Kostas Antetokounmpo</x:v>
       </x:c>
-      <x:c r="G37" s="76" t="str">
+      <x:c r="G37" s="98" t="str">
         <x:v>UNCHANGED</x:v>
       </x:c>
-      <x:c r="H37" s="75" t="str">
+      <x:c r="H37" s="82" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I37" s="75" t="str">
+      <x:c r="I37" s="82" t="str">
         <x:v>Second acquired pick and upside bet remain intact.</x:v>
       </x:c>
-      <x:c r="J37" s="75" t="str">
+      <x:c r="J37" s="82" t="str">
         <x:v>Actual path preserved</x:v>
       </x:c>
-      <x:c r="K37" s="75" t="str">
+      <x:c r="K37" s="82" t="str">
         <x:v>S13</x:v>
       </x:c>
     </x:row>
@@ -11635,12 +14505,12 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe4c2387c68d4130"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05b72795a0d942e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -11664,56 +14534,56 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="78" t="str">
+      <x:c r="A4" s="99" t="str">
         <x:v>Actual Spurs</x:v>
       </x:c>
-      <x:c r="B4" s="78" t="str">
+      <x:c r="B4" s="99" t="str">
         <x:v>48-34</x:v>
       </x:c>
-      <x:c r="C4" s="78" t="str">
+      <x:c r="C4" s="99" t="str">
         <x:v>Metu NBA</x:v>
       </x:c>
-      <x:c r="D4" s="78" t="str">
+      <x:c r="D4" s="99" t="str">
         <x:v>29 G / 145.4 MIN</x:v>
       </x:c>
-      <x:c r="E4" s="78" t="str">
+      <x:c r="E4" s="99" t="str">
         <x:v>Metu Austin</x:v>
       </x:c>
-      <x:c r="F4" s="78" t="str">
+      <x:c r="F4" s="99" t="str">
         <x:v>26 G / 710.4 MIN</x:v>
       </x:c>
-      <x:c r="G4" s="78" t="str">
+      <x:c r="G4" s="99" t="str">
         <x:v>CF base</x:v>
       </x:c>
-      <x:c r="H4" s="78" t="str">
+      <x:c r="H4" s="99" t="str">
         <x:v>29 G / 145.4 MIN</x:v>
       </x:c>
-      <x:c r="I4" s="78" t="str">
+      <x:c r="I4" s="99" t="str">
         <x:v>ATL series</x:v>
       </x:c>
-      <x:c r="J4" s="78" t="str">
+      <x:c r="J4" s="99" t="str">
         <x:v>2 G / 0 MIN</x:v>
       </x:c>
-      <x:c r="K4" s="78" t="str">
+      <x:c r="K4" s="99" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="L4" s="78" t="str">
+      <x:c r="L4" s="99" t="str">
         <x:v>BASELINE_ROLE_PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="79"/>
-      <x:c r="B5" s="79"/>
-      <x:c r="C5" s="79"/>
-      <x:c r="D5" s="79"/>
-      <x:c r="E5" s="79"/>
-      <x:c r="F5" s="79"/>
-      <x:c r="G5" s="79"/>
-      <x:c r="H5" s="79"/>
-      <x:c r="I5" s="79"/>
-      <x:c r="J5" s="79"/>
-      <x:c r="K5" s="79"/>
-      <x:c r="L5" s="79"/>
+      <x:c r="A5" s="100"/>
+      <x:c r="B5" s="100"/>
+      <x:c r="C5" s="100"/>
+      <x:c r="D5" s="100"/>
+      <x:c r="E5" s="100"/>
+      <x:c r="F5" s="100"/>
+      <x:c r="G5" s="100"/>
+      <x:c r="H5" s="100"/>
+      <x:c r="I5" s="100"/>
+      <x:c r="J5" s="100"/>
+      <x:c r="K5" s="100"/>
+      <x:c r="L5" s="100"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="51" t="str">
@@ -11740,114 +14610,114 @@
       <x:c r="H6" s="51" t="str">
         <x:v>Required evidence</x:v>
       </x:c>
-      <x:c r="I6" s="79"/>
-      <x:c r="J6" s="79"/>
-      <x:c r="K6" s="79"/>
-      <x:c r="L6" s="79"/>
+      <x:c r="I6" s="100"/>
+      <x:c r="J6" s="100"/>
+      <x:c r="K6" s="100"/>
+      <x:c r="L6" s="100"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="80" t="str">
+      <x:c r="A7" s="101" t="str">
         <x:v>LOW</x:v>
       </x:c>
-      <x:c r="B7" s="80" t="n">
+      <x:c r="B7" s="101" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C7" s="80" t="n">
+      <x:c r="C7" s="101" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="80" t="n">
+      <x:c r="D7" s="101" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="E7" s="80" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F7" s="80" t="n">
+      <x:c r="E7" s="101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="101" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G7" s="80" t="str">
+      <x:c r="G7" s="101" t="str">
         <x:v>No automatic game changes</x:v>
       </x:c>
-      <x:c r="H7" s="80" t="str">
+      <x:c r="H7" s="101" t="str">
         <x:v>Stay inside Metu/deep-reserve slot</x:v>
       </x:c>
-      <x:c r="I7" s="79"/>
-      <x:c r="J7" s="79"/>
-      <x:c r="K7" s="79"/>
-      <x:c r="L7" s="79"/>
+      <x:c r="I7" s="100"/>
+      <x:c r="J7" s="100"/>
+      <x:c r="K7" s="100"/>
+      <x:c r="L7" s="100"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="80" t="str">
+      <x:c r="A8" s="101" t="str">
         <x:v>BASE</x:v>
       </x:c>
-      <x:c r="B8" s="80" t="n">
+      <x:c r="B8" s="101" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C8" s="80" t="n">
+      <x:c r="C8" s="101" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D8" s="80" t="n">
+      <x:c r="D8" s="101" t="n">
         <x:v>145.4</x:v>
       </x:c>
-      <x:c r="E8" s="80" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="80" t="n">
+      <x:c r="E8" s="101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="101" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="G8" s="80" t="str">
+      <x:c r="G8" s="101" t="str">
         <x:v>No automatic game changes</x:v>
       </x:c>
-      <x:c r="H8" s="80" t="str">
+      <x:c r="H8" s="101" t="str">
         <x:v>Metu actual role baseline</x:v>
       </x:c>
-      <x:c r="I8" s="79"/>
-      <x:c r="J8" s="79"/>
-      <x:c r="K8" s="79"/>
-      <x:c r="L8" s="79"/>
+      <x:c r="I8" s="100"/>
+      <x:c r="J8" s="100"/>
+      <x:c r="K8" s="100"/>
+      <x:c r="L8" s="100"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="80" t="str">
+      <x:c r="A9" s="101" t="str">
         <x:v>HIGH</x:v>
       </x:c>
-      <x:c r="B9" s="80" t="n">
+      <x:c r="B9" s="101" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C9" s="80" t="n">
+      <x:c r="C9" s="101" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D9" s="80" t="n">
+      <x:c r="D9" s="101" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="E9" s="80" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="80" t="n">
+      <x:c r="E9" s="101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="101" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G9" s="80" t="str">
+      <x:c r="G9" s="101" t="str">
         <x:v>GAME_REVIEW if competitive</x:v>
       </x:c>
-      <x:c r="H9" s="80" t="str">
+      <x:c r="H9" s="101" t="str">
         <x:v>Dated donor required above 145.4</x:v>
       </x:c>
-      <x:c r="I9" s="79"/>
-      <x:c r="J9" s="79"/>
-      <x:c r="K9" s="79"/>
-      <x:c r="L9" s="79"/>
+      <x:c r="I9" s="100"/>
+      <x:c r="J9" s="100"/>
+      <x:c r="K9" s="100"/>
+      <x:c r="L9" s="100"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="79"/>
-      <x:c r="B10" s="79"/>
-      <x:c r="C10" s="79"/>
-      <x:c r="D10" s="79"/>
-      <x:c r="E10" s="79"/>
-      <x:c r="F10" s="79"/>
-      <x:c r="G10" s="79"/>
-      <x:c r="H10" s="79"/>
-      <x:c r="I10" s="79"/>
-      <x:c r="J10" s="79"/>
-      <x:c r="K10" s="79"/>
-      <x:c r="L10" s="79"/>
+      <x:c r="A10" s="100"/>
+      <x:c r="B10" s="100"/>
+      <x:c r="C10" s="100"/>
+      <x:c r="D10" s="100"/>
+      <x:c r="E10" s="100"/>
+      <x:c r="F10" s="100"/>
+      <x:c r="G10" s="100"/>
+      <x:c r="H10" s="100"/>
+      <x:c r="I10" s="100"/>
+      <x:c r="J10" s="100"/>
+      <x:c r="K10" s="100"/>
+      <x:c r="L10" s="100"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="51" t="str">
@@ -11888,94 +14758,94 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="81" t="n">
+      <x:c r="A12" s="102" t="n">
         <x:v>43530.5</x:v>
       </x:c>
-      <x:c r="B12" s="80" t="str">
+      <x:c r="B12" s="101" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="C12" s="80" t="str">
+      <x:c r="C12" s="101" t="str">
         <x:v>Atlanta Hawks</x:v>
       </x:c>
-      <x:c r="D12" s="80" t="str">
+      <x:c r="D12" s="101" t="str">
         <x:v>W</x:v>
       </x:c>
-      <x:c r="E12" s="80" t="n">
+      <x:c r="E12" s="101" t="n">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="F12" s="80" t="n">
+      <x:c r="F12" s="101" t="n">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G12" s="80" t="n">
+      <x:c r="G12" s="101" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H12" s="80" t="str">
+      <x:c r="H12" s="101" t="str">
         <x:v>NBA roster</x:v>
       </x:c>
-      <x:c r="I12" s="80" t="str">
+      <x:c r="I12" s="101" t="str">
         <x:v>DNP-CD / 0</x:v>
       </x:c>
-      <x:c r="J12" s="80" t="str">
+      <x:c r="J12" s="101" t="str">
         <x:v>NO_DIRECT_MINUTES</x:v>
       </x:c>
-      <x:c r="K12" s="80" t="str">
+      <x:c r="K12" s="101" t="str">
         <x:v>ATL-side execution HOLD</x:v>
       </x:c>
-      <x:c r="L12" s="80" t="str">
+      <x:c r="L12" s="101" t="str">
         <x:v>S25</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="81" t="n">
+      <x:c r="A13" s="102" t="n">
         <x:v>43557.5</x:v>
       </x:c>
-      <x:c r="B13" s="80" t="str">
+      <x:c r="B13" s="101" t="str">
         <x:v>H</x:v>
       </x:c>
-      <x:c r="C13" s="80" t="str">
+      <x:c r="C13" s="101" t="str">
         <x:v>Atlanta Hawks</x:v>
       </x:c>
-      <x:c r="D13" s="80" t="str">
+      <x:c r="D13" s="101" t="str">
         <x:v>W</x:v>
       </x:c>
-      <x:c r="E13" s="80" t="n">
+      <x:c r="E13" s="101" t="n">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="F13" s="80" t="n">
+      <x:c r="F13" s="101" t="n">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G13" s="80" t="n">
+      <x:c r="G13" s="101" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H13" s="80" t="str">
+      <x:c r="H13" s="101" t="str">
         <x:v>NBA roster</x:v>
       </x:c>
-      <x:c r="I13" s="80" t="str">
+      <x:c r="I13" s="101" t="str">
         <x:v>Inactive/0</x:v>
       </x:c>
-      <x:c r="J13" s="80" t="str">
+      <x:c r="J13" s="101" t="str">
         <x:v>NO_DIRECT_MINUTES</x:v>
       </x:c>
-      <x:c r="K13" s="80" t="str">
+      <x:c r="K13" s="101" t="str">
         <x:v>ATL-side execution HOLD</x:v>
       </x:c>
-      <x:c r="L13" s="80" t="str">
+      <x:c r="L13" s="101" t="str">
         <x:v>S26</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="79"/>
-      <x:c r="B14" s="79"/>
-      <x:c r="C14" s="79"/>
-      <x:c r="D14" s="79"/>
-      <x:c r="E14" s="79"/>
-      <x:c r="F14" s="79"/>
-      <x:c r="G14" s="79"/>
-      <x:c r="H14" s="79"/>
-      <x:c r="I14" s="79"/>
-      <x:c r="J14" s="79"/>
-      <x:c r="K14" s="79"/>
-      <x:c r="L14" s="79"/>
+      <x:c r="A14" s="100"/>
+      <x:c r="B14" s="100"/>
+      <x:c r="C14" s="100"/>
+      <x:c r="D14" s="100"/>
+      <x:c r="E14" s="100"/>
+      <x:c r="F14" s="100"/>
+      <x:c r="G14" s="100"/>
+      <x:c r="H14" s="100"/>
+      <x:c r="I14" s="100"/>
+      <x:c r="J14" s="100"/>
+      <x:c r="K14" s="100"/>
+      <x:c r="L14" s="100"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="51" t="str">
@@ -12002,7 +14872,7 @@
       <x:c r="H15" s="51" t="str">
         <x:v>Source ID</x:v>
       </x:c>
-      <x:c r="I15" s="79"/>
+      <x:c r="I15" s="100"/>
       <x:c r="J15" s="51" t="str">
         <x:v>Audit</x:v>
       </x:c>
@@ -12014,624 +14884,624 @@
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="80" t="n">
+      <x:c r="A16" s="101" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B16" s="81" t="n">
+      <x:c r="B16" s="102" t="n">
         <x:v>43398.5</x:v>
       </x:c>
-      <x:c r="C16" s="81" t="n">
+      <x:c r="C16" s="102" t="n">
         <x:v>43400.5</x:v>
       </x:c>
-      <x:c r="D16" s="80" t="n">
+      <x:c r="D16" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E16" s="80" t="str">
+      <x:c r="E16" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F16" s="80" t="str">
+      <x:c r="F16" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G16" s="80" t="str">
+      <x:c r="G16" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H16" s="80" t="str">
+      <x:c r="H16" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I16" s="79"/>
-      <x:c r="J16" s="80" t="str">
+      <x:c r="I16" s="100"/>
+      <x:c r="J16" s="101" t="str">
         <x:v>Assignment windows</x:v>
       </x:c>
-      <x:c r="K16" s="80" t="n">
+      <x:c r="K16" s="101" t="n">
         <x:f>COUNTA(A16:A34)</x:f>
         <x:v>19</x:v>
       </x:c>
-      <x:c r="L16" s="80" t="str">
+      <x:c r="L16" s="101" t="str">
         <x:f>IF(K16=19,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="80" t="n">
+      <x:c r="A17" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B17" s="81" t="n">
+      <x:c r="B17" s="102" t="n">
         <x:v>43409.5</x:v>
       </x:c>
-      <x:c r="C17" s="81" t="n">
+      <x:c r="C17" s="102" t="n">
         <x:v>43409.5</x:v>
       </x:c>
-      <x:c r="D17" s="80" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="80" t="str">
+      <x:c r="D17" s="101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F17" s="80" t="str">
+      <x:c r="F17" s="101" t="str">
         <x:v>Same-day recall</x:v>
       </x:c>
-      <x:c r="G17" s="80" t="str">
+      <x:c r="G17" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H17" s="80" t="str">
+      <x:c r="H17" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I17" s="79"/>
-      <x:c r="J17" s="80" t="str">
+      <x:c r="I17" s="100"/>
+      <x:c r="J17" s="101" t="str">
         <x:v>Direct games</x:v>
       </x:c>
-      <x:c r="K17" s="80" t="n">
+      <x:c r="K17" s="101" t="n">
         <x:f>COUNTA(A12:A13)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L17" s="80" t="str">
+      <x:c r="L17" s="101" t="str">
         <x:f>IF(K17=2,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="80" t="n">
+      <x:c r="A18" s="101" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B18" s="81" t="n">
+      <x:c r="B18" s="102" t="n">
         <x:v>43412.5</x:v>
       </x:c>
-      <x:c r="C18" s="81" t="n">
+      <x:c r="C18" s="102" t="n">
         <x:v>43412.5</x:v>
       </x:c>
-      <x:c r="D18" s="80" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E18" s="80" t="str">
+      <x:c r="D18" s="101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F18" s="80" t="str">
+      <x:c r="F18" s="101" t="str">
         <x:v>Same-day recall</x:v>
       </x:c>
-      <x:c r="G18" s="80" t="str">
+      <x:c r="G18" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H18" s="80" t="str">
+      <x:c r="H18" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I18" s="79"/>
-      <x:c r="J18" s="80" t="str">
+      <x:c r="I18" s="100"/>
+      <x:c r="J18" s="101" t="str">
         <x:v>Direct Metu minutes</x:v>
       </x:c>
-      <x:c r="K18" s="80" t="n">
+      <x:c r="K18" s="101" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="80" t="str">
+      <x:c r="L18" s="101" t="str">
         <x:f>IF(K18=0,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="80" t="n">
+      <x:c r="A19" s="101" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B19" s="81" t="n">
+      <x:c r="B19" s="102" t="n">
         <x:v>43424.5</x:v>
       </x:c>
-      <x:c r="C19" s="81" t="n">
+      <x:c r="C19" s="102" t="n">
         <x:v>43425.5</x:v>
       </x:c>
-      <x:c r="D19" s="80" t="n">
+      <x:c r="D19" s="101" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E19" s="80" t="str">
+      <x:c r="E19" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F19" s="80" t="str">
+      <x:c r="F19" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G19" s="80" t="str">
+      <x:c r="G19" s="101" t="str">
         <x:v>Second reported assignment</x:v>
       </x:c>
-      <x:c r="H19" s="80" t="str">
+      <x:c r="H19" s="101" t="str">
         <x:v>S22/S24</x:v>
       </x:c>
-      <x:c r="I19" s="79"/>
-      <x:c r="J19" s="80" t="str">
+      <x:c r="I19" s="100"/>
+      <x:c r="J19" s="101" t="str">
         <x:v>Base minutes</x:v>
       </x:c>
-      <x:c r="K19" s="80" t="n">
+      <x:c r="K19" s="101" t="n">
         <x:f>D8</x:f>
         <x:v>145.4</x:v>
       </x:c>
-      <x:c r="L19" s="80" t="str">
+      <x:c r="L19" s="101" t="str">
         <x:f>IF(ABS(K19-145.4)&lt;0.01,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="80" t="n">
+      <x:c r="A20" s="101" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B20" s="81" t="n">
+      <x:c r="B20" s="102" t="n">
         <x:v>43435.5</x:v>
       </x:c>
-      <x:c r="C20" s="81" t="n">
+      <x:c r="C20" s="102" t="n">
         <x:v>43436.5</x:v>
       </x:c>
-      <x:c r="D20" s="80" t="n">
+      <x:c r="D20" s="101" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E20" s="80" t="str">
+      <x:c r="E20" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F20" s="80" t="str">
+      <x:c r="F20" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G20" s="80" t="str">
+      <x:c r="G20" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H20" s="80" t="str">
+      <x:c r="H20" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I20" s="79"/>
-      <x:c r="J20" s="80" t="str">
+      <x:c r="I20" s="100"/>
+      <x:c r="J20" s="101" t="str">
         <x:v>High-base excess</x:v>
       </x:c>
-      <x:c r="K20" s="80" t="n">
+      <x:c r="K20" s="101" t="n">
         <x:f>D9-D8</x:f>
         <x:v>34.599999999999994</x:v>
       </x:c>
-      <x:c r="L20" s="80" t="str">
+      <x:c r="L20" s="101" t="str">
         <x:f>IF(ABS(K20-34.6)&lt;0.01,"DONOR REQUIRED","CHECK")</x:f>
         <x:v>DONOR REQUIRED</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="80" t="n">
+      <x:c r="A21" s="101" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B21" s="81" t="n">
+      <x:c r="B21" s="102" t="n">
         <x:v>43442.5</x:v>
       </x:c>
-      <x:c r="C21" s="81" t="n">
+      <x:c r="C21" s="102" t="n">
         <x:v>43443.5</x:v>
       </x:c>
-      <x:c r="D21" s="80" t="n">
+      <x:c r="D21" s="101" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E21" s="80" t="str">
+      <x:c r="E21" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F21" s="80" t="str">
+      <x:c r="F21" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G21" s="80" t="str">
+      <x:c r="G21" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H21" s="80" t="str">
+      <x:c r="H21" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I21" s="79"/>
-      <x:c r="J21" s="80" t="str">
+      <x:c r="I21" s="100"/>
+      <x:c r="J21" s="101" t="str">
         <x:v>Outcome lock</x:v>
       </x:c>
-      <x:c r="K21" s="80" t="str">
+      <x:c r="K21" s="101" t="str">
         <x:f>IF(K18=0,"SPURS-SIDE DIRECT PASS","REVIEW")</x:f>
         <x:v>SPURS-SIDE DIRECT PASS</x:v>
       </x:c>
-      <x:c r="L21" s="80" t="str">
+      <x:c r="L21" s="101" t="str">
         <x:f>IF(K21="SPURS-SIDE DIRECT PASS","PASS","HOLD")</x:f>
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="80" t="n">
+      <x:c r="A22" s="101" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B22" s="81" t="n">
+      <x:c r="B22" s="102" t="n">
         <x:v>43448.5</x:v>
       </x:c>
-      <x:c r="C22" s="81" t="n">
+      <x:c r="C22" s="102" t="n">
         <x:v>43457.5</x:v>
       </x:c>
-      <x:c r="D22" s="80" t="n">
+      <x:c r="D22" s="101" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E22" s="80" t="str">
+      <x:c r="E22" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F22" s="80" t="str">
+      <x:c r="F22" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G22" s="80" t="str">
+      <x:c r="G22" s="101" t="str">
         <x:v>Development window</x:v>
       </x:c>
-      <x:c r="H22" s="80" t="str">
+      <x:c r="H22" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I22" s="79"/>
-      <x:c r="J22" s="79"/>
-      <x:c r="K22" s="79"/>
-      <x:c r="L22" s="79"/>
+      <x:c r="I22" s="100"/>
+      <x:c r="J22" s="100"/>
+      <x:c r="K22" s="100"/>
+      <x:c r="L22" s="100"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="80" t="n">
+      <x:c r="A23" s="101" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B23" s="81" t="n">
+      <x:c r="B23" s="102" t="n">
         <x:v>43461.5</x:v>
       </x:c>
-      <x:c r="C23" s="81" t="n">
+      <x:c r="C23" s="102" t="n">
         <x:v>43468.5</x:v>
       </x:c>
-      <x:c r="D23" s="80" t="n">
+      <x:c r="D23" s="101" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E23" s="80" t="str">
+      <x:c r="E23" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F23" s="80" t="str">
+      <x:c r="F23" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G23" s="80" t="str">
+      <x:c r="G23" s="101" t="str">
         <x:v>Development window</x:v>
       </x:c>
-      <x:c r="H23" s="80" t="str">
+      <x:c r="H23" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I23" s="79"/>
-      <x:c r="J23" s="82" t="str">
+      <x:c r="I23" s="100"/>
+      <x:c r="J23" s="103" t="str">
         <x:v>48-34 remains BASELINE, not a locked counterfactual result. Atlanta-side player impact is still HOLD.</x:v>
       </x:c>
-      <x:c r="K23" s="82"/>
-      <x:c r="L23" s="82"/>
+      <x:c r="K23" s="103"/>
+      <x:c r="L23" s="103"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="80" t="n">
+      <x:c r="A24" s="101" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B24" s="81" t="n">
+      <x:c r="B24" s="102" t="n">
         <x:v>43470.5</x:v>
       </x:c>
-      <x:c r="C24" s="81" t="n">
+      <x:c r="C24" s="102" t="n">
         <x:v>43470.5</x:v>
       </x:c>
-      <x:c r="D24" s="80" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E24" s="80" t="str">
+      <x:c r="D24" s="101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F24" s="80" t="str">
+      <x:c r="F24" s="101" t="str">
         <x:v>Same-day recall</x:v>
       </x:c>
-      <x:c r="G24" s="80" t="str">
+      <x:c r="G24" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H24" s="80" t="str">
+      <x:c r="H24" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I24" s="79"/>
-      <x:c r="J24" s="79"/>
-      <x:c r="K24" s="79"/>
-      <x:c r="L24" s="79"/>
+      <x:c r="I24" s="100"/>
+      <x:c r="J24" s="100"/>
+      <x:c r="K24" s="100"/>
+      <x:c r="L24" s="100"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="80" t="n">
+      <x:c r="A25" s="101" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B25" s="81" t="n">
+      <x:c r="B25" s="102" t="n">
         <x:v>43472.5</x:v>
       </x:c>
-      <x:c r="C25" s="81" t="n">
+      <x:c r="C25" s="102" t="n">
         <x:v>43482.5</x:v>
       </x:c>
-      <x:c r="D25" s="80" t="n">
+      <x:c r="D25" s="101" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E25" s="80" t="str">
+      <x:c r="E25" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F25" s="80" t="str">
+      <x:c r="F25" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G25" s="80" t="str">
+      <x:c r="G25" s="101" t="str">
         <x:v>Development window</x:v>
       </x:c>
-      <x:c r="H25" s="80" t="str">
+      <x:c r="H25" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I25" s="79"/>
-      <x:c r="J25" s="79"/>
-      <x:c r="K25" s="79"/>
-      <x:c r="L25" s="79"/>
+      <x:c r="I25" s="100"/>
+      <x:c r="J25" s="100"/>
+      <x:c r="K25" s="100"/>
+      <x:c r="L25" s="100"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="80" t="n">
+      <x:c r="A26" s="101" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B26" s="81" t="n">
+      <x:c r="B26" s="102" t="n">
         <x:v>43484.5</x:v>
       </x:c>
-      <x:c r="C26" s="81" t="n">
+      <x:c r="C26" s="102" t="n">
         <x:v>43485.5</x:v>
       </x:c>
-      <x:c r="D26" s="80" t="n">
+      <x:c r="D26" s="101" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E26" s="80" t="str">
+      <x:c r="E26" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F26" s="80" t="str">
+      <x:c r="F26" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G26" s="80" t="str">
+      <x:c r="G26" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H26" s="80" t="str">
+      <x:c r="H26" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I26" s="79"/>
-      <x:c r="J26" s="79"/>
-      <x:c r="K26" s="79"/>
-      <x:c r="L26" s="79"/>
+      <x:c r="I26" s="100"/>
+      <x:c r="J26" s="100"/>
+      <x:c r="K26" s="100"/>
+      <x:c r="L26" s="100"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="80" t="n">
+      <x:c r="A27" s="101" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B27" s="81" t="n">
+      <x:c r="B27" s="102" t="n">
         <x:v>43490.5</x:v>
       </x:c>
-      <x:c r="C27" s="81" t="n">
+      <x:c r="C27" s="102" t="n">
         <x:v>43491.5</x:v>
       </x:c>
-      <x:c r="D27" s="80" t="n">
+      <x:c r="D27" s="101" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E27" s="80" t="str">
+      <x:c r="E27" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F27" s="80" t="str">
+      <x:c r="F27" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G27" s="80" t="str">
+      <x:c r="G27" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H27" s="80" t="str">
+      <x:c r="H27" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I27" s="79"/>
-      <x:c r="J27" s="79"/>
-      <x:c r="K27" s="79"/>
-      <x:c r="L27" s="79"/>
+      <x:c r="I27" s="100"/>
+      <x:c r="J27" s="100"/>
+      <x:c r="K27" s="100"/>
+      <x:c r="L27" s="100"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="80" t="n">
+      <x:c r="A28" s="101" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B28" s="81" t="n">
+      <x:c r="B28" s="102" t="n">
         <x:v>43497.5</x:v>
       </x:c>
-      <x:c r="C28" s="81" t="n">
+      <x:c r="C28" s="102" t="n">
         <x:v>43498.5</x:v>
       </x:c>
-      <x:c r="D28" s="80" t="n">
+      <x:c r="D28" s="101" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E28" s="80" t="str">
+      <x:c r="E28" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F28" s="80" t="str">
+      <x:c r="F28" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G28" s="80" t="str">
+      <x:c r="G28" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H28" s="80" t="str">
+      <x:c r="H28" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I28" s="79"/>
-      <x:c r="J28" s="79"/>
-      <x:c r="K28" s="79"/>
-      <x:c r="L28" s="79"/>
+      <x:c r="I28" s="100"/>
+      <x:c r="J28" s="100"/>
+      <x:c r="K28" s="100"/>
+      <x:c r="L28" s="100"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="80" t="n">
+      <x:c r="A29" s="101" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B29" s="81" t="n">
+      <x:c r="B29" s="102" t="n">
         <x:v>43506.5</x:v>
       </x:c>
-      <x:c r="C29" s="81" t="n">
+      <x:c r="C29" s="102" t="n">
         <x:v>43507.5</x:v>
       </x:c>
-      <x:c r="D29" s="80" t="n">
+      <x:c r="D29" s="101" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E29" s="80" t="str">
+      <x:c r="E29" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F29" s="80" t="str">
+      <x:c r="F29" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G29" s="80" t="str">
+      <x:c r="G29" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H29" s="80" t="str">
+      <x:c r="H29" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I29" s="79"/>
-      <x:c r="J29" s="79"/>
-      <x:c r="K29" s="79"/>
-      <x:c r="L29" s="79"/>
+      <x:c r="I29" s="100"/>
+      <x:c r="J29" s="100"/>
+      <x:c r="K29" s="100"/>
+      <x:c r="L29" s="100"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="80" t="n">
+      <x:c r="A30" s="101" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B30" s="81" t="n">
+      <x:c r="B30" s="102" t="n">
         <x:v>43524.5</x:v>
       </x:c>
-      <x:c r="C30" s="81" t="n">
+      <x:c r="C30" s="102" t="n">
         <x:v>43525.5</x:v>
       </x:c>
-      <x:c r="D30" s="80" t="n">
+      <x:c r="D30" s="101" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E30" s="80" t="str">
+      <x:c r="E30" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F30" s="80" t="str">
+      <x:c r="F30" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G30" s="80" t="str">
+      <x:c r="G30" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H30" s="80" t="str">
+      <x:c r="H30" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I30" s="79"/>
-      <x:c r="J30" s="79"/>
-      <x:c r="K30" s="79"/>
-      <x:c r="L30" s="79"/>
+      <x:c r="I30" s="100"/>
+      <x:c r="J30" s="100"/>
+      <x:c r="K30" s="100"/>
+      <x:c r="L30" s="100"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="80" t="n">
+      <x:c r="A31" s="101" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B31" s="81" t="n">
+      <x:c r="B31" s="102" t="n">
         <x:v>43531.5</x:v>
       </x:c>
-      <x:c r="C31" s="81" t="n">
+      <x:c r="C31" s="102" t="n">
         <x:v>43534.5</x:v>
       </x:c>
-      <x:c r="D31" s="80" t="n">
+      <x:c r="D31" s="101" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E31" s="80" t="str">
+      <x:c r="E31" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F31" s="80" t="str">
+      <x:c r="F31" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G31" s="80" t="str">
+      <x:c r="G31" s="101" t="str">
         <x:v>After Atlanta game</x:v>
       </x:c>
-      <x:c r="H31" s="80" t="str">
+      <x:c r="H31" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I31" s="79"/>
-      <x:c r="J31" s="79"/>
-      <x:c r="K31" s="79"/>
-      <x:c r="L31" s="79"/>
+      <x:c r="I31" s="100"/>
+      <x:c r="J31" s="100"/>
+      <x:c r="K31" s="100"/>
+      <x:c r="L31" s="100"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="80" t="n">
+      <x:c r="A32" s="101" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B32" s="81" t="n">
+      <x:c r="B32" s="102" t="n">
         <x:v>43537.5</x:v>
       </x:c>
-      <x:c r="C32" s="81" t="n">
+      <x:c r="C32" s="102" t="n">
         <x:v>43539.5</x:v>
       </x:c>
-      <x:c r="D32" s="80" t="n">
+      <x:c r="D32" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E32" s="80" t="str">
+      <x:c r="E32" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F32" s="80" t="str">
+      <x:c r="F32" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G32" s="80" t="str">
+      <x:c r="G32" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H32" s="80" t="str">
+      <x:c r="H32" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I32" s="79"/>
-      <x:c r="J32" s="79"/>
-      <x:c r="K32" s="79"/>
-      <x:c r="L32" s="79"/>
+      <x:c r="I32" s="100"/>
+      <x:c r="J32" s="100"/>
+      <x:c r="K32" s="100"/>
+      <x:c r="L32" s="100"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="80" t="n">
+      <x:c r="A33" s="101" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B33" s="81" t="n">
+      <x:c r="B33" s="102" t="n">
         <x:v>43543.5</x:v>
       </x:c>
-      <x:c r="C33" s="81" t="n">
+      <x:c r="C33" s="102" t="n">
         <x:v>43544.5</x:v>
       </x:c>
-      <x:c r="D33" s="80" t="n">
+      <x:c r="D33" s="101" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E33" s="80" t="str">
+      <x:c r="E33" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F33" s="80" t="str">
+      <x:c r="F33" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G33" s="80" t="str">
+      <x:c r="G33" s="101" t="str">
         <x:v>NBA contract retained</x:v>
       </x:c>
-      <x:c r="H33" s="80" t="str">
+      <x:c r="H33" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I33" s="79"/>
-      <x:c r="J33" s="79"/>
-      <x:c r="K33" s="79"/>
-      <x:c r="L33" s="79"/>
+      <x:c r="I33" s="100"/>
+      <x:c r="J33" s="100"/>
+      <x:c r="K33" s="100"/>
+      <x:c r="L33" s="100"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="80" t="n">
+      <x:c r="A34" s="101" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B34" s="81" t="n">
+      <x:c r="B34" s="102" t="n">
         <x:v>43545.5</x:v>
       </x:c>
-      <x:c r="C34" s="81" t="n">
+      <x:c r="C34" s="102" t="n">
         <x:v>43548.5</x:v>
       </x:c>
-      <x:c r="D34" s="80" t="n">
+      <x:c r="D34" s="101" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E34" s="80" t="str">
+      <x:c r="E34" s="101" t="str">
         <x:v>Austin assignment</x:v>
       </x:c>
-      <x:c r="F34" s="80" t="str">
+      <x:c r="F34" s="101" t="str">
         <x:v>Recall</x:v>
       </x:c>
-      <x:c r="G34" s="80" t="str">
+      <x:c r="G34" s="101" t="str">
         <x:v>Final logged window</x:v>
       </x:c>
-      <x:c r="H34" s="80" t="str">
+      <x:c r="H34" s="101" t="str">
         <x:v>S22</x:v>
       </x:c>
-      <x:c r="I34" s="79"/>
-      <x:c r="J34" s="79"/>
-      <x:c r="K34" s="79"/>
-      <x:c r="L34" s="79"/>
+      <x:c r="I34" s="100"/>
+      <x:c r="J34" s="100"/>
+      <x:c r="K34" s="100"/>
+      <x:c r="L34" s="100"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -12640,12 +15510,12 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a3fdd213b5447f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R001c54ba682f417d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -12670,54 +15540,54 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="78" t="str">
+      <x:c r="A4" s="99" t="str">
         <x:v>Dallas base</x:v>
       </x:c>
-      <x:c r="B4" s="78" t="str">
+      <x:c r="B4" s="99" t="str">
         <x:v>1 G / 1 MIN</x:v>
       </x:c>
-      <x:c r="C4" s="78"/>
-      <x:c r="D4" s="78" t="str">
+      <x:c r="C4" s="99"/>
+      <x:c r="D4" s="99" t="str">
         <x:v>Texas</x:v>
       </x:c>
-      <x:c r="E4" s="78" t="str">
+      <x:c r="E4" s="99" t="str">
         <x:v>29 G / 30.1 MPG</x:v>
       </x:c>
-      <x:c r="F4" s="78"/>
-      <x:c r="G4" s="78" t="str">
+      <x:c r="F4" s="99"/>
+      <x:c r="G4" s="99" t="str">
         <x:v>Denver base</x:v>
       </x:c>
-      <x:c r="H4" s="78" t="str">
+      <x:c r="H4" s="99" t="str">
         <x:v>11 G / 36 MIN</x:v>
       </x:c>
-      <x:c r="I4" s="78"/>
-      <x:c r="J4" s="78" t="str">
+      <x:c r="I4" s="99"/>
+      <x:c r="J4" s="99" t="str">
         <x:v>ATL series</x:v>
       </x:c>
-      <x:c r="K4" s="78" t="str">
+      <x:c r="K4" s="99" t="str">
         <x:v>4 G / 0 MIN</x:v>
       </x:c>
-      <x:c r="L4" s="78" t="str">
+      <x:c r="L4" s="99" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="M4" s="78" t="str">
+      <x:c r="M4" s="99" t="str">
         <x:v>CONTRACT_LAYER_PASS</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="79"/>
-      <x:c r="B5" s="79"/>
-      <x:c r="C5" s="79"/>
-      <x:c r="D5" s="79"/>
-      <x:c r="E5" s="79"/>
-      <x:c r="F5" s="79"/>
-      <x:c r="G5" s="79"/>
-      <x:c r="H5" s="79"/>
-      <x:c r="I5" s="79"/>
-      <x:c r="J5" s="79"/>
-      <x:c r="K5" s="79"/>
-      <x:c r="L5" s="79"/>
-      <x:c r="M5" s="79"/>
+      <x:c r="A5" s="100"/>
+      <x:c r="B5" s="100"/>
+      <x:c r="C5" s="100"/>
+      <x:c r="D5" s="100"/>
+      <x:c r="E5" s="100"/>
+      <x:c r="F5" s="100"/>
+      <x:c r="G5" s="100"/>
+      <x:c r="H5" s="100"/>
+      <x:c r="I5" s="100"/>
+      <x:c r="J5" s="100"/>
+      <x:c r="K5" s="100"/>
+      <x:c r="L5" s="100"/>
+      <x:c r="M5" s="100"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="51" t="str">
@@ -12761,270 +15631,270 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="83" t="str">
+      <x:c r="A7" s="91" t="str">
         <x:v>Dallas</x:v>
       </x:c>
-      <x:c r="B7" s="83" t="str">
+      <x:c r="B7" s="91" t="str">
         <x:v>ACTUAL</x:v>
       </x:c>
-      <x:c r="C7" s="83" t="str">
+      <x:c r="C7" s="91" t="str">
         <x:v>Ray Spalding</x:v>
       </x:c>
-      <x:c r="D7" s="83" t="n">
+      <x:c r="D7" s="91" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E7" s="83" t="str">
+      <x:c r="E7" s="91" t="str">
         <x:v>Standard NBA</x:v>
       </x:c>
-      <x:c r="F7" s="83" t="str">
+      <x:c r="F7" s="91" t="str">
         <x:v>Texas assignment</x:v>
       </x:c>
-      <x:c r="G7" s="83" t="n">
+      <x:c r="G7" s="91" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H7" s="83" t="n">
+      <x:c r="H7" s="91" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I7" s="83" t="n">
+      <x:c r="I7" s="91" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="J7" s="83" t="str">
+      <x:c r="J7" s="91" t="str">
         <x:v>Waived 2019-01-31</x:v>
       </x:c>
-      <x:c r="K7" s="83" t="str">
+      <x:c r="K7" s="91" t="str">
         <x:v>ACTUAL_REPLACED</x:v>
       </x:c>
-      <x:c r="L7" s="83" t="str">
+      <x:c r="L7" s="91" t="str">
         <x:v>Reference only</x:v>
       </x:c>
-      <x:c r="M7" s="83" t="str">
+      <x:c r="M7" s="91" t="str">
         <x:v>S28/S29/S30</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="83" t="str">
+      <x:c r="A8" s="91" t="str">
         <x:v>Dallas</x:v>
       </x:c>
-      <x:c r="B8" s="83" t="str">
+      <x:c r="B8" s="91" t="str">
         <x:v>CF</x:v>
       </x:c>
-      <x:c r="C8" s="83" t="str">
+      <x:c r="C8" s="91" t="str">
         <x:v>Chimezie Metu</x:v>
       </x:c>
-      <x:c r="D8" s="83" t="n">
+      <x:c r="D8" s="91" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E8" s="83" t="str">
+      <x:c r="E8" s="91" t="str">
         <x:v>Standard NBA layer</x:v>
       </x:c>
-      <x:c r="F8" s="83" t="str">
+      <x:c r="F8" s="91" t="str">
         <x:v>Texas assignment baseline</x:v>
       </x:c>
-      <x:c r="G8" s="83" t="n">
+      <x:c r="G8" s="91" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H8" s="83" t="n">
+      <x:c r="H8" s="91" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I8" s="83" t="n">
+      <x:c r="I8" s="91" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="J8" s="83" t="str">
+      <x:c r="J8" s="91" t="str">
         <x:v>Jan. 31 waiver choice HOLD</x:v>
       </x:c>
-      <x:c r="K8" s="83" t="str">
+      <x:c r="K8" s="91" t="str">
         <x:v>CF_CHANGED_STANDARD</x:v>
       </x:c>
-      <x:c r="L8" s="83" t="str">
+      <x:c r="L8" s="91" t="str">
         <x:v>&gt;1 NBA MIN or a different waiver opens Dallas player-game review</x:v>
       </x:c>
-      <x:c r="M8" s="83" t="str">
+      <x:c r="M8" s="91" t="str">
         <x:v>S28/S29/S30</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="83" t="str">
+      <x:c r="A9" s="91" t="str">
         <x:v>Denver</x:v>
       </x:c>
-      <x:c r="B9" s="83" t="str">
+      <x:c r="B9" s="91" t="str">
         <x:v>ACTUAL</x:v>
       </x:c>
-      <x:c r="C9" s="83" t="str">
+      <x:c r="C9" s="91" t="str">
         <x:v>Thomas Welsh</x:v>
       </x:c>
-      <x:c r="D9" s="83" t="n">
+      <x:c r="D9" s="91" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E9" s="83" t="str">
+      <x:c r="E9" s="91" t="str">
         <x:v>Two-way</x:v>
       </x:c>
-      <x:c r="F9" s="83" t="str">
+      <x:c r="F9" s="91" t="str">
         <x:v>Capital City / Iowa</x:v>
       </x:c>
-      <x:c r="G9" s="83" t="n">
+      <x:c r="G9" s="91" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="H9" s="83" t="n">
+      <x:c r="H9" s="91" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="I9" s="83" t="n">
+      <x:c r="I9" s="91" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="J9" s="83" t="str">
+      <x:c r="J9" s="91" t="str">
         <x:v>Two-way ended 2019-07-30</x:v>
       </x:c>
-      <x:c r="K9" s="83" t="str">
+      <x:c r="K9" s="91" t="str">
         <x:v>ACTUAL_REPLACED</x:v>
       </x:c>
-      <x:c r="L9" s="83" t="str">
+      <x:c r="L9" s="91" t="str">
         <x:v>Reference only</x:v>
       </x:c>
-      <x:c r="M9" s="83" t="str">
+      <x:c r="M9" s="91" t="str">
         <x:v>S31/S34/S35</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="83" t="str">
+      <x:c r="A10" s="91" t="str">
         <x:v>Denver</x:v>
       </x:c>
-      <x:c r="B10" s="83" t="str">
+      <x:c r="B10" s="91" t="str">
         <x:v>CF</x:v>
       </x:c>
-      <x:c r="C10" s="83" t="str">
+      <x:c r="C10" s="91" t="str">
         <x:v>Ray Spalding</x:v>
       </x:c>
-      <x:c r="D10" s="83" t="n">
+      <x:c r="D10" s="91" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E10" s="83" t="str">
+      <x:c r="E10" s="91" t="str">
         <x:v>Two-way (Welsh slot)</x:v>
       </x:c>
-      <x:c r="F10" s="83" t="str">
+      <x:c r="F10" s="91" t="str">
         <x:v>External G League assignment class</x:v>
       </x:c>
-      <x:c r="G10" s="83" t="n">
+      <x:c r="G10" s="91" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="H10" s="83" t="n">
+      <x:c r="H10" s="91" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="I10" s="83" t="n">
+      <x:c r="I10" s="91" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="J10" s="83" t="str">
+      <x:c r="J10" s="91" t="str">
         <x:v>Season role baseline</x:v>
       </x:c>
-      <x:c r="K10" s="83" t="str">
+      <x:c r="K10" s="91" t="str">
         <x:v>CF_CHANGED_TWO_WAY</x:v>
       </x:c>
-      <x:c r="L10" s="83" t="str">
+      <x:c r="L10" s="91" t="str">
         <x:v>&gt;36 NBA MIN or different dates opens Denver player-game review</x:v>
       </x:c>
-      <x:c r="M10" s="83" t="str">
+      <x:c r="M10" s="91" t="str">
         <x:v>S31/S32/S33/S34</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="83" t="str">
+      <x:c r="A11" s="91" t="str">
         <x:v>Denver</x:v>
       </x:c>
-      <x:c r="B11" s="83" t="str">
+      <x:c r="B11" s="91" t="str">
         <x:v>CF</x:v>
       </x:c>
-      <x:c r="C11" s="83" t="str">
+      <x:c r="C11" s="91" t="str">
         <x:v>DeVaughn Akoon-Purcell</x:v>
       </x:c>
-      <x:c r="D11" s="83"/>
-      <x:c r="E11" s="83" t="str">
+      <x:c r="D11" s="91"/>
+      <x:c r="E11" s="91" t="str">
         <x:v>Two-way</x:v>
       </x:c>
-      <x:c r="F11" s="83" t="str">
+      <x:c r="F11" s="91" t="str">
         <x:v>G League development</x:v>
       </x:c>
-      <x:c r="G11" s="83"/>
-      <x:c r="H11" s="83"/>
-      <x:c r="I11" s="83"/>
-      <x:c r="J11" s="83" t="str">
+      <x:c r="G11" s="91"/>
+      <x:c r="H11" s="91"/>
+      <x:c r="I11" s="91"/>
+      <x:c r="J11" s="91" t="str">
         <x:v>Actual second slot preserved</x:v>
       </x:c>
-      <x:c r="K11" s="83" t="str">
+      <x:c r="K11" s="91" t="str">
         <x:v>CF_PROTECTED_TWO_WAY</x:v>
       </x:c>
-      <x:c r="L11" s="83" t="str">
+      <x:c r="L11" s="91" t="str">
         <x:v>Do not displace without a new transaction cause</x:v>
       </x:c>
-      <x:c r="M11" s="83" t="str">
+      <x:c r="M11" s="91" t="str">
         <x:v>S32/S33</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="83" t="str">
+      <x:c r="A12" s="91" t="str">
         <x:v>Denver</x:v>
       </x:c>
-      <x:c r="B12" s="83" t="str">
+      <x:c r="B12" s="91" t="str">
         <x:v>CF</x:v>
       </x:c>
-      <x:c r="C12" s="83" t="str">
+      <x:c r="C12" s="91" t="str">
         <x:v>Thomas Welsh</x:v>
       </x:c>
-      <x:c r="D12" s="83"/>
-      <x:c r="E12" s="83" t="str">
+      <x:c r="D12" s="91"/>
+      <x:c r="E12" s="91" t="str">
         <x:v>No Denver slot</x:v>
       </x:c>
-      <x:c r="F12" s="83" t="str">
+      <x:c r="F12" s="91" t="str">
         <x:v>Undrafted free-agent market</x:v>
       </x:c>
-      <x:c r="G12" s="83" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H12" s="83" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I12" s="83" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12" s="83" t="str">
+      <x:c r="G12" s="91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="91" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="91" t="str">
         <x:v>Destination unresolved</x:v>
       </x:c>
-      <x:c r="K12" s="83" t="str">
+      <x:c r="K12" s="91" t="str">
         <x:v>CF_OUT_NO_SLOT</x:v>
       </x:c>
-      <x:c r="L12" s="83" t="str">
+      <x:c r="L12" s="91" t="str">
         <x:v>Any NBA signing creates a new team-impact branch</x:v>
       </x:c>
-      <x:c r="M12" s="83" t="str">
+      <x:c r="M12" s="91" t="str">
         <x:v>S31/S32/S33/S35</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="79"/>
-      <x:c r="B13" s="79"/>
-      <x:c r="C13" s="79"/>
-      <x:c r="D13" s="79"/>
-      <x:c r="E13" s="79"/>
-      <x:c r="F13" s="79"/>
-      <x:c r="G13" s="79"/>
-      <x:c r="H13" s="79"/>
-      <x:c r="I13" s="79"/>
-      <x:c r="J13" s="79"/>
-      <x:c r="K13" s="79"/>
-      <x:c r="L13" s="79"/>
-      <x:c r="M13" s="79"/>
+      <x:c r="A13" s="100"/>
+      <x:c r="B13" s="100"/>
+      <x:c r="C13" s="100"/>
+      <x:c r="D13" s="100"/>
+      <x:c r="E13" s="100"/>
+      <x:c r="F13" s="100"/>
+      <x:c r="G13" s="100"/>
+      <x:c r="H13" s="100"/>
+      <x:c r="I13" s="100"/>
+      <x:c r="J13" s="100"/>
+      <x:c r="K13" s="100"/>
+      <x:c r="L13" s="100"/>
+      <x:c r="M13" s="100"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="79"/>
-      <x:c r="B14" s="79"/>
-      <x:c r="C14" s="79"/>
-      <x:c r="D14" s="79"/>
-      <x:c r="E14" s="79"/>
-      <x:c r="F14" s="79"/>
-      <x:c r="G14" s="79"/>
-      <x:c r="H14" s="79"/>
-      <x:c r="I14" s="79"/>
-      <x:c r="J14" s="79"/>
-      <x:c r="K14" s="79"/>
-      <x:c r="L14" s="79"/>
-      <x:c r="M14" s="79"/>
+      <x:c r="A14" s="100"/>
+      <x:c r="B14" s="100"/>
+      <x:c r="C14" s="100"/>
+      <x:c r="D14" s="100"/>
+      <x:c r="E14" s="100"/>
+      <x:c r="F14" s="100"/>
+      <x:c r="G14" s="100"/>
+      <x:c r="H14" s="100"/>
+      <x:c r="I14" s="100"/>
+      <x:c r="J14" s="100"/>
+      <x:c r="K14" s="100"/>
+      <x:c r="L14" s="100"/>
+      <x:c r="M14" s="100"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="51" t="str">
@@ -13063,191 +15933,191 @@
       <x:c r="L15" s="51" t="str">
         <x:v>Source ID</x:v>
       </x:c>
-      <x:c r="M15" s="79"/>
+      <x:c r="M15" s="100"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="80" t="str">
+      <x:c r="A16" s="101" t="str">
         <x:v>Dallas</x:v>
       </x:c>
-      <x:c r="B16" s="81" t="n">
+      <x:c r="B16" s="102" t="n">
         <x:v>43397.5</x:v>
       </x:c>
-      <x:c r="C16" s="80" t="str">
+      <x:c r="C16" s="101" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="D16" s="80" t="str">
+      <x:c r="D16" s="101" t="str">
         <x:v>L</x:v>
       </x:c>
-      <x:c r="E16" s="80" t="n">
+      <x:c r="E16" s="101" t="n">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="F16" s="80" t="n">
+      <x:c r="F16" s="101" t="n">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G16" s="80" t="n">
+      <x:c r="G16" s="101" t="n">
         <x:v>-7</x:v>
       </x:c>
-      <x:c r="H16" s="80" t="str">
+      <x:c r="H16" s="101" t="str">
         <x:v>Ray Spalding</x:v>
       </x:c>
-      <x:c r="I16" s="80" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J16" s="80" t="str">
+      <x:c r="I16" s="101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="101" t="str">
         <x:v>NO_DIRECT_MINUTES</x:v>
       </x:c>
-      <x:c r="K16" s="80" t="str">
+      <x:c r="K16" s="101" t="str">
         <x:v>ATL-side execution HOLD</x:v>
       </x:c>
-      <x:c r="L16" s="80" t="str">
+      <x:c r="L16" s="101" t="str">
         <x:v>S10/S29</x:v>
       </x:c>
-      <x:c r="M16" s="79"/>
+      <x:c r="M16" s="100"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="80" t="str">
+      <x:c r="A17" s="101" t="str">
         <x:v>Dallas</x:v>
       </x:c>
-      <x:c r="B17" s="81" t="n">
+      <x:c r="B17" s="102" t="n">
         <x:v>43446.5</x:v>
       </x:c>
-      <x:c r="C17" s="80" t="str">
+      <x:c r="C17" s="101" t="str">
         <x:v>H</x:v>
       </x:c>
-      <x:c r="D17" s="80" t="str">
+      <x:c r="D17" s="101" t="str">
         <x:v>W</x:v>
       </x:c>
-      <x:c r="E17" s="80" t="n">
+      <x:c r="E17" s="101" t="n">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="F17" s="80" t="n">
+      <x:c r="F17" s="101" t="n">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G17" s="80" t="n">
+      <x:c r="G17" s="101" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H17" s="80" t="str">
+      <x:c r="H17" s="101" t="str">
         <x:v>Ray Spalding</x:v>
       </x:c>
-      <x:c r="I17" s="80" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="80" t="str">
+      <x:c r="I17" s="101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="101" t="str">
         <x:v>NO_DIRECT_MINUTES</x:v>
       </x:c>
-      <x:c r="K17" s="80" t="str">
+      <x:c r="K17" s="101" t="str">
         <x:v>ATL-side execution HOLD</x:v>
       </x:c>
-      <x:c r="L17" s="80" t="str">
+      <x:c r="L17" s="101" t="str">
         <x:v>S11/S29</x:v>
       </x:c>
-      <x:c r="M17" s="79"/>
+      <x:c r="M17" s="100"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="80" t="str">
+      <x:c r="A18" s="101" t="str">
         <x:v>Denver</x:v>
       </x:c>
-      <x:c r="B18" s="81" t="n">
+      <x:c r="B18" s="102" t="n">
         <x:v>43419.5</x:v>
       </x:c>
-      <x:c r="C18" s="80" t="str">
+      <x:c r="C18" s="101" t="str">
         <x:v>H</x:v>
       </x:c>
-      <x:c r="D18" s="80" t="str">
+      <x:c r="D18" s="101" t="str">
         <x:v>W</x:v>
       </x:c>
-      <x:c r="E18" s="80" t="n">
+      <x:c r="E18" s="101" t="n">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="F18" s="80" t="n">
+      <x:c r="F18" s="101" t="n">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G18" s="80" t="n">
+      <x:c r="G18" s="101" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H18" s="80" t="str">
+      <x:c r="H18" s="101" t="str">
         <x:v>Thomas Welsh</x:v>
       </x:c>
-      <x:c r="I18" s="80" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J18" s="80" t="str">
+      <x:c r="I18" s="101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="101" t="str">
         <x:v>NO_DIRECT_MINUTES</x:v>
       </x:c>
-      <x:c r="K18" s="80" t="str">
+      <x:c r="K18" s="101" t="str">
         <x:v>ATL-side execution HOLD</x:v>
       </x:c>
-      <x:c r="L18" s="80" t="str">
+      <x:c r="L18" s="101" t="str">
         <x:v>S36/S37</x:v>
       </x:c>
-      <x:c r="M18" s="79"/>
+      <x:c r="M18" s="100"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="80" t="str">
+      <x:c r="A19" s="101" t="str">
         <x:v>Denver</x:v>
       </x:c>
-      <x:c r="B19" s="81" t="n">
+      <x:c r="B19" s="102" t="n">
         <x:v>43442.5</x:v>
       </x:c>
-      <x:c r="C19" s="80" t="str">
+      <x:c r="C19" s="101" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="D19" s="80" t="str">
+      <x:c r="D19" s="101" t="str">
         <x:v>L</x:v>
       </x:c>
-      <x:c r="E19" s="80" t="n">
+      <x:c r="E19" s="101" t="n">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="F19" s="80" t="n">
+      <x:c r="F19" s="101" t="n">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="G19" s="80" t="n">
+      <x:c r="G19" s="101" t="n">
         <x:v>-8</x:v>
       </x:c>
-      <x:c r="H19" s="80" t="str">
+      <x:c r="H19" s="101" t="str">
         <x:v>Thomas Welsh</x:v>
       </x:c>
-      <x:c r="I19" s="80" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J19" s="80" t="str">
+      <x:c r="I19" s="101" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="101" t="str">
         <x:v>NO_DIRECT_MINUTES</x:v>
       </x:c>
-      <x:c r="K19" s="80" t="str">
+      <x:c r="K19" s="101" t="str">
         <x:v>ATL-side execution HOLD</x:v>
       </x:c>
-      <x:c r="L19" s="80" t="str">
+      <x:c r="L19" s="101" t="str">
         <x:v>S38/S39</x:v>
       </x:c>
-      <x:c r="M19" s="79"/>
+      <x:c r="M19" s="100"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="79"/>
-      <x:c r="B20" s="79"/>
-      <x:c r="C20" s="79"/>
-      <x:c r="D20" s="79"/>
-      <x:c r="E20" s="79"/>
-      <x:c r="F20" s="79"/>
-      <x:c r="G20" s="79"/>
-      <x:c r="H20" s="79"/>
-      <x:c r="I20" s="79"/>
-      <x:c r="J20" s="79"/>
-      <x:c r="K20" s="79"/>
-      <x:c r="L20" s="79"/>
-      <x:c r="M20" s="79"/>
+      <x:c r="A20" s="100"/>
+      <x:c r="B20" s="100"/>
+      <x:c r="C20" s="100"/>
+      <x:c r="D20" s="100"/>
+      <x:c r="E20" s="100"/>
+      <x:c r="F20" s="100"/>
+      <x:c r="G20" s="100"/>
+      <x:c r="H20" s="100"/>
+      <x:c r="I20" s="100"/>
+      <x:c r="J20" s="100"/>
+      <x:c r="K20" s="100"/>
+      <x:c r="L20" s="100"/>
+      <x:c r="M20" s="100"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="82" t="str">
+      <x:c r="A21" s="103" t="str">
         <x:v>Dallas: Metu begins inside Spalding's standard-contract / Texas assignment slot; a different Jan. 31 waiver choice remains HOLD. Denver: Spalding takes Welsh's two-way slot, Akoon-Purcell keeps the other, and Welsh moves to the undrafted free-agent market. Any minutes above the displaced-player base reopen player-game review.</x:v>
       </x:c>
-      <x:c r="B21" s="82"/>
-      <x:c r="C21" s="82"/>
-      <x:c r="D21" s="82"/>
-      <x:c r="E21" s="82"/>
-      <x:c r="F21" s="82"/>
-      <x:c r="G21" s="82"/>
-      <x:c r="H21" s="82"/>
-      <x:c r="I21" s="79"/>
+      <x:c r="B21" s="103"/>
+      <x:c r="C21" s="103"/>
+      <x:c r="D21" s="103"/>
+      <x:c r="E21" s="103"/>
+      <x:c r="F21" s="103"/>
+      <x:c r="G21" s="103"/>
+      <x:c r="H21" s="103"/>
+      <x:c r="I21" s="100"/>
       <x:c r="J21" s="51" t="str">
         <x:v>Audit</x:v>
       </x:c>
@@ -13257,145 +16127,145 @@
       <x:c r="L21" s="51" t="str">
         <x:v>Check</x:v>
       </x:c>
-      <x:c r="M21" s="79"/>
+      <x:c r="M21" s="100"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="82"/>
-      <x:c r="B22" s="82"/>
-      <x:c r="C22" s="82"/>
-      <x:c r="D22" s="82"/>
-      <x:c r="E22" s="82"/>
-      <x:c r="F22" s="82"/>
-      <x:c r="G22" s="82"/>
-      <x:c r="H22" s="82"/>
-      <x:c r="I22" s="79"/>
-      <x:c r="J22" s="80" t="str">
+      <x:c r="A22" s="103"/>
+      <x:c r="B22" s="103"/>
+      <x:c r="C22" s="103"/>
+      <x:c r="D22" s="103"/>
+      <x:c r="E22" s="103"/>
+      <x:c r="F22" s="103"/>
+      <x:c r="G22" s="103"/>
+      <x:c r="H22" s="103"/>
+      <x:c r="I22" s="100"/>
+      <x:c r="J22" s="101" t="str">
         <x:v>Changed contract chains</x:v>
       </x:c>
-      <x:c r="K22" s="80" t="n">
+      <x:c r="K22" s="101" t="n">
         <x:f>COUNTIF(K7:K12,"CF_CHANGED_STANDARD")+COUNTIF(K7:K12,"CF_CHANGED_TWO_WAY")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L22" s="80" t="str">
+      <x:c r="L22" s="101" t="str">
         <x:f>IF(K22=2,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="M22" s="79"/>
+      <x:c r="M22" s="100"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="82"/>
-      <x:c r="B23" s="82"/>
-      <x:c r="C23" s="82"/>
-      <x:c r="D23" s="82"/>
-      <x:c r="E23" s="82"/>
-      <x:c r="F23" s="82"/>
-      <x:c r="G23" s="82"/>
-      <x:c r="H23" s="82"/>
-      <x:c r="I23" s="79"/>
-      <x:c r="J23" s="80" t="str">
+      <x:c r="A23" s="103"/>
+      <x:c r="B23" s="103"/>
+      <x:c r="C23" s="103"/>
+      <x:c r="D23" s="103"/>
+      <x:c r="E23" s="103"/>
+      <x:c r="F23" s="103"/>
+      <x:c r="G23" s="103"/>
+      <x:c r="H23" s="103"/>
+      <x:c r="I23" s="100"/>
+      <x:c r="J23" s="101" t="str">
         <x:v>Direct games</x:v>
       </x:c>
-      <x:c r="K23" s="80" t="n">
+      <x:c r="K23" s="101" t="n">
         <x:f>COUNTA(A16:A19)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L23" s="80" t="str">
+      <x:c r="L23" s="101" t="str">
         <x:f>IF(K23=4,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="M23" s="79"/>
+      <x:c r="M23" s="100"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="79"/>
-      <x:c r="B24" s="79"/>
-      <x:c r="C24" s="79"/>
-      <x:c r="D24" s="79"/>
-      <x:c r="E24" s="79"/>
-      <x:c r="F24" s="79"/>
-      <x:c r="G24" s="79"/>
-      <x:c r="H24" s="79"/>
-      <x:c r="I24" s="79"/>
-      <x:c r="J24" s="80" t="str">
+      <x:c r="A24" s="100"/>
+      <x:c r="B24" s="100"/>
+      <x:c r="C24" s="100"/>
+      <x:c r="D24" s="100"/>
+      <x:c r="E24" s="100"/>
+      <x:c r="F24" s="100"/>
+      <x:c r="G24" s="100"/>
+      <x:c r="H24" s="100"/>
+      <x:c r="I24" s="100"/>
+      <x:c r="J24" s="101" t="str">
         <x:v>Direct replaced minutes</x:v>
       </x:c>
-      <x:c r="K24" s="80" t="n">
+      <x:c r="K24" s="101" t="n">
         <x:f>SUM(I16:I19)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="80" t="str">
+      <x:c r="L24" s="101" t="str">
         <x:f>IF(K24=0,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="M24" s="79"/>
+      <x:c r="M24" s="100"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="79"/>
-      <x:c r="B25" s="79"/>
-      <x:c r="C25" s="79"/>
-      <x:c r="D25" s="79"/>
-      <x:c r="E25" s="79"/>
-      <x:c r="F25" s="79"/>
-      <x:c r="G25" s="79"/>
-      <x:c r="H25" s="79"/>
-      <x:c r="I25" s="79"/>
-      <x:c r="J25" s="80" t="str">
+      <x:c r="A25" s="100"/>
+      <x:c r="B25" s="100"/>
+      <x:c r="C25" s="100"/>
+      <x:c r="D25" s="100"/>
+      <x:c r="E25" s="100"/>
+      <x:c r="F25" s="100"/>
+      <x:c r="G25" s="100"/>
+      <x:c r="H25" s="100"/>
+      <x:c r="I25" s="100"/>
+      <x:c r="J25" s="101" t="str">
         <x:v>Denver CF two-way slots</x:v>
       </x:c>
-      <x:c r="K25" s="80" t="n">
+      <x:c r="K25" s="101" t="n">
         <x:f>COUNTIF(K7:K12,"CF_CHANGED_TWO_WAY")+COUNTIF(K7:K12,"CF_PROTECTED_TWO_WAY")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L25" s="80" t="str">
+      <x:c r="L25" s="101" t="str">
         <x:f>IF(K25=2,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="M25" s="79"/>
+      <x:c r="M25" s="100"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="79"/>
-      <x:c r="B26" s="79"/>
-      <x:c r="C26" s="79"/>
-      <x:c r="D26" s="79"/>
-      <x:c r="E26" s="79"/>
-      <x:c r="F26" s="79"/>
-      <x:c r="G26" s="79"/>
-      <x:c r="H26" s="79"/>
-      <x:c r="I26" s="79"/>
-      <x:c r="J26" s="80" t="str">
+      <x:c r="A26" s="100"/>
+      <x:c r="B26" s="100"/>
+      <x:c r="C26" s="100"/>
+      <x:c r="D26" s="100"/>
+      <x:c r="E26" s="100"/>
+      <x:c r="F26" s="100"/>
+      <x:c r="G26" s="100"/>
+      <x:c r="H26" s="100"/>
+      <x:c r="I26" s="100"/>
+      <x:c r="J26" s="101" t="str">
         <x:v>Welsh duplicate blocked</x:v>
       </x:c>
-      <x:c r="K26" s="80" t="n">
+      <x:c r="K26" s="101" t="n">
         <x:f>COUNTIF(K7:K12,"CF_OUT_NO_SLOT")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L26" s="80" t="str">
+      <x:c r="L26" s="101" t="str">
         <x:f>IF(K26=1,"PASS","FAIL")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="M26" s="79"/>
+      <x:c r="M26" s="100"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="79"/>
-      <x:c r="B27" s="79"/>
-      <x:c r="C27" s="79"/>
-      <x:c r="D27" s="79"/>
-      <x:c r="E27" s="79"/>
-      <x:c r="F27" s="79"/>
-      <x:c r="G27" s="79"/>
-      <x:c r="H27" s="79"/>
-      <x:c r="I27" s="79"/>
-      <x:c r="J27" s="80" t="str">
+      <x:c r="A27" s="100"/>
+      <x:c r="B27" s="100"/>
+      <x:c r="C27" s="100"/>
+      <x:c r="D27" s="100"/>
+      <x:c r="E27" s="100"/>
+      <x:c r="F27" s="100"/>
+      <x:c r="G27" s="100"/>
+      <x:c r="H27" s="100"/>
+      <x:c r="I27" s="100"/>
+      <x:c r="J27" s="101" t="str">
         <x:v>Outcome lock</x:v>
       </x:c>
-      <x:c r="K27" s="80" t="str">
+      <x:c r="K27" s="101" t="str">
         <x:f>IF(AND(K24=0,K25=2,K26=1),"CASCADE DIRECT PASS","REVIEW")</x:f>
         <x:v>CASCADE DIRECT PASS</x:v>
       </x:c>
-      <x:c r="L27" s="80" t="str">
+      <x:c r="L27" s="101" t="str">
         <x:f>IF(K27="CASCADE DIRECT PASS","PASS","HOLD")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="M27" s="79"/>
+      <x:c r="M27" s="100"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -13404,13 +16274,13 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb01f3f1699ff4536"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d30f4bfca8246db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79f8176844bc4bfb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re099e542549648ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -13476,10 +16346,10 @@
       <x:c r="D5" s="17" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E5" s="84" t="n">
+      <x:c r="E5" s="104" t="n">
         <x:v>0.105</x:v>
       </x:c>
-      <x:c r="F5" s="84" t="n">
+      <x:c r="F5" s="104" t="n">
         <x:v>0.4212</x:v>
       </x:c>
       <x:c r="G5" s="17" t="n">
@@ -13508,10 +16378,10 @@
       <x:c r="D6" s="17" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E6" s="84" t="n">
+      <x:c r="E6" s="104" t="n">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="F6" s="84" t="n">
+      <x:c r="F6" s="104" t="n">
         <x:v>0.263</x:v>
       </x:c>
       <x:c r="G6" s="17" t="n">
@@ -13607,8 +16477,8 @@
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="87" t="str">
-        <x:v>FINAL BLOCKER: Atlanta's 82-game donor vector is balanced. Name the 183.1-minute reserve receivers, then execute preregistered impacts before standings/lottery.</x:v>
+      <x:c r="A14" s="107" t="str">
+        <x:v>FINAL BLOCKER: Atlanta's 82-game donor vector and 183.1 named receiver allocation are balanced. Preregister production and impact priors before standings/lottery.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13620,271 +16490,4 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>R09 AUDIT GATES</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="11" t="str">
-        <x:v>Gate</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="str">
-        <x:v>Requirement</x:v>
-      </x:c>
-      <x:c r="C4" s="11" t="str">
-        <x:v>Current evidence</x:v>
-      </x:c>
-      <x:c r="D4" s="11" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="E4" s="11" t="str">
-        <x:v>Blocks</x:v>
-      </x:c>
-      <x:c r="F4" s="11" t="str">
-        <x:v>Next action</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="75" t="str">
-        <x:v>G0</x:v>
-      </x:c>
-      <x:c r="B5" s="75" t="str">
-        <x:v>Changed-pick contract and direct-game baselines</x:v>
-      </x:c>
-      <x:c r="C5" s="75" t="str">
-        <x:v>Spurs 145.4 min; Dallas 1 min; Denver 36 min; ATL series all 0</x:v>
-      </x:c>
-      <x:c r="D5" s="77" t="str">
-        <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="E5" s="75" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="F5" s="75" t="str">
-        <x:v>Preserve team-specific caps and triggers</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="75" t="str">
-        <x:v>G1</x:v>
-      </x:c>
-      <x:c r="B6" s="75" t="str">
-        <x:v>82 unique + 29-53 + score/OT checksum</x:v>
-      </x:c>
-      <x:c r="C6" s="75" t="str">
-        <x:v>82 rows; 29-53; 9,294 pts; 19,855 game-min</x:v>
-      </x:c>
-      <x:c r="D6" s="77" t="str">
-        <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="E6" s="75" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="F6" s="75" t="str">
-        <x:v>Preserve immutable baseline</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="75" t="str">
-        <x:v>G2</x:v>
-      </x:c>
-      <x:c r="B7" s="75" t="str">
-        <x:v>Rotation/assignment/impact priors before results</x:v>
-      </x:c>
-      <x:c r="C7" s="75" t="str">
-        <x:v>≥7 donor gate; 16 cap; Nov. 19 cost; Dec. 7-22 Erie</x:v>
-      </x:c>
-      <x:c r="D7" s="77" t="str">
-        <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="E7" s="75" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="F7" s="75" t="str">
-        <x:v>Preserve before outcome model</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="75" t="str">
-        <x:v>G3</x:v>
-      </x:c>
-      <x:c r="B8" s="75" t="str">
-        <x:v>Every game minute-conserved; no NBA/Erie collision</x:v>
-      </x:c>
-      <x:c r="C8" s="75" t="str">
-        <x:v>621.9 protagonist + 183.1 remainder = 805.0; Erie dates NBA 0</x:v>
-      </x:c>
-      <x:c r="D8" s="77" t="str">
-        <x:v>PASS_WITH_BRIDGE</x:v>
-      </x:c>
-      <x:c r="E8" s="75" t="str">
-        <x:v>Named box scores</x:v>
-      </x:c>
-      <x:c r="F8" s="75" t="str">
-        <x:v>Resolve ATL remainder recipients</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="75" t="str">
-        <x:v>G4</x:v>
-      </x:c>
-      <x:c r="B9" s="75" t="str">
-        <x:v>All 82 games contact classified</x:v>
-      </x:c>
-      <x:c r="C9" s="75" t="str">
-        <x:v>43 DIRECT / 39 ROSTER</x:v>
-      </x:c>
-      <x:c r="D9" s="77" t="str">
-        <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="E9" s="75" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="F9" s="75" t="str">
-        <x:v>Upgrade CASCADE only with evidence</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="75" t="str">
-        <x:v>G5</x:v>
-      </x:c>
-      <x:c r="B10" s="75" t="str">
-        <x:v>Pregame-only pB; fixed latent u; no manual flip</x:v>
-      </x:c>
-      <x:c r="C10" s="75" t="str">
-        <x:v>Method selected; inputs absent</x:v>
-      </x:c>
-      <x:c r="D10" s="77" t="str">
-        <x:v>HOLD</x:v>
-      </x:c>
-      <x:c r="E10" s="75" t="str">
-        <x:v>CF result</x:v>
-      </x:c>
-      <x:c r="F10" s="75" t="str">
-        <x:v>Calibrate and preregister</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="75" t="str">
-        <x:v>G6</x:v>
-      </x:c>
-      <x:c r="B11" s="75" t="str">
-        <x:v>Chronological injury/fatigue/trade updates</x:v>
-      </x:c>
-      <x:c r="C11" s="75" t="str">
-        <x:v>Not executed</x:v>
-      </x:c>
-      <x:c r="D11" s="77" t="str">
-        <x:v>HOLD</x:v>
-      </x:c>
-      <x:c r="E11" s="75" t="str">
-        <x:v>CF result</x:v>
-      </x:c>
-      <x:c r="F11" s="75" t="str">
-        <x:v>Process in date order</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="75" t="str">
-        <x:v>G7</x:v>
-      </x:c>
-      <x:c r="B12" s="75" t="str">
-        <x:v>No exact score invention; sensitivity isolated</x:v>
-      </x:c>
-      <x:c r="C12" s="75" t="str">
-        <x:v>No CF scores/results created</x:v>
-      </x:c>
-      <x:c r="D12" s="77" t="str">
-        <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="E12" s="75" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="F12" s="75" t="str">
-        <x:v>Keep results HOLD until model</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="75" t="str">
-        <x:v>G8</x:v>
-      </x:c>
-      <x:c r="B13" s="75" t="str">
-        <x:v>Opponent W/L + league standings/tiebreaker</x:v>
-      </x:c>
-      <x:c r="C13" s="75" t="str">
-        <x:v>Not executed</x:v>
-      </x:c>
-      <x:c r="D13" s="77" t="str">
-        <x:v>HOLD</x:v>
-      </x:c>
-      <x:c r="E13" s="75" t="str">
-        <x:v>2019 lottery</x:v>
-      </x:c>
-      <x:c r="F13" s="75" t="str">
-        <x:v>Build league bridge</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="75" t="str">
-        <x:v>G9</x:v>
-      </x:c>
-      <x:c r="B14" s="75" t="str">
-        <x:v>Raw baseline immutable; run/model/seed logged</x:v>
-      </x:c>
-      <x:c r="C14" s="75" t="str">
-        <x:v>Baseline + date-level allocation rule recorded</x:v>
-      </x:c>
-      <x:c r="D14" s="77" t="str">
-        <x:v>PARTIAL</x:v>
-      </x:c>
-      <x:c r="E14" s="75" t="str">
-        <x:v>Reproduction</x:v>
-      </x:c>
-      <x:c r="F14" s="75" t="str">
-        <x:v>Add outcome-model run manifest</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="89"/>
-      <x:c r="B15" s="89"/>
-      <x:c r="C15" s="89"/>
-      <x:c r="D15" s="89"/>
-      <x:c r="E15" s="89"/>
-      <x:c r="F15" s="89"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="74" t="str">
-        <x:v>OVERALL</x:v>
-      </x:c>
-      <x:c r="B16" s="74" t="str">
-        <x:v>ATL_DONOR_VECTOR_PASS / OUTCOME_HOLD</x:v>
-      </x:c>
-      <x:c r="C16" s="74"/>
-      <x:c r="D16" s="74"/>
-      <x:c r="E16" s="74"/>
-      <x:c r="F16" s="74" t="str">
-        <x:v>Name 183.1-minute ATL remainder recipients before player box-score execution</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:F2"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>